--- a/public/files/report_card_templates/JHS.xlsx
+++ b/public/files/report_card_templates/JHS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\schoolsys\public\files\report_card_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DB32D3-B808-47E6-AE85-A1BE0BC86AD4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEF45E4-AC18-4BBD-9571-311C703ECD04}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -504,14 +504,158 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -542,156 +686,23 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1032,260 +1043,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O1" s="61" t="s">
+      <c r="O1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
-      <c r="U1" s="61"/>
-      <c r="V1" s="61"/>
-      <c r="W1" s="61"/>
-      <c r="X1" s="61"/>
-      <c r="Y1" s="61"/>
-      <c r="Z1" s="61"/>
-      <c r="AA1" s="61"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
     </row>
     <row r="2" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="Q2" s="15" t="s">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="Q2" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
     </row>
     <row r="3" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55"/>
-      <c r="V3" s="62" t="s">
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="55"/>
-      <c r="AA3" s="55"/>
-      <c r="AB3" s="55"/>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="55"/>
-      <c r="AE3" s="55"/>
-      <c r="AF3" s="55"/>
-      <c r="AG3" s="55"/>
-      <c r="AH3" s="55"/>
-      <c r="AI3" s="55"/>
-      <c r="AJ3" s="55"/>
-      <c r="AK3" s="55"/>
-      <c r="AL3" s="55"/>
-      <c r="AM3" s="55"/>
-      <c r="AN3" s="55"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="45"/>
+      <c r="AM3" s="45"/>
+      <c r="AN3" s="45"/>
     </row>
     <row r="4" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="59" t="s">
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="59"/>
-      <c r="S4" s="59"/>
-      <c r="T4" s="59"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="56"/>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="56"/>
-      <c r="AG4" s="56"/>
-      <c r="AH4" s="59"/>
-      <c r="AI4" s="59"/>
-      <c r="AJ4" s="59"/>
-      <c r="AK4" s="59"/>
-      <c r="AL4" s="59"/>
-      <c r="AM4" s="59"/>
-      <c r="AN4" s="59"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
+      <c r="Z4" s="46"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="46"/>
+      <c r="AD4" s="46"/>
+      <c r="AE4" s="46"/>
+      <c r="AF4" s="46"/>
+      <c r="AG4" s="46"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
     </row>
     <row r="5" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="19" t="s">
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="47"/>
+      <c r="X5" s="47"/>
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="47"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="AE5" s="20"/>
-      <c r="AF5" s="20"/>
-      <c r="AG5" s="20"/>
-      <c r="AH5" s="20"/>
-      <c r="AI5" s="21"/>
-      <c r="AJ5" s="19" t="s">
+      <c r="AE5" s="68"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="69"/>
+      <c r="AJ5" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="AK5" s="20"/>
-      <c r="AL5" s="20"/>
-      <c r="AM5" s="20"/>
-      <c r="AN5" s="21"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
+      <c r="AM5" s="68"/>
+      <c r="AN5" s="69"/>
     </row>
     <row r="6" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="57" t="s">
+      <c r="A6" s="47"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="O6" s="57"/>
-      <c r="P6" s="57"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="57" t="s">
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="S6" s="57"/>
-      <c r="T6" s="57"/>
-      <c r="U6" s="57"/>
-      <c r="V6" s="57" t="s">
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="57"/>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="57" t="s">
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="57"/>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="23"/>
-      <c r="AF6" s="23"/>
-      <c r="AG6" s="23"/>
-      <c r="AH6" s="23"/>
-      <c r="AI6" s="24"/>
-      <c r="AJ6" s="22"/>
-      <c r="AK6" s="23"/>
-      <c r="AL6" s="23"/>
-      <c r="AM6" s="23"/>
-      <c r="AN6" s="24"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="70"/>
+      <c r="AE6" s="71"/>
+      <c r="AF6" s="71"/>
+      <c r="AG6" s="71"/>
+      <c r="AH6" s="71"/>
+      <c r="AI6" s="72"/>
+      <c r="AJ6" s="70"/>
+      <c r="AK6" s="71"/>
+      <c r="AL6" s="71"/>
+      <c r="AM6" s="71"/>
+      <c r="AN6" s="72"/>
     </row>
     <row r="7" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
       <c r="N7" s="28"/>
       <c r="O7" s="28"/>
       <c r="P7" s="28"/>
@@ -1302,15 +1313,15 @@
       <c r="AA7" s="28"/>
       <c r="AB7" s="28"/>
       <c r="AC7" s="28"/>
-      <c r="AD7" s="29" t="str">
+      <c r="AD7" s="25" t="str">
         <f>IF(COUNT(N7:AC7)=4,SUM(N7:AC7)/4,"")</f>
         <v/>
       </c>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="31"/>
+      <c r="AE7" s="26"/>
+      <c r="AF7" s="26"/>
+      <c r="AG7" s="26"/>
+      <c r="AH7" s="26"/>
+      <c r="AI7" s="27"/>
       <c r="AJ7" s="28" t="str">
         <f>IF(AD7&lt;&gt;"",IF(AD7&gt;=75,"Passed","Failed"),"")</f>
         <v/>
@@ -1321,21 +1332,21 @@
       <c r="AN7" s="28"/>
     </row>
     <row r="8" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
       <c r="N8" s="28"/>
       <c r="O8" s="28"/>
       <c r="P8" s="28"/>
@@ -1352,15 +1363,15 @@
       <c r="AA8" s="28"/>
       <c r="AB8" s="28"/>
       <c r="AC8" s="28"/>
-      <c r="AD8" s="29" t="str">
+      <c r="AD8" s="25" t="str">
         <f t="shared" ref="AD8:AD19" si="0">IF(COUNT(N8:AC8)=4,SUM(N8:AC8)/4,"")</f>
         <v/>
       </c>
-      <c r="AE8" s="30"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="30"/>
-      <c r="AH8" s="30"/>
-      <c r="AI8" s="31"/>
+      <c r="AE8" s="26"/>
+      <c r="AF8" s="26"/>
+      <c r="AG8" s="26"/>
+      <c r="AH8" s="26"/>
+      <c r="AI8" s="27"/>
       <c r="AJ8" s="28" t="str">
         <f t="shared" ref="AJ8:AJ19" si="1">IF(AD8&lt;&gt;"",IF(AD8&gt;=75,"Passed","Failed"),"")</f>
         <v/>
@@ -1371,21 +1382,21 @@
       <c r="AN8" s="28"/>
     </row>
     <row r="9" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
       <c r="N9" s="28"/>
       <c r="O9" s="28"/>
       <c r="P9" s="28"/>
@@ -1402,15 +1413,15 @@
       <c r="AA9" s="28"/>
       <c r="AB9" s="28"/>
       <c r="AC9" s="28"/>
-      <c r="AD9" s="29" t="str">
+      <c r="AD9" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE9" s="30"/>
-      <c r="AF9" s="30"/>
-      <c r="AG9" s="30"/>
-      <c r="AH9" s="30"/>
-      <c r="AI9" s="31"/>
+      <c r="AE9" s="26"/>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26"/>
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="27"/>
       <c r="AJ9" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1421,21 +1432,21 @@
       <c r="AN9" s="28"/>
     </row>
     <row r="10" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="27"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="40"/>
       <c r="N10" s="28"/>
       <c r="O10" s="28"/>
       <c r="P10" s="28"/>
@@ -1452,15 +1463,15 @@
       <c r="AA10" s="28"/>
       <c r="AB10" s="28"/>
       <c r="AC10" s="28"/>
-      <c r="AD10" s="29" t="str">
+      <c r="AD10" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="30"/>
-      <c r="AG10" s="30"/>
-      <c r="AH10" s="30"/>
-      <c r="AI10" s="31"/>
+      <c r="AE10" s="26"/>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="26"/>
+      <c r="AH10" s="26"/>
+      <c r="AI10" s="27"/>
       <c r="AJ10" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1471,21 +1482,21 @@
       <c r="AN10" s="28"/>
     </row>
     <row r="11" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="49"/>
-      <c r="M11" s="49"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
       <c r="N11" s="28"/>
       <c r="O11" s="28"/>
       <c r="P11" s="28"/>
@@ -1502,15 +1513,15 @@
       <c r="AA11" s="28"/>
       <c r="AB11" s="28"/>
       <c r="AC11" s="28"/>
-      <c r="AD11" s="29" t="str">
+      <c r="AD11" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="30"/>
-      <c r="AG11" s="30"/>
-      <c r="AH11" s="30"/>
-      <c r="AI11" s="31"/>
+      <c r="AE11" s="26"/>
+      <c r="AF11" s="26"/>
+      <c r="AG11" s="26"/>
+      <c r="AH11" s="26"/>
+      <c r="AI11" s="27"/>
       <c r="AJ11" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1521,21 +1532,21 @@
       <c r="AN11" s="28"/>
     </row>
     <row r="12" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="54"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="44"/>
       <c r="N12" s="28"/>
       <c r="O12" s="28"/>
       <c r="P12" s="28"/>
@@ -1552,15 +1563,15 @@
       <c r="AA12" s="28"/>
       <c r="AB12" s="28"/>
       <c r="AC12" s="28"/>
-      <c r="AD12" s="29" t="str">
+      <c r="AD12" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE12" s="30"/>
-      <c r="AF12" s="30"/>
-      <c r="AG12" s="30"/>
-      <c r="AH12" s="30"/>
-      <c r="AI12" s="31"/>
+      <c r="AE12" s="26"/>
+      <c r="AF12" s="26"/>
+      <c r="AG12" s="26"/>
+      <c r="AH12" s="26"/>
+      <c r="AI12" s="27"/>
       <c r="AJ12" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1571,21 +1582,21 @@
       <c r="AN12" s="28"/>
     </row>
     <row r="13" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
       <c r="N13" s="28"/>
       <c r="O13" s="28"/>
       <c r="P13" s="28"/>
@@ -1602,15 +1613,15 @@
       <c r="AA13" s="28"/>
       <c r="AB13" s="28"/>
       <c r="AC13" s="28"/>
-      <c r="AD13" s="29" t="str">
+      <c r="AD13" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE13" s="30"/>
-      <c r="AF13" s="30"/>
-      <c r="AG13" s="30"/>
-      <c r="AH13" s="30"/>
-      <c r="AI13" s="31"/>
+      <c r="AE13" s="26"/>
+      <c r="AF13" s="26"/>
+      <c r="AG13" s="26"/>
+      <c r="AH13" s="26"/>
+      <c r="AI13" s="27"/>
       <c r="AJ13" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1622,20 +1633,20 @@
     </row>
     <row r="14" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="27"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="40"/>
       <c r="N14" s="28"/>
       <c r="O14" s="28"/>
       <c r="P14" s="28"/>
@@ -1652,15 +1663,15 @@
       <c r="AA14" s="28"/>
       <c r="AB14" s="28"/>
       <c r="AC14" s="28"/>
-      <c r="AD14" s="29" t="str">
+      <c r="AD14" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE14" s="30"/>
-      <c r="AF14" s="30"/>
-      <c r="AG14" s="30"/>
-      <c r="AH14" s="30"/>
-      <c r="AI14" s="31"/>
+      <c r="AE14" s="26"/>
+      <c r="AF14" s="26"/>
+      <c r="AG14" s="26"/>
+      <c r="AH14" s="26"/>
+      <c r="AI14" s="27"/>
       <c r="AJ14" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1672,20 +1683,20 @@
     </row>
     <row r="15" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="27"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="40"/>
       <c r="N15" s="28"/>
       <c r="O15" s="28"/>
       <c r="P15" s="28"/>
@@ -1702,15 +1713,15 @@
       <c r="AA15" s="28"/>
       <c r="AB15" s="28"/>
       <c r="AC15" s="28"/>
-      <c r="AD15" s="29" t="str">
+      <c r="AD15" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE15" s="30"/>
-      <c r="AF15" s="30"/>
-      <c r="AG15" s="30"/>
-      <c r="AH15" s="30"/>
-      <c r="AI15" s="31"/>
+      <c r="AE15" s="26"/>
+      <c r="AF15" s="26"/>
+      <c r="AG15" s="26"/>
+      <c r="AH15" s="26"/>
+      <c r="AI15" s="27"/>
       <c r="AJ15" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1722,20 +1733,20 @@
     </row>
     <row r="16" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="27"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="40"/>
       <c r="N16" s="28"/>
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
@@ -1752,15 +1763,15 @@
       <c r="AA16" s="28"/>
       <c r="AB16" s="28"/>
       <c r="AC16" s="28"/>
-      <c r="AD16" s="29" t="str">
+      <c r="AD16" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE16" s="30"/>
-      <c r="AF16" s="30"/>
-      <c r="AG16" s="30"/>
-      <c r="AH16" s="30"/>
-      <c r="AI16" s="31"/>
+      <c r="AE16" s="26"/>
+      <c r="AF16" s="26"/>
+      <c r="AG16" s="26"/>
+      <c r="AH16" s="26"/>
+      <c r="AI16" s="27"/>
       <c r="AJ16" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1772,20 +1783,20 @@
     </row>
     <row r="17" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="27"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="40"/>
       <c r="N17" s="28"/>
       <c r="O17" s="28"/>
       <c r="P17" s="28"/>
@@ -1802,15 +1813,15 @@
       <c r="AA17" s="28"/>
       <c r="AB17" s="28"/>
       <c r="AC17" s="28"/>
-      <c r="AD17" s="29" t="str">
+      <c r="AD17" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE17" s="30"/>
-      <c r="AF17" s="30"/>
-      <c r="AG17" s="30"/>
-      <c r="AH17" s="30"/>
-      <c r="AI17" s="31"/>
+      <c r="AE17" s="26"/>
+      <c r="AF17" s="26"/>
+      <c r="AG17" s="26"/>
+      <c r="AH17" s="26"/>
+      <c r="AI17" s="27"/>
       <c r="AJ17" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1821,21 +1832,21 @@
       <c r="AN17" s="28"/>
     </row>
     <row r="18" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
       <c r="N18" s="28"/>
       <c r="O18" s="28"/>
       <c r="P18" s="28"/>
@@ -1852,15 +1863,15 @@
       <c r="AA18" s="28"/>
       <c r="AB18" s="28"/>
       <c r="AC18" s="28"/>
-      <c r="AD18" s="29" t="str">
+      <c r="AD18" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE18" s="30"/>
-      <c r="AF18" s="30"/>
-      <c r="AG18" s="30"/>
-      <c r="AH18" s="30"/>
-      <c r="AI18" s="31"/>
+      <c r="AE18" s="26"/>
+      <c r="AF18" s="26"/>
+      <c r="AG18" s="26"/>
+      <c r="AH18" s="26"/>
+      <c r="AI18" s="27"/>
       <c r="AJ18" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1871,21 +1882,21 @@
       <c r="AN18" s="28"/>
     </row>
     <row r="19" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
       <c r="N19" s="28"/>
       <c r="O19" s="28"/>
       <c r="P19" s="28"/>
@@ -1902,15 +1913,15 @@
       <c r="AA19" s="28"/>
       <c r="AB19" s="28"/>
       <c r="AC19" s="28"/>
-      <c r="AD19" s="29" t="str">
+      <c r="AD19" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="30"/>
-      <c r="AH19" s="30"/>
-      <c r="AI19" s="31"/>
+      <c r="AE19" s="26"/>
+      <c r="AF19" s="26"/>
+      <c r="AG19" s="26"/>
+      <c r="AH19" s="26"/>
+      <c r="AI19" s="27"/>
       <c r="AJ19" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1923,53 +1934,53 @@
     <row r="20" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="46" t="str">
-        <f>IF($AD21&lt;&gt;"",SUM(N7:Q13,N18)/8,"")</f>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="38" t="str">
+        <f>IF(SUM(N7:Q13,N18)/8 &gt; 0, SUM(N7:Q13,N18)/8, "")</f>
         <v/>
       </c>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="46" t="str">
-        <f t="shared" ref="R20" si="2">IF($AD21&lt;&gt;"",SUM(R7:U13,R18)/8,"")</f>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38" t="str">
+        <f t="shared" ref="R20" si="2">IF(SUM(R7:U13,R18)/8 &gt; 0, SUM(R7:U13,R18)/8, "")</f>
         <v/>
       </c>
-      <c r="S20" s="46"/>
-      <c r="T20" s="46"/>
-      <c r="U20" s="46"/>
-      <c r="V20" s="46" t="str">
-        <f t="shared" ref="V20" si="3">IF($AD21&lt;&gt;"",SUM(V7:Y13,V18)/8,"")</f>
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38" t="str">
+        <f t="shared" ref="V20" si="3">IF(SUM(V7:Y13,V18)/8 &gt; 0, SUM(V7:Y13,V18)/8, "")</f>
         <v/>
       </c>
-      <c r="W20" s="46"/>
-      <c r="X20" s="46"/>
-      <c r="Y20" s="46"/>
-      <c r="Z20" s="46" t="str">
-        <f t="shared" ref="Z20" si="4">IF($AD21&lt;&gt;"",SUM(Z7:AC13,Z18)/8,"")</f>
+      <c r="W20" s="38"/>
+      <c r="X20" s="38"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="38" t="str">
+        <f t="shared" ref="Z20" si="4">IF(SUM(Z7:AC13,Z18)/8 &gt; 0, SUM(Z7:AC13,Z18)/8, "")</f>
         <v/>
       </c>
-      <c r="AA20" s="46"/>
-      <c r="AB20" s="46"/>
-      <c r="AC20" s="46"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
-      <c r="AG20" s="30"/>
-      <c r="AH20" s="30"/>
-      <c r="AI20" s="31"/>
+      <c r="AA20" s="38"/>
+      <c r="AB20" s="38"/>
+      <c r="AC20" s="38"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="26"/>
+      <c r="AF20" s="26"/>
+      <c r="AG20" s="26"/>
+      <c r="AH20" s="26"/>
+      <c r="AI20" s="27"/>
       <c r="AJ20" s="28"/>
       <c r="AK20" s="28"/>
       <c r="AL20" s="28"/>
@@ -1979,51 +1990,51 @@
     <row r="21" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="37" t="s">
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="38"/>
-      <c r="V21" s="38"/>
-      <c r="W21" s="38"/>
-      <c r="X21" s="38"/>
-      <c r="Y21" s="38"/>
-      <c r="Z21" s="38"/>
-      <c r="AA21" s="38"/>
-      <c r="AB21" s="38"/>
-      <c r="AC21" s="39"/>
-      <c r="AD21" s="63" t="str">
+      <c r="O21" s="59"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="59"/>
+      <c r="R21" s="59"/>
+      <c r="S21" s="59"/>
+      <c r="T21" s="59"/>
+      <c r="U21" s="59"/>
+      <c r="V21" s="59"/>
+      <c r="W21" s="59"/>
+      <c r="X21" s="59"/>
+      <c r="Y21" s="59"/>
+      <c r="Z21" s="59"/>
+      <c r="AA21" s="59"/>
+      <c r="AB21" s="59"/>
+      <c r="AC21" s="60"/>
+      <c r="AD21" s="29" t="str">
         <f>IF(COUNT(AD7:AI13,AD18)=8,SUM(AD7:AI13,AD18)/8,"")</f>
         <v/>
       </c>
-      <c r="AE21" s="64"/>
-      <c r="AF21" s="64"/>
-      <c r="AG21" s="64"/>
-      <c r="AH21" s="64"/>
-      <c r="AI21" s="65"/>
-      <c r="AJ21" s="57"/>
-      <c r="AK21" s="57"/>
-      <c r="AL21" s="57"/>
-      <c r="AM21" s="57"/>
-      <c r="AN21" s="57"/>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="30"/>
+      <c r="AG21" s="30"/>
+      <c r="AH21" s="30"/>
+      <c r="AI21" s="31"/>
+      <c r="AJ21" s="32"/>
+      <c r="AK21" s="32"/>
+      <c r="AL21" s="32"/>
+      <c r="AM21" s="32"/>
+      <c r="AN21" s="32"/>
     </row>
     <row r="22" spans="1:40" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
@@ -2055,12 +2066,12 @@
       <c r="AA22" s="10"/>
       <c r="AB22" s="10"/>
       <c r="AC22" s="10"/>
-      <c r="AD22" s="68"/>
-      <c r="AE22" s="68"/>
-      <c r="AF22" s="68"/>
-      <c r="AG22" s="68"/>
-      <c r="AH22" s="68"/>
-      <c r="AI22" s="68"/>
+      <c r="AD22" s="13"/>
+      <c r="AE22" s="13"/>
+      <c r="AF22" s="13"/>
+      <c r="AG22" s="13"/>
+      <c r="AH22" s="13"/>
+      <c r="AI22" s="13"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
@@ -2097,367 +2108,367 @@
       <c r="Y23" s="2"/>
     </row>
     <row r="24" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="34" t="s">
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="47"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34" t="s">
+      <c r="Q24" s="55"/>
+      <c r="R24" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="S24" s="34"/>
-      <c r="T24" s="34" t="s">
+      <c r="S24" s="55"/>
+      <c r="T24" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="U24" s="34"/>
-      <c r="V24" s="34" t="s">
+      <c r="U24" s="55"/>
+      <c r="V24" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="W24" s="34"/>
-      <c r="Y24" s="17" t="s">
+      <c r="W24" s="55"/>
+      <c r="Y24" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="Z24" s="17"/>
-      <c r="AA24" s="17"/>
-      <c r="AB24" s="17"/>
-      <c r="AC24" s="17"/>
-      <c r="AD24" s="17"/>
-      <c r="AE24" s="17"/>
-      <c r="AF24" s="17"/>
-      <c r="AG24" s="17"/>
-      <c r="AH24" s="17"/>
-      <c r="AI24" s="17"/>
-      <c r="AJ24" s="17"/>
+      <c r="Z24" s="65"/>
+      <c r="AA24" s="65"/>
+      <c r="AB24" s="65"/>
+      <c r="AC24" s="65"/>
+      <c r="AD24" s="65"/>
+      <c r="AE24" s="65"/>
+      <c r="AF24" s="65"/>
+      <c r="AG24" s="65"/>
+      <c r="AH24" s="65"/>
+      <c r="AI24" s="65"/>
+      <c r="AJ24" s="65"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
       <c r="AN24" s="3"/>
     </row>
     <row r="25" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="44"/>
-      <c r="R25" s="44"/>
-      <c r="S25" s="44"/>
-      <c r="T25" s="44"/>
-      <c r="U25" s="44"/>
-      <c r="V25" s="45"/>
-      <c r="W25" s="45"/>
-      <c r="Y25" s="18" t="s">
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="Y25" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="Z25" s="18"/>
-      <c r="AA25" s="18"/>
-      <c r="AB25" s="18"/>
-      <c r="AC25" s="18"/>
-      <c r="AD25" s="18"/>
-      <c r="AE25" s="18"/>
-      <c r="AF25" s="18"/>
-      <c r="AG25" s="18"/>
-      <c r="AH25" s="18"/>
-      <c r="AI25" s="18"/>
-      <c r="AJ25" s="18"/>
-      <c r="AK25" s="18"/>
-      <c r="AL25" s="18"/>
-      <c r="AM25" s="18"/>
+      <c r="Z25" s="66"/>
+      <c r="AA25" s="66"/>
+      <c r="AB25" s="66"/>
+      <c r="AC25" s="66"/>
+      <c r="AD25" s="66"/>
+      <c r="AE25" s="66"/>
+      <c r="AF25" s="66"/>
+      <c r="AG25" s="66"/>
+      <c r="AH25" s="66"/>
+      <c r="AI25" s="66"/>
+      <c r="AJ25" s="66"/>
+      <c r="AK25" s="66"/>
+      <c r="AL25" s="66"/>
+      <c r="AM25" s="66"/>
       <c r="AN25" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="45"/>
-      <c r="U26" s="45"/>
-      <c r="V26" s="45"/>
-      <c r="W26" s="45"/>
-      <c r="Y26" s="18" t="s">
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="Y26" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="Z26" s="18"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="18"/>
-      <c r="AC26" s="18"/>
-      <c r="AD26" s="18"/>
-      <c r="AE26" s="18"/>
-      <c r="AF26" s="18"/>
-      <c r="AG26" s="18"/>
-      <c r="AH26" s="18"/>
-      <c r="AI26" s="18"/>
-      <c r="AJ26" s="18"/>
-      <c r="AK26" s="18"/>
-      <c r="AL26" s="18"/>
-      <c r="AM26" s="18"/>
+      <c r="Z26" s="66"/>
+      <c r="AA26" s="66"/>
+      <c r="AB26" s="66"/>
+      <c r="AC26" s="66"/>
+      <c r="AD26" s="66"/>
+      <c r="AE26" s="66"/>
+      <c r="AF26" s="66"/>
+      <c r="AG26" s="66"/>
+      <c r="AH26" s="66"/>
+      <c r="AI26" s="66"/>
+      <c r="AJ26" s="66"/>
+      <c r="AK26" s="66"/>
+      <c r="AL26" s="66"/>
+      <c r="AM26" s="66"/>
       <c r="AN26" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="45"/>
-      <c r="U27" s="45"/>
-      <c r="V27" s="45"/>
-      <c r="W27" s="45"/>
-      <c r="Y27" s="18" t="s">
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="Y27" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="Z27" s="18"/>
-      <c r="AA27" s="18"/>
-      <c r="AB27" s="18"/>
-      <c r="AC27" s="18"/>
-      <c r="AD27" s="18"/>
-      <c r="AE27" s="18"/>
-      <c r="AF27" s="18"/>
-      <c r="AG27" s="18"/>
-      <c r="AH27" s="18"/>
-      <c r="AI27" s="18"/>
-      <c r="AJ27" s="18"/>
-      <c r="AK27" s="18"/>
-      <c r="AL27" s="18"/>
-      <c r="AM27" s="18"/>
+      <c r="Z27" s="66"/>
+      <c r="AA27" s="66"/>
+      <c r="AB27" s="66"/>
+      <c r="AC27" s="66"/>
+      <c r="AD27" s="66"/>
+      <c r="AE27" s="66"/>
+      <c r="AF27" s="66"/>
+      <c r="AG27" s="66"/>
+      <c r="AH27" s="66"/>
+      <c r="AI27" s="66"/>
+      <c r="AJ27" s="66"/>
+      <c r="AK27" s="66"/>
+      <c r="AL27" s="66"/>
+      <c r="AM27" s="66"/>
       <c r="AN27" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="45"/>
-      <c r="U28" s="45"/>
-      <c r="V28" s="45"/>
-      <c r="W28" s="45"/>
-      <c r="Y28" s="18" t="s">
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="Y28" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="Z28" s="18"/>
-      <c r="AA28" s="18"/>
-      <c r="AB28" s="18"/>
-      <c r="AC28" s="18"/>
-      <c r="AD28" s="18"/>
-      <c r="AE28" s="18"/>
-      <c r="AF28" s="18"/>
-      <c r="AG28" s="18"/>
-      <c r="AH28" s="18"/>
-      <c r="AI28" s="18"/>
-      <c r="AJ28" s="18"/>
-      <c r="AK28" s="18"/>
-      <c r="AL28" s="18"/>
-      <c r="AM28" s="18"/>
+      <c r="Z28" s="66"/>
+      <c r="AA28" s="66"/>
+      <c r="AB28" s="66"/>
+      <c r="AC28" s="66"/>
+      <c r="AD28" s="66"/>
+      <c r="AE28" s="66"/>
+      <c r="AF28" s="66"/>
+      <c r="AG28" s="66"/>
+      <c r="AH28" s="66"/>
+      <c r="AI28" s="66"/>
+      <c r="AJ28" s="66"/>
+      <c r="AK28" s="66"/>
+      <c r="AL28" s="66"/>
+      <c r="AM28" s="66"/>
       <c r="AN28" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="41" t="s">
+      <c r="A29" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="45"/>
-      <c r="U29" s="45"/>
-      <c r="V29" s="45"/>
-      <c r="W29" s="45"/>
-      <c r="Y29" s="18" t="s">
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="53"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="Y29" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="Z29" s="18"/>
-      <c r="AA29" s="18"/>
-      <c r="AB29" s="18"/>
-      <c r="AC29" s="18"/>
-      <c r="AD29" s="18"/>
-      <c r="AE29" s="18"/>
-      <c r="AF29" s="18"/>
-      <c r="AG29" s="18"/>
-      <c r="AH29" s="18"/>
-      <c r="AI29" s="18"/>
-      <c r="AJ29" s="18"/>
-      <c r="AK29" s="18"/>
-      <c r="AL29" s="18"/>
-      <c r="AM29" s="18"/>
+      <c r="Z29" s="66"/>
+      <c r="AA29" s="66"/>
+      <c r="AB29" s="66"/>
+      <c r="AC29" s="66"/>
+      <c r="AD29" s="66"/>
+      <c r="AE29" s="66"/>
+      <c r="AF29" s="66"/>
+      <c r="AG29" s="66"/>
+      <c r="AH29" s="66"/>
+      <c r="AI29" s="66"/>
+      <c r="AJ29" s="66"/>
+      <c r="AK29" s="66"/>
+      <c r="AL29" s="66"/>
+      <c r="AM29" s="66"/>
       <c r="AN29" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="45"/>
-      <c r="U30" s="45"/>
-      <c r="V30" s="45"/>
-      <c r="W30" s="45"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="53"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
       <c r="X30" s="3"/>
-      <c r="Y30" s="18" t="s">
+      <c r="Y30" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="Z30" s="18"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="18"/>
-      <c r="AD30" s="18"/>
-      <c r="AE30" s="18"/>
-      <c r="AF30" s="18"/>
-      <c r="AG30" s="18"/>
-      <c r="AH30" s="18"/>
-      <c r="AI30" s="18"/>
-      <c r="AJ30" s="18"/>
-      <c r="AK30" s="18"/>
-      <c r="AL30" s="18"/>
-      <c r="AM30" s="18"/>
+      <c r="Z30" s="66"/>
+      <c r="AA30" s="66"/>
+      <c r="AB30" s="66"/>
+      <c r="AC30" s="66"/>
+      <c r="AD30" s="66"/>
+      <c r="AE30" s="66"/>
+      <c r="AF30" s="66"/>
+      <c r="AG30" s="66"/>
+      <c r="AH30" s="66"/>
+      <c r="AI30" s="66"/>
+      <c r="AJ30" s="66"/>
+      <c r="AK30" s="66"/>
+      <c r="AL30" s="66"/>
+      <c r="AM30" s="66"/>
       <c r="AN30" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="41" t="s">
+      <c r="A31" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="41"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="45"/>
-      <c r="U31" s="45"/>
-      <c r="V31" s="45"/>
-      <c r="W31" s="45"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="53"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="8"/>
       <c r="Z31" s="8"/>
@@ -2477,31 +2488,31 @@
       <c r="AN31" s="3"/>
     </row>
     <row r="32" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="42" t="s">
+      <c r="A32" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="44"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="45"/>
-      <c r="U32" s="45"/>
-      <c r="V32" s="45"/>
-      <c r="W32" s="45"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
+      <c r="L32" s="62"/>
+      <c r="M32" s="62"/>
+      <c r="N32" s="62"/>
+      <c r="O32" s="62"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="11"/>
       <c r="Z32" s="11"/>
@@ -2521,31 +2532,31 @@
       <c r="AN32" s="3"/>
     </row>
     <row r="33" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="41"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="41"/>
-      <c r="O33" s="41"/>
-      <c r="P33" s="44"/>
-      <c r="Q33" s="44"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="45"/>
-      <c r="U33" s="45"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="45"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="11"/>
       <c r="Z33" s="11"/>
@@ -2565,31 +2576,31 @@
       <c r="AN33" s="3"/>
     </row>
     <row r="34" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="44"/>
-      <c r="Q34" s="44"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="45"/>
-      <c r="U34" s="45"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="45"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="11"/>
       <c r="Z34" s="11"/>
@@ -2609,85 +2620,85 @@
       <c r="AN34" s="3"/>
     </row>
     <row r="35" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="43" t="s">
+      <c r="A35" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="43"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="45">
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="63"/>
+      <c r="P35" s="14">
         <f>SUM(P25:Q34)/10</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="45"/>
-      <c r="R35" s="45">
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14">
         <f>SUM(R25:S34)/10</f>
         <v>0</v>
       </c>
-      <c r="S35" s="45"/>
-      <c r="T35" s="45">
+      <c r="S35" s="14"/>
+      <c r="T35" s="14">
         <f>SUM(T25:U34)/10</f>
         <v>0</v>
       </c>
-      <c r="U35" s="45"/>
-      <c r="V35" s="45">
+      <c r="U35" s="14"/>
+      <c r="V35" s="14">
         <f>SUM(V25:W34)/10</f>
         <v>0</v>
       </c>
-      <c r="W35" s="45"/>
+      <c r="W35" s="14"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="11"/>
       <c r="Z35" s="11"/>
       <c r="AA35" s="11"/>
       <c r="AB35" s="11"/>
       <c r="AC35" s="11"/>
-      <c r="AD35" s="69"/>
-      <c r="AE35" s="69"/>
-      <c r="AF35" s="69"/>
-      <c r="AG35" s="69"/>
-      <c r="AH35" s="69"/>
-      <c r="AI35" s="69"/>
-      <c r="AJ35" s="69"/>
-      <c r="AK35" s="69"/>
-      <c r="AL35" s="69"/>
-      <c r="AM35" s="69"/>
-      <c r="AN35" s="69"/>
+      <c r="AD35" s="16"/>
+      <c r="AE35" s="16"/>
+      <c r="AF35" s="16"/>
+      <c r="AG35" s="16"/>
+      <c r="AH35" s="16"/>
+      <c r="AI35" s="16"/>
+      <c r="AJ35" s="16"/>
+      <c r="AK35" s="16"/>
+      <c r="AL35" s="16"/>
+      <c r="AM35" s="16"/>
+      <c r="AN35" s="16"/>
     </row>
     <row r="36" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="40"/>
-      <c r="B36" s="40"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="51"/>
-      <c r="Q36" s="51"/>
-      <c r="R36" s="51"/>
-      <c r="S36" s="51"/>
-      <c r="T36" s="51"/>
-      <c r="U36" s="51"/>
-      <c r="V36" s="51"/>
-      <c r="W36" s="51"/>
+      <c r="A36" s="61"/>
+      <c r="B36" s="61"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="61"/>
+      <c r="N36" s="61"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="49"/>
+      <c r="Q36" s="49"/>
+      <c r="R36" s="49"/>
+      <c r="S36" s="49"/>
+      <c r="T36" s="49"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="49"/>
+      <c r="W36" s="49"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="11"/>
       <c r="Z36" s="11"/>
@@ -2709,29 +2720,29 @@
       <c r="AN36" s="12"/>
     </row>
     <row r="37" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="40"/>
-      <c r="B37" s="40"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
-      <c r="N37" s="40"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="51"/>
-      <c r="Q37" s="51"/>
-      <c r="R37" s="51"/>
-      <c r="S37" s="51"/>
-      <c r="T37" s="51"/>
-      <c r="U37" s="51"/>
-      <c r="V37" s="51"/>
-      <c r="W37" s="51"/>
+      <c r="A37" s="61"/>
+      <c r="B37" s="61"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="61"/>
+      <c r="N37" s="61"/>
+      <c r="O37" s="61"/>
+      <c r="P37" s="49"/>
+      <c r="Q37" s="49"/>
+      <c r="R37" s="49"/>
+      <c r="S37" s="49"/>
+      <c r="T37" s="49"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="49"/>
+      <c r="W37" s="49"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="11"/>
       <c r="Z37" s="11"/>
@@ -2740,72 +2751,72 @@
       <c r="AC37" s="11"/>
       <c r="AE37" s="2"/>
       <c r="AF37" s="2"/>
-      <c r="AG37" s="60" t="s">
+      <c r="AG37" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="AH37" s="60"/>
-      <c r="AI37" s="60"/>
-      <c r="AJ37" s="60"/>
-      <c r="AK37" s="60"/>
-      <c r="AL37" s="60"/>
+      <c r="AH37" s="33"/>
+      <c r="AI37" s="33"/>
+      <c r="AJ37" s="33"/>
+      <c r="AK37" s="33"/>
+      <c r="AL37" s="33"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
     </row>
     <row r="38" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="47" t="s">
+      <c r="A38" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="13" t="s">
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13" t="s">
+      <c r="H38" s="17"/>
+      <c r="I38" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13" t="s">
+      <c r="J38" s="17"/>
+      <c r="K38" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13" t="s">
+      <c r="L38" s="17"/>
+      <c r="M38" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13" t="s">
+      <c r="N38" s="17"/>
+      <c r="O38" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="P38" s="13"/>
-      <c r="Q38" s="13" t="s">
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="R38" s="13"/>
-      <c r="S38" s="13" t="s">
+      <c r="R38" s="17"/>
+      <c r="S38" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="T38" s="13"/>
-      <c r="U38" s="13" t="s">
+      <c r="T38" s="17"/>
+      <c r="U38" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="V38" s="13"/>
-      <c r="W38" s="13" t="s">
+      <c r="V38" s="17"/>
+      <c r="W38" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="X38" s="13"/>
-      <c r="Y38" s="13" t="s">
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="Z38" s="13"/>
-      <c r="AA38" s="13" t="s">
+      <c r="Z38" s="17"/>
+      <c r="AA38" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="AB38" s="13"/>
-      <c r="AC38" s="47"/>
-      <c r="AD38" s="47"/>
+      <c r="AB38" s="17"/>
+      <c r="AC38" s="15"/>
+      <c r="AD38" s="15"/>
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
       <c r="AI38" s="3"/>
@@ -2816,61 +2827,61 @@
       <c r="AN38" s="3"/>
     </row>
     <row r="39" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="66" t="s">
+      <c r="A39" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="66"/>
-      <c r="C39" s="66"/>
-      <c r="D39" s="66"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="44">
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="19">
         <v>18</v>
       </c>
-      <c r="H39" s="44"/>
-      <c r="I39" s="44">
+      <c r="H39" s="19"/>
+      <c r="I39" s="19">
         <v>23</v>
       </c>
-      <c r="J39" s="44"/>
-      <c r="K39" s="44">
+      <c r="J39" s="19"/>
+      <c r="K39" s="19">
         <v>22</v>
       </c>
-      <c r="L39" s="44"/>
-      <c r="M39" s="44">
+      <c r="L39" s="19"/>
+      <c r="M39" s="19">
         <v>19</v>
       </c>
-      <c r="N39" s="44"/>
-      <c r="O39" s="44">
+      <c r="N39" s="19"/>
+      <c r="O39" s="19">
         <v>16</v>
       </c>
-      <c r="P39" s="44"/>
-      <c r="Q39" s="44">
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19">
         <v>22</v>
       </c>
-      <c r="R39" s="44"/>
-      <c r="S39" s="44">
+      <c r="R39" s="19"/>
+      <c r="S39" s="19">
         <v>22</v>
       </c>
-      <c r="T39" s="44"/>
-      <c r="U39" s="44">
+      <c r="T39" s="19"/>
+      <c r="U39" s="19">
         <v>20</v>
       </c>
-      <c r="V39" s="44"/>
-      <c r="W39" s="44">
+      <c r="V39" s="19"/>
+      <c r="W39" s="19">
         <v>22</v>
       </c>
-      <c r="X39" s="44"/>
-      <c r="Y39" s="44">
+      <c r="X39" s="19"/>
+      <c r="Y39" s="19">
         <v>16</v>
       </c>
-      <c r="Z39" s="72"/>
-      <c r="AA39" s="45">
+      <c r="Z39" s="21"/>
+      <c r="AA39" s="14">
         <f>SUM(G39:Z39)</f>
         <v>200</v>
       </c>
-      <c r="AB39" s="45"/>
-      <c r="AC39" s="14"/>
-      <c r="AD39" s="14"/>
+      <c r="AB39" s="14"/>
+      <c r="AC39" s="54"/>
+      <c r="AD39" s="54"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
@@ -2881,78 +2892,78 @@
       <c r="AN39" s="3"/>
     </row>
     <row r="40" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="44"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="67"/>
-      <c r="M40" s="44"/>
-      <c r="N40" s="44"/>
-      <c r="O40" s="44"/>
-      <c r="P40" s="44"/>
-      <c r="Q40" s="71"/>
-      <c r="R40" s="71"/>
-      <c r="S40" s="44"/>
-      <c r="T40" s="44"/>
-      <c r="U40" s="44"/>
-      <c r="V40" s="44"/>
-      <c r="W40" s="71"/>
-      <c r="X40" s="71"/>
-      <c r="Y40" s="67"/>
-      <c r="Z40" s="73"/>
-      <c r="AA40" s="70">
-        <f t="shared" ref="AA40:AA41" si="5">SUM(G40:Z40)</f>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="22"/>
+      <c r="Z40" s="23"/>
+      <c r="AA40" s="18">
+        <f>SUM(G40:Z40)</f>
         <v>0</v>
       </c>
-      <c r="AB40" s="70"/>
-      <c r="AC40" s="14"/>
-      <c r="AD40" s="14"/>
+      <c r="AB40" s="18"/>
+      <c r="AC40" s="54"/>
+      <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="44"/>
-      <c r="J41" s="44"/>
-      <c r="K41" s="44"/>
-      <c r="L41" s="44"/>
-      <c r="M41" s="44"/>
-      <c r="N41" s="44"/>
-      <c r="O41" s="44"/>
-      <c r="P41" s="44"/>
-      <c r="Q41" s="44"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="44"/>
-      <c r="T41" s="44"/>
-      <c r="U41" s="44"/>
-      <c r="V41" s="44"/>
-      <c r="W41" s="44"/>
-      <c r="X41" s="44"/>
-      <c r="Y41" s="44"/>
-      <c r="Z41" s="72"/>
-      <c r="AA41" s="45">
-        <f t="shared" si="5"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="19"/>
+      <c r="U41" s="19"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="19"/>
+      <c r="X41" s="19"/>
+      <c r="Y41" s="19"/>
+      <c r="Z41" s="21"/>
+      <c r="AA41" s="14">
+        <f t="shared" ref="AA40:AA41" si="5">SUM(G41:Z41)</f>
         <v>0</v>
       </c>
-      <c r="AB41" s="45"/>
-      <c r="AC41" s="14"/>
-      <c r="AD41" s="14"/>
+      <c r="AB41" s="14"/>
+      <c r="AC41" s="54"/>
+      <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
@@ -3021,6 +3032,238 @@
     <row r="82" ht="12.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="256">
+    <mergeCell ref="Y38:Z38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="AC41:AD41"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:N2"/>
+    <mergeCell ref="Y24:AJ24"/>
+    <mergeCell ref="Y25:AM25"/>
+    <mergeCell ref="Y26:AM26"/>
+    <mergeCell ref="Y27:AM27"/>
+    <mergeCell ref="Y28:AM28"/>
+    <mergeCell ref="Y29:AM29"/>
+    <mergeCell ref="Y30:AM30"/>
+    <mergeCell ref="AD5:AI6"/>
+    <mergeCell ref="AJ5:AN6"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="N10:Q10"/>
+    <mergeCell ref="R10:U10"/>
+    <mergeCell ref="V10:Y10"/>
+    <mergeCell ref="Z10:AC10"/>
+    <mergeCell ref="AJ10:AN10"/>
+    <mergeCell ref="AJ12:AN12"/>
+    <mergeCell ref="AJ11:AN11"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="R17:U17"/>
+    <mergeCell ref="R18:U18"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="C20:M20"/>
+    <mergeCell ref="N21:AC21"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A32:O32"/>
+    <mergeCell ref="A33:O33"/>
+    <mergeCell ref="A34:O34"/>
+    <mergeCell ref="A35:O35"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="Z20:AC20"/>
+    <mergeCell ref="R20:U20"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="AC38:AD38"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="V35:W35"/>
+    <mergeCell ref="V36:W36"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N15:Q15"/>
+    <mergeCell ref="N16:Q16"/>
+    <mergeCell ref="N17:Q17"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="N12:Q12"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="E3:U3"/>
+    <mergeCell ref="Z3:AN3"/>
+    <mergeCell ref="U4:AG4"/>
+    <mergeCell ref="G4:P4"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="N5:AC5"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="V6:Y6"/>
+    <mergeCell ref="Z6:AC6"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="B16:M16"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="B15:M15"/>
+    <mergeCell ref="R15:U15"/>
+    <mergeCell ref="R16:U16"/>
+    <mergeCell ref="R12:U12"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="N8:Q8"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="N13:Q13"/>
+    <mergeCell ref="N14:Q14"/>
+    <mergeCell ref="V8:Y8"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="V11:Y11"/>
+    <mergeCell ref="V13:Y13"/>
+    <mergeCell ref="V14:Y14"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="R7:U7"/>
+    <mergeCell ref="R8:U8"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="R11:U11"/>
+    <mergeCell ref="R13:U13"/>
+    <mergeCell ref="R14:U14"/>
+    <mergeCell ref="Z13:AC13"/>
+    <mergeCell ref="Z14:AC14"/>
+    <mergeCell ref="Z15:AC15"/>
+    <mergeCell ref="Z16:AC16"/>
+    <mergeCell ref="Z17:AC17"/>
+    <mergeCell ref="V16:Y16"/>
+    <mergeCell ref="V17:Y17"/>
+    <mergeCell ref="V18:Y18"/>
+    <mergeCell ref="V19:Y19"/>
+    <mergeCell ref="AG37:AL37"/>
+    <mergeCell ref="V15:Y15"/>
+    <mergeCell ref="Z18:AC18"/>
+    <mergeCell ref="Z19:AC19"/>
+    <mergeCell ref="O1:AA1"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="AH4:AN4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="AJ7:AN7"/>
+    <mergeCell ref="AJ8:AN8"/>
+    <mergeCell ref="AJ9:AN9"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="R19:U19"/>
+    <mergeCell ref="Z12:AC12"/>
+    <mergeCell ref="V12:Y12"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="V20:Y20"/>
+    <mergeCell ref="Z7:AC7"/>
+    <mergeCell ref="Z8:AC8"/>
+    <mergeCell ref="Z9:AC9"/>
+    <mergeCell ref="Z11:AC11"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="AJ19:AN19"/>
+    <mergeCell ref="AJ20:AN20"/>
+    <mergeCell ref="AJ18:AN18"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AJ13:AN13"/>
+    <mergeCell ref="AJ14:AN14"/>
+    <mergeCell ref="AJ15:AN15"/>
+    <mergeCell ref="AJ16:AN16"/>
+    <mergeCell ref="AJ17:AN17"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AJ21:AN21"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="AD22:AI22"/>
     <mergeCell ref="AA41:AB41"/>
     <mergeCell ref="A38:F38"/>
@@ -3045,239 +3288,17 @@
     <mergeCell ref="K39:L39"/>
     <mergeCell ref="M39:N39"/>
     <mergeCell ref="M40:N40"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="AJ19:AN19"/>
-    <mergeCell ref="AJ20:AN20"/>
-    <mergeCell ref="AJ18:AN18"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AJ13:AN13"/>
-    <mergeCell ref="AJ14:AN14"/>
-    <mergeCell ref="AJ15:AN15"/>
-    <mergeCell ref="AJ16:AN16"/>
-    <mergeCell ref="AJ17:AN17"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AJ21:AN21"/>
-    <mergeCell ref="AG37:AL37"/>
-    <mergeCell ref="V15:Y15"/>
-    <mergeCell ref="Z18:AC18"/>
-    <mergeCell ref="Z19:AC19"/>
-    <mergeCell ref="O1:AA1"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="AH4:AN4"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="AJ7:AN7"/>
-    <mergeCell ref="AJ8:AN8"/>
-    <mergeCell ref="AJ9:AN9"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="R19:U19"/>
-    <mergeCell ref="Z12:AC12"/>
-    <mergeCell ref="V12:Y12"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="V20:Y20"/>
-    <mergeCell ref="Z7:AC7"/>
-    <mergeCell ref="Z8:AC8"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="Z11:AC11"/>
-    <mergeCell ref="Z13:AC13"/>
-    <mergeCell ref="Z14:AC14"/>
-    <mergeCell ref="Z15:AC15"/>
-    <mergeCell ref="Z16:AC16"/>
-    <mergeCell ref="Z17:AC17"/>
-    <mergeCell ref="V16:Y16"/>
-    <mergeCell ref="V17:Y17"/>
-    <mergeCell ref="V18:Y18"/>
-    <mergeCell ref="V19:Y19"/>
-    <mergeCell ref="V8:Y8"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="V11:Y11"/>
-    <mergeCell ref="V13:Y13"/>
-    <mergeCell ref="V14:Y14"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="R7:U7"/>
-    <mergeCell ref="R8:U8"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="R11:U11"/>
-    <mergeCell ref="R13:U13"/>
-    <mergeCell ref="R14:U14"/>
-    <mergeCell ref="R15:U15"/>
-    <mergeCell ref="R16:U16"/>
-    <mergeCell ref="R12:U12"/>
-    <mergeCell ref="N7:Q7"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="N13:Q13"/>
-    <mergeCell ref="N14:Q14"/>
-    <mergeCell ref="B16:M16"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="B15:M15"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N15:Q15"/>
-    <mergeCell ref="N16:Q16"/>
-    <mergeCell ref="N17:Q17"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="E3:U3"/>
-    <mergeCell ref="Z3:AN3"/>
-    <mergeCell ref="U4:AG4"/>
-    <mergeCell ref="G4:P4"/>
-    <mergeCell ref="A5:M6"/>
-    <mergeCell ref="N5:AC5"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="R6:U6"/>
-    <mergeCell ref="V6:Y6"/>
-    <mergeCell ref="Z6:AC6"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="V35:W35"/>
-    <mergeCell ref="V36:W36"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="N19:Q19"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="Z20:AC20"/>
-    <mergeCell ref="R20:U20"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="AC38:AD38"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A26:O26"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="C20:M20"/>
-    <mergeCell ref="N21:AC21"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="A33:O33"/>
-    <mergeCell ref="A34:O34"/>
-    <mergeCell ref="A35:O35"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="AC41:AD41"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:N2"/>
-    <mergeCell ref="Y24:AJ24"/>
-    <mergeCell ref="Y25:AM25"/>
-    <mergeCell ref="Y26:AM26"/>
-    <mergeCell ref="Y27:AM27"/>
-    <mergeCell ref="Y28:AM28"/>
-    <mergeCell ref="Y29:AM29"/>
-    <mergeCell ref="Y30:AM30"/>
-    <mergeCell ref="AD5:AI6"/>
-    <mergeCell ref="AJ5:AN6"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="N10:Q10"/>
-    <mergeCell ref="R10:U10"/>
-    <mergeCell ref="V10:Y10"/>
-    <mergeCell ref="Z10:AC10"/>
-    <mergeCell ref="AJ10:AN10"/>
-    <mergeCell ref="AJ12:AN12"/>
-    <mergeCell ref="AJ11:AN11"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="R17:U17"/>
-    <mergeCell ref="R18:U18"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="Y38:Z38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S38:T38"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="W38:X38"/>
   </mergeCells>
+  <conditionalFormatting sqref="AD7:AI19">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ7:AN19">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.9" bottom="0.25" header="0" footer="0"/>
   <pageSetup paperSize="10000" orientation="portrait" r:id="rId1"/>

--- a/public/files/report_card_templates/JHS.xlsx
+++ b/public/files/report_card_templates/JHS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\schoolsys\public\files\report_card_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEF45E4-AC18-4BBD-9571-311C703ECD04}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98734B0-E9E8-4866-B299-A6628249FA36}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -504,194 +504,204 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFC00000"/>
@@ -1043,260 +1053,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O1" s="34" t="s">
+      <c r="O1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="61"/>
+      <c r="Z1" s="61"/>
+      <c r="AA1" s="61"/>
     </row>
     <row r="2" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
-      <c r="Q2" s="35" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="Q2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="37" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="55"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="55"/>
+      <c r="V3" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="45"/>
-      <c r="AI3" s="45"/>
-      <c r="AJ3" s="45"/>
-      <c r="AK3" s="45"/>
-      <c r="AL3" s="45"/>
-      <c r="AM3" s="45"/>
-      <c r="AN3" s="45"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="55"/>
+      <c r="AC3" s="55"/>
+      <c r="AD3" s="55"/>
+      <c r="AE3" s="55"/>
+      <c r="AF3" s="55"/>
+      <c r="AG3" s="55"/>
+      <c r="AH3" s="55"/>
+      <c r="AI3" s="55"/>
+      <c r="AJ3" s="55"/>
+      <c r="AK3" s="55"/>
+      <c r="AL3" s="55"/>
+      <c r="AM3" s="55"/>
+      <c r="AN3" s="55"/>
     </row>
     <row r="4" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="36" t="s">
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="46"/>
-      <c r="Y4" s="46"/>
-      <c r="Z4" s="46"/>
-      <c r="AA4" s="46"/>
-      <c r="AB4" s="46"/>
-      <c r="AC4" s="46"/>
-      <c r="AD4" s="46"/>
-      <c r="AE4" s="46"/>
-      <c r="AF4" s="46"/>
-      <c r="AG4" s="46"/>
-      <c r="AH4" s="36"/>
-      <c r="AI4" s="36"/>
-      <c r="AJ4" s="36"/>
-      <c r="AK4" s="36"/>
-      <c r="AL4" s="36"/>
-      <c r="AM4" s="36"/>
-      <c r="AN4" s="36"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="59"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="56"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="56"/>
+      <c r="Y4" s="56"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="56"/>
+      <c r="AB4" s="56"/>
+      <c r="AC4" s="56"/>
+      <c r="AD4" s="56"/>
+      <c r="AE4" s="56"/>
+      <c r="AF4" s="56"/>
+      <c r="AG4" s="56"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
     </row>
     <row r="5" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="47"/>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="47"/>
-      <c r="AD5" s="67" t="s">
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="33"/>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="33"/>
+      <c r="AA5" s="33"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="33"/>
+      <c r="AD5" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="AE5" s="68"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="69"/>
-      <c r="AJ5" s="67" t="s">
+      <c r="AE5" s="20"/>
+      <c r="AF5" s="20"/>
+      <c r="AG5" s="20"/>
+      <c r="AH5" s="20"/>
+      <c r="AI5" s="21"/>
+      <c r="AJ5" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
-      <c r="AM5" s="68"/>
-      <c r="AN5" s="69"/>
+      <c r="AK5" s="20"/>
+      <c r="AL5" s="20"/>
+      <c r="AM5" s="20"/>
+      <c r="AN5" s="21"/>
     </row>
     <row r="6" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="32" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="32" t="s">
+      <c r="O6" s="57"/>
+      <c r="P6" s="57"/>
+      <c r="Q6" s="57"/>
+      <c r="R6" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="S6" s="32"/>
-      <c r="T6" s="32"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="32" t="s">
+      <c r="S6" s="57"/>
+      <c r="T6" s="57"/>
+      <c r="U6" s="57"/>
+      <c r="V6" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="W6" s="32"/>
-      <c r="X6" s="32"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32" t="s">
+      <c r="W6" s="57"/>
+      <c r="X6" s="57"/>
+      <c r="Y6" s="57"/>
+      <c r="Z6" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="70"/>
-      <c r="AE6" s="71"/>
-      <c r="AF6" s="71"/>
-      <c r="AG6" s="71"/>
-      <c r="AH6" s="71"/>
-      <c r="AI6" s="72"/>
-      <c r="AJ6" s="70"/>
-      <c r="AK6" s="71"/>
-      <c r="AL6" s="71"/>
-      <c r="AM6" s="71"/>
-      <c r="AN6" s="72"/>
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="57"/>
+      <c r="AC6" s="57"/>
+      <c r="AD6" s="22"/>
+      <c r="AE6" s="23"/>
+      <c r="AF6" s="23"/>
+      <c r="AG6" s="23"/>
+      <c r="AH6" s="23"/>
+      <c r="AI6" s="24"/>
+      <c r="AJ6" s="22"/>
+      <c r="AK6" s="23"/>
+      <c r="AL6" s="23"/>
+      <c r="AM6" s="23"/>
+      <c r="AN6" s="24"/>
     </row>
     <row r="7" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
       <c r="N7" s="28"/>
       <c r="O7" s="28"/>
       <c r="P7" s="28"/>
@@ -1313,15 +1323,15 @@
       <c r="AA7" s="28"/>
       <c r="AB7" s="28"/>
       <c r="AC7" s="28"/>
-      <c r="AD7" s="25" t="str">
+      <c r="AD7" s="29" t="str">
         <f>IF(COUNT(N7:AC7)=4,SUM(N7:AC7)/4,"")</f>
         <v/>
       </c>
-      <c r="AE7" s="26"/>
-      <c r="AF7" s="26"/>
-      <c r="AG7" s="26"/>
-      <c r="AH7" s="26"/>
-      <c r="AI7" s="27"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="31"/>
       <c r="AJ7" s="28" t="str">
         <f>IF(AD7&lt;&gt;"",IF(AD7&gt;=75,"Passed","Failed"),"")</f>
         <v/>
@@ -1332,21 +1342,21 @@
       <c r="AN7" s="28"/>
     </row>
     <row r="8" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
       <c r="N8" s="28"/>
       <c r="O8" s="28"/>
       <c r="P8" s="28"/>
@@ -1363,15 +1373,15 @@
       <c r="AA8" s="28"/>
       <c r="AB8" s="28"/>
       <c r="AC8" s="28"/>
-      <c r="AD8" s="25" t="str">
+      <c r="AD8" s="29" t="str">
         <f t="shared" ref="AD8:AD19" si="0">IF(COUNT(N8:AC8)=4,SUM(N8:AC8)/4,"")</f>
         <v/>
       </c>
-      <c r="AE8" s="26"/>
-      <c r="AF8" s="26"/>
-      <c r="AG8" s="26"/>
-      <c r="AH8" s="26"/>
-      <c r="AI8" s="27"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="30"/>
+      <c r="AH8" s="30"/>
+      <c r="AI8" s="31"/>
       <c r="AJ8" s="28" t="str">
         <f t="shared" ref="AJ8:AJ19" si="1">IF(AD8&lt;&gt;"",IF(AD8&gt;=75,"Passed","Failed"),"")</f>
         <v/>
@@ -1382,21 +1392,21 @@
       <c r="AN8" s="28"/>
     </row>
     <row r="9" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
       <c r="N9" s="28"/>
       <c r="O9" s="28"/>
       <c r="P9" s="28"/>
@@ -1413,15 +1423,15 @@
       <c r="AA9" s="28"/>
       <c r="AB9" s="28"/>
       <c r="AC9" s="28"/>
-      <c r="AD9" s="25" t="str">
+      <c r="AD9" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE9" s="26"/>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="26"/>
-      <c r="AH9" s="26"/>
-      <c r="AI9" s="27"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="31"/>
       <c r="AJ9" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1432,21 +1442,21 @@
       <c r="AN9" s="28"/>
     </row>
     <row r="10" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="40"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="27"/>
       <c r="N10" s="28"/>
       <c r="O10" s="28"/>
       <c r="P10" s="28"/>
@@ -1463,15 +1473,15 @@
       <c r="AA10" s="28"/>
       <c r="AB10" s="28"/>
       <c r="AC10" s="28"/>
-      <c r="AD10" s="25" t="str">
+      <c r="AD10" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE10" s="26"/>
-      <c r="AF10" s="26"/>
-      <c r="AG10" s="26"/>
-      <c r="AH10" s="26"/>
-      <c r="AI10" s="27"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="30"/>
+      <c r="AG10" s="30"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="31"/>
       <c r="AJ10" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1482,21 +1492,21 @@
       <c r="AN10" s="28"/>
     </row>
     <row r="11" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="49"/>
       <c r="N11" s="28"/>
       <c r="O11" s="28"/>
       <c r="P11" s="28"/>
@@ -1513,15 +1523,15 @@
       <c r="AA11" s="28"/>
       <c r="AB11" s="28"/>
       <c r="AC11" s="28"/>
-      <c r="AD11" s="25" t="str">
+      <c r="AD11" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE11" s="26"/>
-      <c r="AF11" s="26"/>
-      <c r="AG11" s="26"/>
-      <c r="AH11" s="26"/>
-      <c r="AI11" s="27"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="30"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="31"/>
       <c r="AJ11" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1532,21 +1542,21 @@
       <c r="AN11" s="28"/>
     </row>
     <row r="12" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="44"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="54"/>
       <c r="N12" s="28"/>
       <c r="O12" s="28"/>
       <c r="P12" s="28"/>
@@ -1563,15 +1573,15 @@
       <c r="AA12" s="28"/>
       <c r="AB12" s="28"/>
       <c r="AC12" s="28"/>
-      <c r="AD12" s="25" t="str">
+      <c r="AD12" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE12" s="26"/>
-      <c r="AF12" s="26"/>
-      <c r="AG12" s="26"/>
-      <c r="AH12" s="26"/>
-      <c r="AI12" s="27"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="30"/>
+      <c r="AG12" s="30"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="31"/>
       <c r="AJ12" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1582,21 +1592,21 @@
       <c r="AN12" s="28"/>
     </row>
     <row r="13" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
       <c r="N13" s="28"/>
       <c r="O13" s="28"/>
       <c r="P13" s="28"/>
@@ -1613,15 +1623,15 @@
       <c r="AA13" s="28"/>
       <c r="AB13" s="28"/>
       <c r="AC13" s="28"/>
-      <c r="AD13" s="25" t="str">
+      <c r="AD13" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE13" s="26"/>
-      <c r="AF13" s="26"/>
-      <c r="AG13" s="26"/>
-      <c r="AH13" s="26"/>
-      <c r="AI13" s="27"/>
+      <c r="AE13" s="30"/>
+      <c r="AF13" s="30"/>
+      <c r="AG13" s="30"/>
+      <c r="AH13" s="30"/>
+      <c r="AI13" s="31"/>
       <c r="AJ13" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1633,20 +1643,20 @@
     </row>
     <row r="14" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="40"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="27"/>
       <c r="N14" s="28"/>
       <c r="O14" s="28"/>
       <c r="P14" s="28"/>
@@ -1663,15 +1673,15 @@
       <c r="AA14" s="28"/>
       <c r="AB14" s="28"/>
       <c r="AC14" s="28"/>
-      <c r="AD14" s="25" t="str">
+      <c r="AD14" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE14" s="26"/>
-      <c r="AF14" s="26"/>
-      <c r="AG14" s="26"/>
-      <c r="AH14" s="26"/>
-      <c r="AI14" s="27"/>
+      <c r="AE14" s="30"/>
+      <c r="AF14" s="30"/>
+      <c r="AG14" s="30"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="31"/>
       <c r="AJ14" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1683,20 +1693,20 @@
     </row>
     <row r="15" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="40"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="27"/>
       <c r="N15" s="28"/>
       <c r="O15" s="28"/>
       <c r="P15" s="28"/>
@@ -1713,15 +1723,15 @@
       <c r="AA15" s="28"/>
       <c r="AB15" s="28"/>
       <c r="AC15" s="28"/>
-      <c r="AD15" s="25" t="str">
+      <c r="AD15" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE15" s="26"/>
-      <c r="AF15" s="26"/>
-      <c r="AG15" s="26"/>
-      <c r="AH15" s="26"/>
-      <c r="AI15" s="27"/>
+      <c r="AE15" s="30"/>
+      <c r="AF15" s="30"/>
+      <c r="AG15" s="30"/>
+      <c r="AH15" s="30"/>
+      <c r="AI15" s="31"/>
       <c r="AJ15" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1733,20 +1743,20 @@
     </row>
     <row r="16" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="40"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="27"/>
       <c r="N16" s="28"/>
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
@@ -1763,15 +1773,15 @@
       <c r="AA16" s="28"/>
       <c r="AB16" s="28"/>
       <c r="AC16" s="28"/>
-      <c r="AD16" s="25" t="str">
+      <c r="AD16" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE16" s="26"/>
-      <c r="AF16" s="26"/>
-      <c r="AG16" s="26"/>
-      <c r="AH16" s="26"/>
-      <c r="AI16" s="27"/>
+      <c r="AE16" s="30"/>
+      <c r="AF16" s="30"/>
+      <c r="AG16" s="30"/>
+      <c r="AH16" s="30"/>
+      <c r="AI16" s="31"/>
       <c r="AJ16" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1783,20 +1793,20 @@
     </row>
     <row r="17" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="40"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="27"/>
       <c r="N17" s="28"/>
       <c r="O17" s="28"/>
       <c r="P17" s="28"/>
@@ -1813,15 +1823,15 @@
       <c r="AA17" s="28"/>
       <c r="AB17" s="28"/>
       <c r="AC17" s="28"/>
-      <c r="AD17" s="25" t="str">
+      <c r="AD17" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE17" s="26"/>
-      <c r="AF17" s="26"/>
-      <c r="AG17" s="26"/>
-      <c r="AH17" s="26"/>
-      <c r="AI17" s="27"/>
+      <c r="AE17" s="30"/>
+      <c r="AF17" s="30"/>
+      <c r="AG17" s="30"/>
+      <c r="AH17" s="30"/>
+      <c r="AI17" s="31"/>
       <c r="AJ17" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1832,21 +1842,21 @@
       <c r="AN17" s="28"/>
     </row>
     <row r="18" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="49"/>
       <c r="N18" s="28"/>
       <c r="O18" s="28"/>
       <c r="P18" s="28"/>
@@ -1863,15 +1873,15 @@
       <c r="AA18" s="28"/>
       <c r="AB18" s="28"/>
       <c r="AC18" s="28"/>
-      <c r="AD18" s="25" t="str">
+      <c r="AD18" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE18" s="26"/>
-      <c r="AF18" s="26"/>
-      <c r="AG18" s="26"/>
-      <c r="AH18" s="26"/>
-      <c r="AI18" s="27"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="30"/>
+      <c r="AH18" s="30"/>
+      <c r="AI18" s="31"/>
       <c r="AJ18" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1882,21 +1892,21 @@
       <c r="AN18" s="28"/>
     </row>
     <row r="19" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
       <c r="N19" s="28"/>
       <c r="O19" s="28"/>
       <c r="P19" s="28"/>
@@ -1913,15 +1923,15 @@
       <c r="AA19" s="28"/>
       <c r="AB19" s="28"/>
       <c r="AC19" s="28"/>
-      <c r="AD19" s="25" t="str">
+      <c r="AD19" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE19" s="26"/>
-      <c r="AF19" s="26"/>
-      <c r="AG19" s="26"/>
-      <c r="AH19" s="26"/>
-      <c r="AI19" s="27"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="30"/>
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="31"/>
       <c r="AJ19" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1934,53 +1944,53 @@
     <row r="20" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="38" t="str">
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="46" t="str">
         <f>IF(SUM(N7:Q13,N18)/8 &gt; 0, SUM(N7:Q13,N18)/8, "")</f>
         <v/>
       </c>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-      <c r="R20" s="38" t="str">
+      <c r="O20" s="46"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="46" t="str">
         <f t="shared" ref="R20" si="2">IF(SUM(R7:U13,R18)/8 &gt; 0, SUM(R7:U13,R18)/8, "")</f>
         <v/>
       </c>
-      <c r="S20" s="38"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="38"/>
-      <c r="V20" s="38" t="str">
+      <c r="S20" s="46"/>
+      <c r="T20" s="46"/>
+      <c r="U20" s="46"/>
+      <c r="V20" s="46" t="str">
         <f t="shared" ref="V20" si="3">IF(SUM(V7:Y13,V18)/8 &gt; 0, SUM(V7:Y13,V18)/8, "")</f>
         <v/>
       </c>
-      <c r="W20" s="38"/>
-      <c r="X20" s="38"/>
-      <c r="Y20" s="38"/>
-      <c r="Z20" s="38" t="str">
+      <c r="W20" s="46"/>
+      <c r="X20" s="46"/>
+      <c r="Y20" s="46"/>
+      <c r="Z20" s="46" t="str">
         <f t="shared" ref="Z20" si="4">IF(SUM(Z7:AC13,Z18)/8 &gt; 0, SUM(Z7:AC13,Z18)/8, "")</f>
         <v/>
       </c>
-      <c r="AA20" s="38"/>
-      <c r="AB20" s="38"/>
-      <c r="AC20" s="38"/>
-      <c r="AD20" s="25"/>
-      <c r="AE20" s="26"/>
-      <c r="AF20" s="26"/>
-      <c r="AG20" s="26"/>
-      <c r="AH20" s="26"/>
-      <c r="AI20" s="27"/>
+      <c r="AA20" s="46"/>
+      <c r="AB20" s="46"/>
+      <c r="AC20" s="46"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
+      <c r="AG20" s="30"/>
+      <c r="AH20" s="30"/>
+      <c r="AI20" s="31"/>
       <c r="AJ20" s="28"/>
       <c r="AK20" s="28"/>
       <c r="AL20" s="28"/>
@@ -1990,51 +2000,51 @@
     <row r="21" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="51" t="s">
+      <c r="C21" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="58" t="s">
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="O21" s="59"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="59"/>
-      <c r="R21" s="59"/>
-      <c r="S21" s="59"/>
-      <c r="T21" s="59"/>
-      <c r="U21" s="59"/>
-      <c r="V21" s="59"/>
-      <c r="W21" s="59"/>
-      <c r="X21" s="59"/>
-      <c r="Y21" s="59"/>
-      <c r="Z21" s="59"/>
-      <c r="AA21" s="59"/>
-      <c r="AB21" s="59"/>
-      <c r="AC21" s="60"/>
-      <c r="AD21" s="29" t="str">
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="38"/>
+      <c r="V21" s="38"/>
+      <c r="W21" s="38"/>
+      <c r="X21" s="38"/>
+      <c r="Y21" s="38"/>
+      <c r="Z21" s="38"/>
+      <c r="AA21" s="38"/>
+      <c r="AB21" s="38"/>
+      <c r="AC21" s="39"/>
+      <c r="AD21" s="63" t="str">
         <f>IF(COUNT(AD7:AI13,AD18)=8,SUM(AD7:AI13,AD18)/8,"")</f>
         <v/>
       </c>
-      <c r="AE21" s="30"/>
-      <c r="AF21" s="30"/>
-      <c r="AG21" s="30"/>
-      <c r="AH21" s="30"/>
-      <c r="AI21" s="31"/>
-      <c r="AJ21" s="32"/>
-      <c r="AK21" s="32"/>
-      <c r="AL21" s="32"/>
-      <c r="AM21" s="32"/>
-      <c r="AN21" s="32"/>
+      <c r="AE21" s="64"/>
+      <c r="AF21" s="64"/>
+      <c r="AG21" s="64"/>
+      <c r="AH21" s="64"/>
+      <c r="AI21" s="65"/>
+      <c r="AJ21" s="57"/>
+      <c r="AK21" s="57"/>
+      <c r="AL21" s="57"/>
+      <c r="AM21" s="57"/>
+      <c r="AN21" s="57"/>
     </row>
     <row r="22" spans="1:40" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
@@ -2066,12 +2076,12 @@
       <c r="AA22" s="10"/>
       <c r="AB22" s="10"/>
       <c r="AC22" s="10"/>
-      <c r="AD22" s="13"/>
-      <c r="AE22" s="13"/>
-      <c r="AF22" s="13"/>
-      <c r="AG22" s="13"/>
-      <c r="AH22" s="13"/>
-      <c r="AI22" s="13"/>
+      <c r="AD22" s="68"/>
+      <c r="AE22" s="68"/>
+      <c r="AF22" s="68"/>
+      <c r="AG22" s="68"/>
+      <c r="AH22" s="68"/>
+      <c r="AI22" s="68"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
@@ -2108,367 +2118,367 @@
       <c r="Y23" s="2"/>
     </row>
     <row r="24" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
+      <c r="A24" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="47"/>
-      <c r="P24" s="55" t="s">
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55" t="s">
+      <c r="Q24" s="34"/>
+      <c r="R24" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="S24" s="55"/>
-      <c r="T24" s="55" t="s">
+      <c r="S24" s="34"/>
+      <c r="T24" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="U24" s="55"/>
-      <c r="V24" s="55" t="s">
+      <c r="U24" s="34"/>
+      <c r="V24" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="W24" s="55"/>
-      <c r="Y24" s="65" t="s">
+      <c r="W24" s="34"/>
+      <c r="Y24" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="Z24" s="65"/>
-      <c r="AA24" s="65"/>
-      <c r="AB24" s="65"/>
-      <c r="AC24" s="65"/>
-      <c r="AD24" s="65"/>
-      <c r="AE24" s="65"/>
-      <c r="AF24" s="65"/>
-      <c r="AG24" s="65"/>
-      <c r="AH24" s="65"/>
-      <c r="AI24" s="65"/>
-      <c r="AJ24" s="65"/>
+      <c r="Z24" s="17"/>
+      <c r="AA24" s="17"/>
+      <c r="AB24" s="17"/>
+      <c r="AC24" s="17"/>
+      <c r="AD24" s="17"/>
+      <c r="AE24" s="17"/>
+      <c r="AF24" s="17"/>
+      <c r="AG24" s="17"/>
+      <c r="AH24" s="17"/>
+      <c r="AI24" s="17"/>
+      <c r="AJ24" s="17"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
       <c r="AN24" s="3"/>
     </row>
     <row r="25" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="53"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="53"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="Y25" s="66" t="s">
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="44"/>
+      <c r="S25" s="44"/>
+      <c r="T25" s="44"/>
+      <c r="U25" s="44"/>
+      <c r="V25" s="45"/>
+      <c r="W25" s="45"/>
+      <c r="Y25" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="Z25" s="66"/>
-      <c r="AA25" s="66"/>
-      <c r="AB25" s="66"/>
-      <c r="AC25" s="66"/>
-      <c r="AD25" s="66"/>
-      <c r="AE25" s="66"/>
-      <c r="AF25" s="66"/>
-      <c r="AG25" s="66"/>
-      <c r="AH25" s="66"/>
-      <c r="AI25" s="66"/>
-      <c r="AJ25" s="66"/>
-      <c r="AK25" s="66"/>
-      <c r="AL25" s="66"/>
-      <c r="AM25" s="66"/>
+      <c r="Z25" s="18"/>
+      <c r="AA25" s="18"/>
+      <c r="AB25" s="18"/>
+      <c r="AC25" s="18"/>
+      <c r="AD25" s="18"/>
+      <c r="AE25" s="18"/>
+      <c r="AF25" s="18"/>
+      <c r="AG25" s="18"/>
+      <c r="AH25" s="18"/>
+      <c r="AI25" s="18"/>
+      <c r="AJ25" s="18"/>
+      <c r="AK25" s="18"/>
+      <c r="AL25" s="18"/>
+      <c r="AM25" s="18"/>
       <c r="AN25" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="Y26" s="66" t="s">
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="45"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="45"/>
+      <c r="U26" s="45"/>
+      <c r="V26" s="45"/>
+      <c r="W26" s="45"/>
+      <c r="Y26" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="Z26" s="66"/>
-      <c r="AA26" s="66"/>
-      <c r="AB26" s="66"/>
-      <c r="AC26" s="66"/>
-      <c r="AD26" s="66"/>
-      <c r="AE26" s="66"/>
-      <c r="AF26" s="66"/>
-      <c r="AG26" s="66"/>
-      <c r="AH26" s="66"/>
-      <c r="AI26" s="66"/>
-      <c r="AJ26" s="66"/>
-      <c r="AK26" s="66"/>
-      <c r="AL26" s="66"/>
-      <c r="AM26" s="66"/>
+      <c r="Z26" s="18"/>
+      <c r="AA26" s="18"/>
+      <c r="AB26" s="18"/>
+      <c r="AC26" s="18"/>
+      <c r="AD26" s="18"/>
+      <c r="AE26" s="18"/>
+      <c r="AF26" s="18"/>
+      <c r="AG26" s="18"/>
+      <c r="AH26" s="18"/>
+      <c r="AI26" s="18"/>
+      <c r="AJ26" s="18"/>
+      <c r="AK26" s="18"/>
+      <c r="AL26" s="18"/>
+      <c r="AM26" s="18"/>
       <c r="AN26" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="53"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="14"/>
-      <c r="Y27" s="66" t="s">
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="45"/>
+      <c r="S27" s="45"/>
+      <c r="T27" s="45"/>
+      <c r="U27" s="45"/>
+      <c r="V27" s="45"/>
+      <c r="W27" s="45"/>
+      <c r="Y27" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="Z27" s="66"/>
-      <c r="AA27" s="66"/>
-      <c r="AB27" s="66"/>
-      <c r="AC27" s="66"/>
-      <c r="AD27" s="66"/>
-      <c r="AE27" s="66"/>
-      <c r="AF27" s="66"/>
-      <c r="AG27" s="66"/>
-      <c r="AH27" s="66"/>
-      <c r="AI27" s="66"/>
-      <c r="AJ27" s="66"/>
-      <c r="AK27" s="66"/>
-      <c r="AL27" s="66"/>
-      <c r="AM27" s="66"/>
+      <c r="Z27" s="18"/>
+      <c r="AA27" s="18"/>
+      <c r="AB27" s="18"/>
+      <c r="AC27" s="18"/>
+      <c r="AD27" s="18"/>
+      <c r="AE27" s="18"/>
+      <c r="AF27" s="18"/>
+      <c r="AG27" s="18"/>
+      <c r="AH27" s="18"/>
+      <c r="AI27" s="18"/>
+      <c r="AJ27" s="18"/>
+      <c r="AK27" s="18"/>
+      <c r="AL27" s="18"/>
+      <c r="AM27" s="18"/>
       <c r="AN27" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="53" t="s">
+      <c r="A28" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="14"/>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
-      <c r="Y28" s="66" t="s">
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="45"/>
+      <c r="U28" s="45"/>
+      <c r="V28" s="45"/>
+      <c r="W28" s="45"/>
+      <c r="Y28" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="Z28" s="66"/>
-      <c r="AA28" s="66"/>
-      <c r="AB28" s="66"/>
-      <c r="AC28" s="66"/>
-      <c r="AD28" s="66"/>
-      <c r="AE28" s="66"/>
-      <c r="AF28" s="66"/>
-      <c r="AG28" s="66"/>
-      <c r="AH28" s="66"/>
-      <c r="AI28" s="66"/>
-      <c r="AJ28" s="66"/>
-      <c r="AK28" s="66"/>
-      <c r="AL28" s="66"/>
-      <c r="AM28" s="66"/>
+      <c r="Z28" s="18"/>
+      <c r="AA28" s="18"/>
+      <c r="AB28" s="18"/>
+      <c r="AC28" s="18"/>
+      <c r="AD28" s="18"/>
+      <c r="AE28" s="18"/>
+      <c r="AF28" s="18"/>
+      <c r="AG28" s="18"/>
+      <c r="AH28" s="18"/>
+      <c r="AI28" s="18"/>
+      <c r="AJ28" s="18"/>
+      <c r="AK28" s="18"/>
+      <c r="AL28" s="18"/>
+      <c r="AM28" s="18"/>
       <c r="AN28" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="53"/>
-      <c r="C29" s="53"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="53"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="53"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="53"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="53"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
-      <c r="Y29" s="66" t="s">
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="45"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="45"/>
+      <c r="U29" s="45"/>
+      <c r="V29" s="45"/>
+      <c r="W29" s="45"/>
+      <c r="Y29" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="Z29" s="66"/>
-      <c r="AA29" s="66"/>
-      <c r="AB29" s="66"/>
-      <c r="AC29" s="66"/>
-      <c r="AD29" s="66"/>
-      <c r="AE29" s="66"/>
-      <c r="AF29" s="66"/>
-      <c r="AG29" s="66"/>
-      <c r="AH29" s="66"/>
-      <c r="AI29" s="66"/>
-      <c r="AJ29" s="66"/>
-      <c r="AK29" s="66"/>
-      <c r="AL29" s="66"/>
-      <c r="AM29" s="66"/>
+      <c r="Z29" s="18"/>
+      <c r="AA29" s="18"/>
+      <c r="AB29" s="18"/>
+      <c r="AC29" s="18"/>
+      <c r="AD29" s="18"/>
+      <c r="AE29" s="18"/>
+      <c r="AF29" s="18"/>
+      <c r="AG29" s="18"/>
+      <c r="AH29" s="18"/>
+      <c r="AI29" s="18"/>
+      <c r="AJ29" s="18"/>
+      <c r="AK29" s="18"/>
+      <c r="AL29" s="18"/>
+      <c r="AM29" s="18"/>
       <c r="AN29" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="53" t="s">
+      <c r="A30" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="53"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="53"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="53"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="45"/>
+      <c r="S30" s="45"/>
+      <c r="T30" s="45"/>
+      <c r="U30" s="45"/>
+      <c r="V30" s="45"/>
+      <c r="W30" s="45"/>
       <c r="X30" s="3"/>
-      <c r="Y30" s="66" t="s">
+      <c r="Y30" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="Z30" s="66"/>
-      <c r="AA30" s="66"/>
-      <c r="AB30" s="66"/>
-      <c r="AC30" s="66"/>
-      <c r="AD30" s="66"/>
-      <c r="AE30" s="66"/>
-      <c r="AF30" s="66"/>
-      <c r="AG30" s="66"/>
-      <c r="AH30" s="66"/>
-      <c r="AI30" s="66"/>
-      <c r="AJ30" s="66"/>
-      <c r="AK30" s="66"/>
-      <c r="AL30" s="66"/>
-      <c r="AM30" s="66"/>
+      <c r="Z30" s="18"/>
+      <c r="AA30" s="18"/>
+      <c r="AB30" s="18"/>
+      <c r="AC30" s="18"/>
+      <c r="AD30" s="18"/>
+      <c r="AE30" s="18"/>
+      <c r="AF30" s="18"/>
+      <c r="AG30" s="18"/>
+      <c r="AH30" s="18"/>
+      <c r="AI30" s="18"/>
+      <c r="AJ30" s="18"/>
+      <c r="AK30" s="18"/>
+      <c r="AL30" s="18"/>
+      <c r="AM30" s="18"/>
       <c r="AN30" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="53"/>
-      <c r="K31" s="53"/>
-      <c r="L31" s="53"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="53"/>
-      <c r="O31" s="53"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14"/>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="45"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="45"/>
+      <c r="U31" s="45"/>
+      <c r="V31" s="45"/>
+      <c r="W31" s="45"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="8"/>
       <c r="Z31" s="8"/>
@@ -2488,31 +2498,31 @@
       <c r="AN31" s="3"/>
     </row>
     <row r="32" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="62" t="s">
+      <c r="A32" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="62"/>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
-      <c r="L32" s="62"/>
-      <c r="M32" s="62"/>
-      <c r="N32" s="62"/>
-      <c r="O32" s="62"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
-      <c r="V32" s="14"/>
-      <c r="W32" s="14"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="45"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="45"/>
+      <c r="U32" s="45"/>
+      <c r="V32" s="45"/>
+      <c r="W32" s="45"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="11"/>
       <c r="Z32" s="11"/>
@@ -2532,31 +2542,31 @@
       <c r="AN32" s="3"/>
     </row>
     <row r="33" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="53" t="s">
+      <c r="A33" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="45"/>
+      <c r="S33" s="45"/>
+      <c r="T33" s="45"/>
+      <c r="U33" s="45"/>
+      <c r="V33" s="45"/>
+      <c r="W33" s="45"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="11"/>
       <c r="Z33" s="11"/>
@@ -2576,31 +2586,31 @@
       <c r="AN33" s="3"/>
     </row>
     <row r="34" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="53"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="14"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="14"/>
-      <c r="V34" s="14"/>
-      <c r="W34" s="14"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="45"/>
+      <c r="S34" s="45"/>
+      <c r="T34" s="45"/>
+      <c r="U34" s="45"/>
+      <c r="V34" s="45"/>
+      <c r="W34" s="45"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="11"/>
       <c r="Z34" s="11"/>
@@ -2620,85 +2630,85 @@
       <c r="AN34" s="3"/>
     </row>
     <row r="35" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="63" t="s">
+      <c r="A35" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="63"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="63"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="63"/>
-      <c r="J35" s="63"/>
-      <c r="K35" s="63"/>
-      <c r="L35" s="63"/>
-      <c r="M35" s="63"/>
-      <c r="N35" s="63"/>
-      <c r="O35" s="63"/>
-      <c r="P35" s="14">
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="45">
         <f>SUM(P25:Q34)/10</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="14"/>
-      <c r="R35" s="14">
+      <c r="Q35" s="45"/>
+      <c r="R35" s="45">
         <f>SUM(R25:S34)/10</f>
         <v>0</v>
       </c>
-      <c r="S35" s="14"/>
-      <c r="T35" s="14">
+      <c r="S35" s="45"/>
+      <c r="T35" s="45">
         <f>SUM(T25:U34)/10</f>
         <v>0</v>
       </c>
-      <c r="U35" s="14"/>
-      <c r="V35" s="14">
+      <c r="U35" s="45"/>
+      <c r="V35" s="45">
         <f>SUM(V25:W34)/10</f>
         <v>0</v>
       </c>
-      <c r="W35" s="14"/>
+      <c r="W35" s="45"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="11"/>
       <c r="Z35" s="11"/>
       <c r="AA35" s="11"/>
       <c r="AB35" s="11"/>
       <c r="AC35" s="11"/>
-      <c r="AD35" s="16"/>
-      <c r="AE35" s="16"/>
-      <c r="AF35" s="16"/>
-      <c r="AG35" s="16"/>
-      <c r="AH35" s="16"/>
-      <c r="AI35" s="16"/>
-      <c r="AJ35" s="16"/>
-      <c r="AK35" s="16"/>
-      <c r="AL35" s="16"/>
-      <c r="AM35" s="16"/>
-      <c r="AN35" s="16"/>
+      <c r="AD35" s="69"/>
+      <c r="AE35" s="69"/>
+      <c r="AF35" s="69"/>
+      <c r="AG35" s="69"/>
+      <c r="AH35" s="69"/>
+      <c r="AI35" s="69"/>
+      <c r="AJ35" s="69"/>
+      <c r="AK35" s="69"/>
+      <c r="AL35" s="69"/>
+      <c r="AM35" s="69"/>
+      <c r="AN35" s="69"/>
     </row>
     <row r="36" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="61"/>
-      <c r="B36" s="61"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="61"/>
-      <c r="M36" s="61"/>
-      <c r="N36" s="61"/>
-      <c r="O36" s="61"/>
-      <c r="P36" s="49"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="49"/>
-      <c r="S36" s="49"/>
-      <c r="T36" s="49"/>
-      <c r="U36" s="49"/>
-      <c r="V36" s="49"/>
-      <c r="W36" s="49"/>
+      <c r="A36" s="40"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="40"/>
+      <c r="M36" s="40"/>
+      <c r="N36" s="40"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="51"/>
+      <c r="Q36" s="51"/>
+      <c r="R36" s="51"/>
+      <c r="S36" s="51"/>
+      <c r="T36" s="51"/>
+      <c r="U36" s="51"/>
+      <c r="V36" s="51"/>
+      <c r="W36" s="51"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="11"/>
       <c r="Z36" s="11"/>
@@ -2720,29 +2730,29 @@
       <c r="AN36" s="12"/>
     </row>
     <row r="37" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="61"/>
-      <c r="B37" s="61"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="61"/>
-      <c r="M37" s="61"/>
-      <c r="N37" s="61"/>
-      <c r="O37" s="61"/>
-      <c r="P37" s="49"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="49"/>
-      <c r="S37" s="49"/>
-      <c r="T37" s="49"/>
-      <c r="U37" s="49"/>
-      <c r="V37" s="49"/>
-      <c r="W37" s="49"/>
+      <c r="A37" s="40"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="40"/>
+      <c r="M37" s="40"/>
+      <c r="N37" s="40"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="51"/>
+      <c r="Q37" s="51"/>
+      <c r="R37" s="51"/>
+      <c r="S37" s="51"/>
+      <c r="T37" s="51"/>
+      <c r="U37" s="51"/>
+      <c r="V37" s="51"/>
+      <c r="W37" s="51"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="11"/>
       <c r="Z37" s="11"/>
@@ -2751,72 +2761,72 @@
       <c r="AC37" s="11"/>
       <c r="AE37" s="2"/>
       <c r="AF37" s="2"/>
-      <c r="AG37" s="33" t="s">
+      <c r="AG37" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="AH37" s="33"/>
-      <c r="AI37" s="33"/>
-      <c r="AJ37" s="33"/>
-      <c r="AK37" s="33"/>
-      <c r="AL37" s="33"/>
+      <c r="AH37" s="60"/>
+      <c r="AI37" s="60"/>
+      <c r="AJ37" s="60"/>
+      <c r="AK37" s="60"/>
+      <c r="AL37" s="60"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
     </row>
     <row r="38" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="17" t="s">
+      <c r="B38" s="47"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17" t="s">
+      <c r="H38" s="13"/>
+      <c r="I38" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17" t="s">
+      <c r="J38" s="13"/>
+      <c r="K38" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17" t="s">
+      <c r="L38" s="13"/>
+      <c r="M38" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17" t="s">
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17" t="s">
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="R38" s="17"/>
-      <c r="S38" s="17" t="s">
+      <c r="R38" s="13"/>
+      <c r="S38" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="T38" s="17"/>
-      <c r="U38" s="17" t="s">
+      <c r="T38" s="13"/>
+      <c r="U38" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="V38" s="17"/>
-      <c r="W38" s="17" t="s">
+      <c r="V38" s="13"/>
+      <c r="W38" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="X38" s="17"/>
-      <c r="Y38" s="17" t="s">
+      <c r="X38" s="13"/>
+      <c r="Y38" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="Z38" s="17"/>
-      <c r="AA38" s="17" t="s">
+      <c r="Z38" s="13"/>
+      <c r="AA38" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AB38" s="17"/>
-      <c r="AC38" s="15"/>
-      <c r="AD38" s="15"/>
+      <c r="AB38" s="13"/>
+      <c r="AC38" s="47"/>
+      <c r="AD38" s="47"/>
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
       <c r="AI38" s="3"/>
@@ -2827,61 +2837,61 @@
       <c r="AN38" s="3"/>
     </row>
     <row r="39" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="19">
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="44">
         <v>18</v>
       </c>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19">
+      <c r="H39" s="44"/>
+      <c r="I39" s="44">
         <v>23</v>
       </c>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19">
+      <c r="J39" s="44"/>
+      <c r="K39" s="44">
         <v>22</v>
       </c>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19">
+      <c r="L39" s="44"/>
+      <c r="M39" s="44">
         <v>19</v>
       </c>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19">
+      <c r="N39" s="44"/>
+      <c r="O39" s="44">
         <v>16</v>
       </c>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="19">
+      <c r="P39" s="44"/>
+      <c r="Q39" s="44">
         <v>22</v>
       </c>
-      <c r="R39" s="19"/>
-      <c r="S39" s="19">
+      <c r="R39" s="44"/>
+      <c r="S39" s="44">
         <v>22</v>
       </c>
-      <c r="T39" s="19"/>
-      <c r="U39" s="19">
+      <c r="T39" s="44"/>
+      <c r="U39" s="44">
         <v>20</v>
       </c>
-      <c r="V39" s="19"/>
-      <c r="W39" s="19">
+      <c r="V39" s="44"/>
+      <c r="W39" s="44">
         <v>22</v>
       </c>
-      <c r="X39" s="19"/>
-      <c r="Y39" s="19">
+      <c r="X39" s="44"/>
+      <c r="Y39" s="44">
         <v>16</v>
       </c>
-      <c r="Z39" s="21"/>
-      <c r="AA39" s="14">
+      <c r="Z39" s="72"/>
+      <c r="AA39" s="45">
         <f>SUM(G39:Z39)</f>
         <v>200</v>
       </c>
-      <c r="AB39" s="14"/>
-      <c r="AC39" s="54"/>
-      <c r="AD39" s="54"/>
+      <c r="AB39" s="45"/>
+      <c r="AC39" s="14"/>
+      <c r="AD39" s="14"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
@@ -2892,78 +2902,78 @@
       <c r="AN39" s="3"/>
     </row>
     <row r="40" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="20"/>
-      <c r="R40" s="20"/>
-      <c r="S40" s="19"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="19"/>
-      <c r="V40" s="19"/>
-      <c r="W40" s="20"/>
-      <c r="X40" s="20"/>
-      <c r="Y40" s="22"/>
-      <c r="Z40" s="23"/>
-      <c r="AA40" s="18">
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="67"/>
+      <c r="M40" s="44"/>
+      <c r="N40" s="44"/>
+      <c r="O40" s="44"/>
+      <c r="P40" s="44"/>
+      <c r="Q40" s="71"/>
+      <c r="R40" s="71"/>
+      <c r="S40" s="44"/>
+      <c r="T40" s="44"/>
+      <c r="U40" s="44"/>
+      <c r="V40" s="44"/>
+      <c r="W40" s="71"/>
+      <c r="X40" s="71"/>
+      <c r="Y40" s="67"/>
+      <c r="Z40" s="73"/>
+      <c r="AA40" s="70">
         <f>SUM(G40:Z40)</f>
         <v>0</v>
       </c>
-      <c r="AB40" s="18"/>
-      <c r="AC40" s="54"/>
-      <c r="AD40" s="54"/>
+      <c r="AB40" s="70"/>
+      <c r="AC40" s="14"/>
+      <c r="AD40" s="14"/>
     </row>
     <row r="41" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="24" t="s">
+      <c r="A41" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="19"/>
-      <c r="T41" s="19"/>
-      <c r="U41" s="19"/>
-      <c r="V41" s="19"/>
-      <c r="W41" s="19"/>
-      <c r="X41" s="19"/>
-      <c r="Y41" s="19"/>
-      <c r="Z41" s="21"/>
-      <c r="AA41" s="14">
-        <f t="shared" ref="AA40:AA41" si="5">SUM(G41:Z41)</f>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="44"/>
+      <c r="L41" s="44"/>
+      <c r="M41" s="44"/>
+      <c r="N41" s="44"/>
+      <c r="O41" s="44"/>
+      <c r="P41" s="44"/>
+      <c r="Q41" s="44"/>
+      <c r="R41" s="44"/>
+      <c r="S41" s="44"/>
+      <c r="T41" s="44"/>
+      <c r="U41" s="44"/>
+      <c r="V41" s="44"/>
+      <c r="W41" s="44"/>
+      <c r="X41" s="44"/>
+      <c r="Y41" s="44"/>
+      <c r="Z41" s="72"/>
+      <c r="AA41" s="45">
+        <f t="shared" ref="AA41" si="5">SUM(G41:Z41)</f>
         <v>0</v>
       </c>
-      <c r="AB41" s="14"/>
-      <c r="AC41" s="54"/>
-      <c r="AD41" s="54"/>
+      <c r="AB41" s="45"/>
+      <c r="AC41" s="14"/>
+      <c r="AD41" s="14"/>
     </row>
     <row r="42" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
@@ -3032,16 +3042,228 @@
     <row r="82" ht="12.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="256">
-    <mergeCell ref="Y38:Z38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S38:T38"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="AD22:AI22"/>
+    <mergeCell ref="AA41:AB41"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="AD35:AN35"/>
+    <mergeCell ref="AA38:AB38"/>
+    <mergeCell ref="AA39:AB39"/>
+    <mergeCell ref="AA40:AB40"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="W41:X41"/>
+    <mergeCell ref="W40:X40"/>
+    <mergeCell ref="W39:X39"/>
+    <mergeCell ref="Y39:Z39"/>
+    <mergeCell ref="Y40:Z40"/>
+    <mergeCell ref="Y41:Z41"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="S41:T41"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="AJ19:AN19"/>
+    <mergeCell ref="AJ20:AN20"/>
+    <mergeCell ref="AJ18:AN18"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AJ13:AN13"/>
+    <mergeCell ref="AJ14:AN14"/>
+    <mergeCell ref="AJ15:AN15"/>
+    <mergeCell ref="AJ16:AN16"/>
+    <mergeCell ref="AJ17:AN17"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AJ21:AN21"/>
+    <mergeCell ref="AG37:AL37"/>
+    <mergeCell ref="V15:Y15"/>
+    <mergeCell ref="Z18:AC18"/>
+    <mergeCell ref="Z19:AC19"/>
+    <mergeCell ref="O1:AA1"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="AH4:AN4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="AJ7:AN7"/>
+    <mergeCell ref="AJ8:AN8"/>
+    <mergeCell ref="AJ9:AN9"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="R19:U19"/>
+    <mergeCell ref="Z12:AC12"/>
+    <mergeCell ref="V12:Y12"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="V20:Y20"/>
+    <mergeCell ref="Z7:AC7"/>
+    <mergeCell ref="Z8:AC8"/>
+    <mergeCell ref="Z9:AC9"/>
+    <mergeCell ref="Z11:AC11"/>
+    <mergeCell ref="Z13:AC13"/>
+    <mergeCell ref="Z14:AC14"/>
+    <mergeCell ref="Z15:AC15"/>
+    <mergeCell ref="Z16:AC16"/>
+    <mergeCell ref="Z17:AC17"/>
+    <mergeCell ref="V16:Y16"/>
+    <mergeCell ref="V17:Y17"/>
+    <mergeCell ref="V18:Y18"/>
+    <mergeCell ref="V19:Y19"/>
+    <mergeCell ref="V8:Y8"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="V11:Y11"/>
+    <mergeCell ref="V13:Y13"/>
+    <mergeCell ref="V14:Y14"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="R7:U7"/>
+    <mergeCell ref="R8:U8"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="R11:U11"/>
+    <mergeCell ref="R13:U13"/>
+    <mergeCell ref="R14:U14"/>
+    <mergeCell ref="R15:U15"/>
+    <mergeCell ref="R16:U16"/>
+    <mergeCell ref="R12:U12"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="N8:Q8"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="N13:Q13"/>
+    <mergeCell ref="N14:Q14"/>
+    <mergeCell ref="B16:M16"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="B15:M15"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N15:Q15"/>
+    <mergeCell ref="N16:Q16"/>
+    <mergeCell ref="N17:Q17"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="N12:Q12"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="E3:U3"/>
+    <mergeCell ref="Z3:AN3"/>
+    <mergeCell ref="U4:AG4"/>
+    <mergeCell ref="G4:P4"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="N5:AC5"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="V6:Y6"/>
+    <mergeCell ref="Z6:AC6"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="V35:W35"/>
+    <mergeCell ref="V36:W36"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="Z20:AC20"/>
+    <mergeCell ref="R20:U20"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="AC38:AD38"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="C20:M20"/>
+    <mergeCell ref="N21:AC21"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A32:O32"/>
+    <mergeCell ref="A33:O33"/>
+    <mergeCell ref="A34:O34"/>
+    <mergeCell ref="A35:O35"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="P25:Q25"/>
     <mergeCell ref="AC41:AD41"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:N2"/>
@@ -3066,237 +3288,35 @@
     <mergeCell ref="R17:U17"/>
     <mergeCell ref="R18:U18"/>
     <mergeCell ref="C21:G21"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="C20:M20"/>
-    <mergeCell ref="N21:AC21"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="A33:O33"/>
-    <mergeCell ref="A34:O34"/>
-    <mergeCell ref="A35:O35"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="Z20:AC20"/>
-    <mergeCell ref="R20:U20"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="AC38:AD38"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A26:O26"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="N19:Q19"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="V35:W35"/>
-    <mergeCell ref="V36:W36"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N15:Q15"/>
-    <mergeCell ref="N16:Q16"/>
-    <mergeCell ref="N17:Q17"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="E3:U3"/>
-    <mergeCell ref="Z3:AN3"/>
-    <mergeCell ref="U4:AG4"/>
-    <mergeCell ref="G4:P4"/>
-    <mergeCell ref="A5:M6"/>
-    <mergeCell ref="N5:AC5"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="R6:U6"/>
-    <mergeCell ref="V6:Y6"/>
-    <mergeCell ref="Z6:AC6"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="B16:M16"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="B15:M15"/>
-    <mergeCell ref="R15:U15"/>
-    <mergeCell ref="R16:U16"/>
-    <mergeCell ref="R12:U12"/>
-    <mergeCell ref="N7:Q7"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="N13:Q13"/>
-    <mergeCell ref="N14:Q14"/>
-    <mergeCell ref="V8:Y8"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="V11:Y11"/>
-    <mergeCell ref="V13:Y13"/>
-    <mergeCell ref="V14:Y14"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="R7:U7"/>
-    <mergeCell ref="R8:U8"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="R11:U11"/>
-    <mergeCell ref="R13:U13"/>
-    <mergeCell ref="R14:U14"/>
-    <mergeCell ref="Z13:AC13"/>
-    <mergeCell ref="Z14:AC14"/>
-    <mergeCell ref="Z15:AC15"/>
-    <mergeCell ref="Z16:AC16"/>
-    <mergeCell ref="Z17:AC17"/>
-    <mergeCell ref="V16:Y16"/>
-    <mergeCell ref="V17:Y17"/>
-    <mergeCell ref="V18:Y18"/>
-    <mergeCell ref="V19:Y19"/>
-    <mergeCell ref="AG37:AL37"/>
-    <mergeCell ref="V15:Y15"/>
-    <mergeCell ref="Z18:AC18"/>
-    <mergeCell ref="Z19:AC19"/>
-    <mergeCell ref="O1:AA1"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="AH4:AN4"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="AJ7:AN7"/>
-    <mergeCell ref="AJ8:AN8"/>
-    <mergeCell ref="AJ9:AN9"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="R19:U19"/>
-    <mergeCell ref="Z12:AC12"/>
-    <mergeCell ref="V12:Y12"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="V20:Y20"/>
-    <mergeCell ref="Z7:AC7"/>
-    <mergeCell ref="Z8:AC8"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="Z11:AC11"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="AJ19:AN19"/>
-    <mergeCell ref="AJ20:AN20"/>
-    <mergeCell ref="AJ18:AN18"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AJ13:AN13"/>
-    <mergeCell ref="AJ14:AN14"/>
-    <mergeCell ref="AJ15:AN15"/>
-    <mergeCell ref="AJ16:AN16"/>
-    <mergeCell ref="AJ17:AN17"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AJ21:AN21"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="AD22:AI22"/>
-    <mergeCell ref="AA41:AB41"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="AD35:AN35"/>
-    <mergeCell ref="AA38:AB38"/>
-    <mergeCell ref="AA39:AB39"/>
-    <mergeCell ref="AA40:AB40"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="U41:V41"/>
-    <mergeCell ref="W41:X41"/>
-    <mergeCell ref="W40:X40"/>
-    <mergeCell ref="W39:X39"/>
-    <mergeCell ref="Y39:Z39"/>
-    <mergeCell ref="Y40:Z40"/>
-    <mergeCell ref="Y41:Z41"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="S41:T41"/>
-    <mergeCell ref="S40:T40"/>
-    <mergeCell ref="S39:T39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="Y38:Z38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="W38:X38"/>
   </mergeCells>
   <conditionalFormatting sqref="AD7:AI19">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ7:AN19">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:AC19">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>75</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ7:AN19">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"Failed"</formula>
+  <conditionalFormatting sqref="AD21:AI21">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>75</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/public/files/report_card_templates/JHS.xlsx
+++ b/public/files/report_card_templates/JHS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\schoolsys\public\files\report_card_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98734B0-E9E8-4866-B299-A6628249FA36}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A060D9D4-73A3-4513-B976-7AAB79F45556}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -504,14 +504,158 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -542,150 +686,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1053,260 +1053,260 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O1" s="61" t="s">
+      <c r="O1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
-      <c r="U1" s="61"/>
-      <c r="V1" s="61"/>
-      <c r="W1" s="61"/>
-      <c r="X1" s="61"/>
-      <c r="Y1" s="61"/>
-      <c r="Z1" s="61"/>
-      <c r="AA1" s="61"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
     </row>
     <row r="2" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="Q2" s="15" t="s">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="Q2" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
     </row>
     <row r="3" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55"/>
-      <c r="V3" s="62" t="s">
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="55"/>
-      <c r="AA3" s="55"/>
-      <c r="AB3" s="55"/>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="55"/>
-      <c r="AE3" s="55"/>
-      <c r="AF3" s="55"/>
-      <c r="AG3" s="55"/>
-      <c r="AH3" s="55"/>
-      <c r="AI3" s="55"/>
-      <c r="AJ3" s="55"/>
-      <c r="AK3" s="55"/>
-      <c r="AL3" s="55"/>
-      <c r="AM3" s="55"/>
-      <c r="AN3" s="55"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="45"/>
+      <c r="AM3" s="45"/>
+      <c r="AN3" s="45"/>
     </row>
     <row r="4" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="59" t="s">
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="59"/>
-      <c r="S4" s="59"/>
-      <c r="T4" s="59"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="56"/>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="56"/>
-      <c r="AG4" s="56"/>
-      <c r="AH4" s="59"/>
-      <c r="AI4" s="59"/>
-      <c r="AJ4" s="59"/>
-      <c r="AK4" s="59"/>
-      <c r="AL4" s="59"/>
-      <c r="AM4" s="59"/>
-      <c r="AN4" s="59"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
+      <c r="Z4" s="46"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="46"/>
+      <c r="AD4" s="46"/>
+      <c r="AE4" s="46"/>
+      <c r="AF4" s="46"/>
+      <c r="AG4" s="46"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
     </row>
     <row r="5" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="19" t="s">
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="47"/>
+      <c r="X5" s="47"/>
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="47"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="AE5" s="20"/>
-      <c r="AF5" s="20"/>
-      <c r="AG5" s="20"/>
-      <c r="AH5" s="20"/>
-      <c r="AI5" s="21"/>
-      <c r="AJ5" s="19" t="s">
+      <c r="AE5" s="68"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="69"/>
+      <c r="AJ5" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="AK5" s="20"/>
-      <c r="AL5" s="20"/>
-      <c r="AM5" s="20"/>
-      <c r="AN5" s="21"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
+      <c r="AM5" s="68"/>
+      <c r="AN5" s="69"/>
     </row>
     <row r="6" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="57" t="s">
+      <c r="A6" s="47"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="O6" s="57"/>
-      <c r="P6" s="57"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="57" t="s">
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="S6" s="57"/>
-      <c r="T6" s="57"/>
-      <c r="U6" s="57"/>
-      <c r="V6" s="57" t="s">
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="57"/>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="57" t="s">
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="57"/>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="23"/>
-      <c r="AF6" s="23"/>
-      <c r="AG6" s="23"/>
-      <c r="AH6" s="23"/>
-      <c r="AI6" s="24"/>
-      <c r="AJ6" s="22"/>
-      <c r="AK6" s="23"/>
-      <c r="AL6" s="23"/>
-      <c r="AM6" s="23"/>
-      <c r="AN6" s="24"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="70"/>
+      <c r="AE6" s="71"/>
+      <c r="AF6" s="71"/>
+      <c r="AG6" s="71"/>
+      <c r="AH6" s="71"/>
+      <c r="AI6" s="72"/>
+      <c r="AJ6" s="70"/>
+      <c r="AK6" s="71"/>
+      <c r="AL6" s="71"/>
+      <c r="AM6" s="71"/>
+      <c r="AN6" s="72"/>
     </row>
     <row r="7" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
       <c r="N7" s="28"/>
       <c r="O7" s="28"/>
       <c r="P7" s="28"/>
@@ -1323,15 +1323,15 @@
       <c r="AA7" s="28"/>
       <c r="AB7" s="28"/>
       <c r="AC7" s="28"/>
-      <c r="AD7" s="29" t="str">
+      <c r="AD7" s="25" t="str">
         <f>IF(COUNT(N7:AC7)=4,SUM(N7:AC7)/4,"")</f>
         <v/>
       </c>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="31"/>
+      <c r="AE7" s="26"/>
+      <c r="AF7" s="26"/>
+      <c r="AG7" s="26"/>
+      <c r="AH7" s="26"/>
+      <c r="AI7" s="27"/>
       <c r="AJ7" s="28" t="str">
         <f>IF(AD7&lt;&gt;"",IF(AD7&gt;=75,"Passed","Failed"),"")</f>
         <v/>
@@ -1342,21 +1342,21 @@
       <c r="AN7" s="28"/>
     </row>
     <row r="8" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
       <c r="N8" s="28"/>
       <c r="O8" s="28"/>
       <c r="P8" s="28"/>
@@ -1373,15 +1373,15 @@
       <c r="AA8" s="28"/>
       <c r="AB8" s="28"/>
       <c r="AC8" s="28"/>
-      <c r="AD8" s="29" t="str">
+      <c r="AD8" s="25" t="str">
         <f t="shared" ref="AD8:AD19" si="0">IF(COUNT(N8:AC8)=4,SUM(N8:AC8)/4,"")</f>
         <v/>
       </c>
-      <c r="AE8" s="30"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="30"/>
-      <c r="AH8" s="30"/>
-      <c r="AI8" s="31"/>
+      <c r="AE8" s="26"/>
+      <c r="AF8" s="26"/>
+      <c r="AG8" s="26"/>
+      <c r="AH8" s="26"/>
+      <c r="AI8" s="27"/>
       <c r="AJ8" s="28" t="str">
         <f t="shared" ref="AJ8:AJ19" si="1">IF(AD8&lt;&gt;"",IF(AD8&gt;=75,"Passed","Failed"),"")</f>
         <v/>
@@ -1392,21 +1392,21 @@
       <c r="AN8" s="28"/>
     </row>
     <row r="9" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
       <c r="N9" s="28"/>
       <c r="O9" s="28"/>
       <c r="P9" s="28"/>
@@ -1423,15 +1423,15 @@
       <c r="AA9" s="28"/>
       <c r="AB9" s="28"/>
       <c r="AC9" s="28"/>
-      <c r="AD9" s="29" t="str">
+      <c r="AD9" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE9" s="30"/>
-      <c r="AF9" s="30"/>
-      <c r="AG9" s="30"/>
-      <c r="AH9" s="30"/>
-      <c r="AI9" s="31"/>
+      <c r="AE9" s="26"/>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26"/>
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="27"/>
       <c r="AJ9" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1442,21 +1442,21 @@
       <c r="AN9" s="28"/>
     </row>
     <row r="10" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="27"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="40"/>
       <c r="N10" s="28"/>
       <c r="O10" s="28"/>
       <c r="P10" s="28"/>
@@ -1473,15 +1473,15 @@
       <c r="AA10" s="28"/>
       <c r="AB10" s="28"/>
       <c r="AC10" s="28"/>
-      <c r="AD10" s="29" t="str">
+      <c r="AD10" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="30"/>
-      <c r="AG10" s="30"/>
-      <c r="AH10" s="30"/>
-      <c r="AI10" s="31"/>
+      <c r="AE10" s="26"/>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="26"/>
+      <c r="AH10" s="26"/>
+      <c r="AI10" s="27"/>
       <c r="AJ10" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1492,21 +1492,21 @@
       <c r="AN10" s="28"/>
     </row>
     <row r="11" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="49"/>
-      <c r="M11" s="49"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
       <c r="N11" s="28"/>
       <c r="O11" s="28"/>
       <c r="P11" s="28"/>
@@ -1523,15 +1523,15 @@
       <c r="AA11" s="28"/>
       <c r="AB11" s="28"/>
       <c r="AC11" s="28"/>
-      <c r="AD11" s="29" t="str">
+      <c r="AD11" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="30"/>
-      <c r="AG11" s="30"/>
-      <c r="AH11" s="30"/>
-      <c r="AI11" s="31"/>
+      <c r="AE11" s="26"/>
+      <c r="AF11" s="26"/>
+      <c r="AG11" s="26"/>
+      <c r="AH11" s="26"/>
+      <c r="AI11" s="27"/>
       <c r="AJ11" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1542,21 +1542,21 @@
       <c r="AN11" s="28"/>
     </row>
     <row r="12" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="54"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="44"/>
       <c r="N12" s="28"/>
       <c r="O12" s="28"/>
       <c r="P12" s="28"/>
@@ -1573,15 +1573,15 @@
       <c r="AA12" s="28"/>
       <c r="AB12" s="28"/>
       <c r="AC12" s="28"/>
-      <c r="AD12" s="29" t="str">
+      <c r="AD12" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE12" s="30"/>
-      <c r="AF12" s="30"/>
-      <c r="AG12" s="30"/>
-      <c r="AH12" s="30"/>
-      <c r="AI12" s="31"/>
+      <c r="AE12" s="26"/>
+      <c r="AF12" s="26"/>
+      <c r="AG12" s="26"/>
+      <c r="AH12" s="26"/>
+      <c r="AI12" s="27"/>
       <c r="AJ12" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1592,21 +1592,21 @@
       <c r="AN12" s="28"/>
     </row>
     <row r="13" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
       <c r="N13" s="28"/>
       <c r="O13" s="28"/>
       <c r="P13" s="28"/>
@@ -1623,15 +1623,15 @@
       <c r="AA13" s="28"/>
       <c r="AB13" s="28"/>
       <c r="AC13" s="28"/>
-      <c r="AD13" s="29" t="str">
+      <c r="AD13" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE13" s="30"/>
-      <c r="AF13" s="30"/>
-      <c r="AG13" s="30"/>
-      <c r="AH13" s="30"/>
-      <c r="AI13" s="31"/>
+      <c r="AE13" s="26"/>
+      <c r="AF13" s="26"/>
+      <c r="AG13" s="26"/>
+      <c r="AH13" s="26"/>
+      <c r="AI13" s="27"/>
       <c r="AJ13" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1643,20 +1643,20 @@
     </row>
     <row r="14" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="27"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="40"/>
       <c r="N14" s="28"/>
       <c r="O14" s="28"/>
       <c r="P14" s="28"/>
@@ -1673,15 +1673,15 @@
       <c r="AA14" s="28"/>
       <c r="AB14" s="28"/>
       <c r="AC14" s="28"/>
-      <c r="AD14" s="29" t="str">
+      <c r="AD14" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE14" s="30"/>
-      <c r="AF14" s="30"/>
-      <c r="AG14" s="30"/>
-      <c r="AH14" s="30"/>
-      <c r="AI14" s="31"/>
+      <c r="AE14" s="26"/>
+      <c r="AF14" s="26"/>
+      <c r="AG14" s="26"/>
+      <c r="AH14" s="26"/>
+      <c r="AI14" s="27"/>
       <c r="AJ14" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1693,20 +1693,20 @@
     </row>
     <row r="15" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="27"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="40"/>
       <c r="N15" s="28"/>
       <c r="O15" s="28"/>
       <c r="P15" s="28"/>
@@ -1723,15 +1723,15 @@
       <c r="AA15" s="28"/>
       <c r="AB15" s="28"/>
       <c r="AC15" s="28"/>
-      <c r="AD15" s="29" t="str">
+      <c r="AD15" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE15" s="30"/>
-      <c r="AF15" s="30"/>
-      <c r="AG15" s="30"/>
-      <c r="AH15" s="30"/>
-      <c r="AI15" s="31"/>
+      <c r="AE15" s="26"/>
+      <c r="AF15" s="26"/>
+      <c r="AG15" s="26"/>
+      <c r="AH15" s="26"/>
+      <c r="AI15" s="27"/>
       <c r="AJ15" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1743,20 +1743,20 @@
     </row>
     <row r="16" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="27"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="40"/>
       <c r="N16" s="28"/>
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
@@ -1773,15 +1773,15 @@
       <c r="AA16" s="28"/>
       <c r="AB16" s="28"/>
       <c r="AC16" s="28"/>
-      <c r="AD16" s="29" t="str">
+      <c r="AD16" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE16" s="30"/>
-      <c r="AF16" s="30"/>
-      <c r="AG16" s="30"/>
-      <c r="AH16" s="30"/>
-      <c r="AI16" s="31"/>
+      <c r="AE16" s="26"/>
+      <c r="AF16" s="26"/>
+      <c r="AG16" s="26"/>
+      <c r="AH16" s="26"/>
+      <c r="AI16" s="27"/>
       <c r="AJ16" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1793,20 +1793,20 @@
     </row>
     <row r="17" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="27"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="40"/>
       <c r="N17" s="28"/>
       <c r="O17" s="28"/>
       <c r="P17" s="28"/>
@@ -1823,15 +1823,15 @@
       <c r="AA17" s="28"/>
       <c r="AB17" s="28"/>
       <c r="AC17" s="28"/>
-      <c r="AD17" s="29" t="str">
+      <c r="AD17" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE17" s="30"/>
-      <c r="AF17" s="30"/>
-      <c r="AG17" s="30"/>
-      <c r="AH17" s="30"/>
-      <c r="AI17" s="31"/>
+      <c r="AE17" s="26"/>
+      <c r="AF17" s="26"/>
+      <c r="AG17" s="26"/>
+      <c r="AH17" s="26"/>
+      <c r="AI17" s="27"/>
       <c r="AJ17" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1842,21 +1842,21 @@
       <c r="AN17" s="28"/>
     </row>
     <row r="18" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
       <c r="N18" s="28"/>
       <c r="O18" s="28"/>
       <c r="P18" s="28"/>
@@ -1873,15 +1873,15 @@
       <c r="AA18" s="28"/>
       <c r="AB18" s="28"/>
       <c r="AC18" s="28"/>
-      <c r="AD18" s="29" t="str">
+      <c r="AD18" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE18" s="30"/>
-      <c r="AF18" s="30"/>
-      <c r="AG18" s="30"/>
-      <c r="AH18" s="30"/>
-      <c r="AI18" s="31"/>
+      <c r="AE18" s="26"/>
+      <c r="AF18" s="26"/>
+      <c r="AG18" s="26"/>
+      <c r="AH18" s="26"/>
+      <c r="AI18" s="27"/>
       <c r="AJ18" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1892,21 +1892,21 @@
       <c r="AN18" s="28"/>
     </row>
     <row r="19" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
       <c r="N19" s="28"/>
       <c r="O19" s="28"/>
       <c r="P19" s="28"/>
@@ -1923,15 +1923,15 @@
       <c r="AA19" s="28"/>
       <c r="AB19" s="28"/>
       <c r="AC19" s="28"/>
-      <c r="AD19" s="29" t="str">
+      <c r="AD19" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="30"/>
-      <c r="AH19" s="30"/>
-      <c r="AI19" s="31"/>
+      <c r="AE19" s="26"/>
+      <c r="AF19" s="26"/>
+      <c r="AG19" s="26"/>
+      <c r="AH19" s="26"/>
+      <c r="AI19" s="27"/>
       <c r="AJ19" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1944,53 +1944,53 @@
     <row r="20" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="46" t="str">
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="38" t="str">
         <f>IF(SUM(N7:Q13,N18)/8 &gt; 0, SUM(N7:Q13,N18)/8, "")</f>
         <v/>
       </c>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="46" t="str">
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38" t="str">
         <f t="shared" ref="R20" si="2">IF(SUM(R7:U13,R18)/8 &gt; 0, SUM(R7:U13,R18)/8, "")</f>
         <v/>
       </c>
-      <c r="S20" s="46"/>
-      <c r="T20" s="46"/>
-      <c r="U20" s="46"/>
-      <c r="V20" s="46" t="str">
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38" t="str">
         <f t="shared" ref="V20" si="3">IF(SUM(V7:Y13,V18)/8 &gt; 0, SUM(V7:Y13,V18)/8, "")</f>
         <v/>
       </c>
-      <c r="W20" s="46"/>
-      <c r="X20" s="46"/>
-      <c r="Y20" s="46"/>
-      <c r="Z20" s="46" t="str">
+      <c r="W20" s="38"/>
+      <c r="X20" s="38"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="38" t="str">
         <f t="shared" ref="Z20" si="4">IF(SUM(Z7:AC13,Z18)/8 &gt; 0, SUM(Z7:AC13,Z18)/8, "")</f>
         <v/>
       </c>
-      <c r="AA20" s="46"/>
-      <c r="AB20" s="46"/>
-      <c r="AC20" s="46"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
-      <c r="AG20" s="30"/>
-      <c r="AH20" s="30"/>
-      <c r="AI20" s="31"/>
+      <c r="AA20" s="38"/>
+      <c r="AB20" s="38"/>
+      <c r="AC20" s="38"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="26"/>
+      <c r="AF20" s="26"/>
+      <c r="AG20" s="26"/>
+      <c r="AH20" s="26"/>
+      <c r="AI20" s="27"/>
       <c r="AJ20" s="28"/>
       <c r="AK20" s="28"/>
       <c r="AL20" s="28"/>
@@ -2000,51 +2000,51 @@
     <row r="21" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="37" t="s">
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="38"/>
-      <c r="V21" s="38"/>
-      <c r="W21" s="38"/>
-      <c r="X21" s="38"/>
-      <c r="Y21" s="38"/>
-      <c r="Z21" s="38"/>
-      <c r="AA21" s="38"/>
-      <c r="AB21" s="38"/>
-      <c r="AC21" s="39"/>
-      <c r="AD21" s="63" t="str">
+      <c r="O21" s="59"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="59"/>
+      <c r="R21" s="59"/>
+      <c r="S21" s="59"/>
+      <c r="T21" s="59"/>
+      <c r="U21" s="59"/>
+      <c r="V21" s="59"/>
+      <c r="W21" s="59"/>
+      <c r="X21" s="59"/>
+      <c r="Y21" s="59"/>
+      <c r="Z21" s="59"/>
+      <c r="AA21" s="59"/>
+      <c r="AB21" s="59"/>
+      <c r="AC21" s="60"/>
+      <c r="AD21" s="29" t="str">
         <f>IF(COUNT(AD7:AI13,AD18)=8,SUM(AD7:AI13,AD18)/8,"")</f>
         <v/>
       </c>
-      <c r="AE21" s="64"/>
-      <c r="AF21" s="64"/>
-      <c r="AG21" s="64"/>
-      <c r="AH21" s="64"/>
-      <c r="AI21" s="65"/>
-      <c r="AJ21" s="57"/>
-      <c r="AK21" s="57"/>
-      <c r="AL21" s="57"/>
-      <c r="AM21" s="57"/>
-      <c r="AN21" s="57"/>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="30"/>
+      <c r="AG21" s="30"/>
+      <c r="AH21" s="30"/>
+      <c r="AI21" s="31"/>
+      <c r="AJ21" s="32"/>
+      <c r="AK21" s="32"/>
+      <c r="AL21" s="32"/>
+      <c r="AM21" s="32"/>
+      <c r="AN21" s="32"/>
     </row>
     <row r="22" spans="1:40" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
@@ -2076,12 +2076,12 @@
       <c r="AA22" s="10"/>
       <c r="AB22" s="10"/>
       <c r="AC22" s="10"/>
-      <c r="AD22" s="68"/>
-      <c r="AE22" s="68"/>
-      <c r="AF22" s="68"/>
-      <c r="AG22" s="68"/>
-      <c r="AH22" s="68"/>
-      <c r="AI22" s="68"/>
+      <c r="AD22" s="13"/>
+      <c r="AE22" s="13"/>
+      <c r="AF22" s="13"/>
+      <c r="AG22" s="13"/>
+      <c r="AH22" s="13"/>
+      <c r="AI22" s="13"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
@@ -2118,367 +2118,367 @@
       <c r="Y23" s="2"/>
     </row>
     <row r="24" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="34" t="s">
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="47"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34" t="s">
+      <c r="Q24" s="55"/>
+      <c r="R24" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="S24" s="34"/>
-      <c r="T24" s="34" t="s">
+      <c r="S24" s="55"/>
+      <c r="T24" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="U24" s="34"/>
-      <c r="V24" s="34" t="s">
+      <c r="U24" s="55"/>
+      <c r="V24" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="W24" s="34"/>
-      <c r="Y24" s="17" t="s">
+      <c r="W24" s="55"/>
+      <c r="Y24" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="Z24" s="17"/>
-      <c r="AA24" s="17"/>
-      <c r="AB24" s="17"/>
-      <c r="AC24" s="17"/>
-      <c r="AD24" s="17"/>
-      <c r="AE24" s="17"/>
-      <c r="AF24" s="17"/>
-      <c r="AG24" s="17"/>
-      <c r="AH24" s="17"/>
-      <c r="AI24" s="17"/>
-      <c r="AJ24" s="17"/>
+      <c r="Z24" s="65"/>
+      <c r="AA24" s="65"/>
+      <c r="AB24" s="65"/>
+      <c r="AC24" s="65"/>
+      <c r="AD24" s="65"/>
+      <c r="AE24" s="65"/>
+      <c r="AF24" s="65"/>
+      <c r="AG24" s="65"/>
+      <c r="AH24" s="65"/>
+      <c r="AI24" s="65"/>
+      <c r="AJ24" s="65"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
       <c r="AN24" s="3"/>
     </row>
     <row r="25" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="44"/>
-      <c r="R25" s="44"/>
-      <c r="S25" s="44"/>
-      <c r="T25" s="44"/>
-      <c r="U25" s="44"/>
-      <c r="V25" s="45"/>
-      <c r="W25" s="45"/>
-      <c r="Y25" s="18" t="s">
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="Y25" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="Z25" s="18"/>
-      <c r="AA25" s="18"/>
-      <c r="AB25" s="18"/>
-      <c r="AC25" s="18"/>
-      <c r="AD25" s="18"/>
-      <c r="AE25" s="18"/>
-      <c r="AF25" s="18"/>
-      <c r="AG25" s="18"/>
-      <c r="AH25" s="18"/>
-      <c r="AI25" s="18"/>
-      <c r="AJ25" s="18"/>
-      <c r="AK25" s="18"/>
-      <c r="AL25" s="18"/>
-      <c r="AM25" s="18"/>
+      <c r="Z25" s="66"/>
+      <c r="AA25" s="66"/>
+      <c r="AB25" s="66"/>
+      <c r="AC25" s="66"/>
+      <c r="AD25" s="66"/>
+      <c r="AE25" s="66"/>
+      <c r="AF25" s="66"/>
+      <c r="AG25" s="66"/>
+      <c r="AH25" s="66"/>
+      <c r="AI25" s="66"/>
+      <c r="AJ25" s="66"/>
+      <c r="AK25" s="66"/>
+      <c r="AL25" s="66"/>
+      <c r="AM25" s="66"/>
       <c r="AN25" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="45"/>
-      <c r="U26" s="45"/>
-      <c r="V26" s="45"/>
-      <c r="W26" s="45"/>
-      <c r="Y26" s="18" t="s">
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="Y26" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="Z26" s="18"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="18"/>
-      <c r="AC26" s="18"/>
-      <c r="AD26" s="18"/>
-      <c r="AE26" s="18"/>
-      <c r="AF26" s="18"/>
-      <c r="AG26" s="18"/>
-      <c r="AH26" s="18"/>
-      <c r="AI26" s="18"/>
-      <c r="AJ26" s="18"/>
-      <c r="AK26" s="18"/>
-      <c r="AL26" s="18"/>
-      <c r="AM26" s="18"/>
+      <c r="Z26" s="66"/>
+      <c r="AA26" s="66"/>
+      <c r="AB26" s="66"/>
+      <c r="AC26" s="66"/>
+      <c r="AD26" s="66"/>
+      <c r="AE26" s="66"/>
+      <c r="AF26" s="66"/>
+      <c r="AG26" s="66"/>
+      <c r="AH26" s="66"/>
+      <c r="AI26" s="66"/>
+      <c r="AJ26" s="66"/>
+      <c r="AK26" s="66"/>
+      <c r="AL26" s="66"/>
+      <c r="AM26" s="66"/>
       <c r="AN26" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="45"/>
-      <c r="U27" s="45"/>
-      <c r="V27" s="45"/>
-      <c r="W27" s="45"/>
-      <c r="Y27" s="18" t="s">
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="Y27" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="Z27" s="18"/>
-      <c r="AA27" s="18"/>
-      <c r="AB27" s="18"/>
-      <c r="AC27" s="18"/>
-      <c r="AD27" s="18"/>
-      <c r="AE27" s="18"/>
-      <c r="AF27" s="18"/>
-      <c r="AG27" s="18"/>
-      <c r="AH27" s="18"/>
-      <c r="AI27" s="18"/>
-      <c r="AJ27" s="18"/>
-      <c r="AK27" s="18"/>
-      <c r="AL27" s="18"/>
-      <c r="AM27" s="18"/>
+      <c r="Z27" s="66"/>
+      <c r="AA27" s="66"/>
+      <c r="AB27" s="66"/>
+      <c r="AC27" s="66"/>
+      <c r="AD27" s="66"/>
+      <c r="AE27" s="66"/>
+      <c r="AF27" s="66"/>
+      <c r="AG27" s="66"/>
+      <c r="AH27" s="66"/>
+      <c r="AI27" s="66"/>
+      <c r="AJ27" s="66"/>
+      <c r="AK27" s="66"/>
+      <c r="AL27" s="66"/>
+      <c r="AM27" s="66"/>
       <c r="AN27" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="45"/>
-      <c r="U28" s="45"/>
-      <c r="V28" s="45"/>
-      <c r="W28" s="45"/>
-      <c r="Y28" s="18" t="s">
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="Y28" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="Z28" s="18"/>
-      <c r="AA28" s="18"/>
-      <c r="AB28" s="18"/>
-      <c r="AC28" s="18"/>
-      <c r="AD28" s="18"/>
-      <c r="AE28" s="18"/>
-      <c r="AF28" s="18"/>
-      <c r="AG28" s="18"/>
-      <c r="AH28" s="18"/>
-      <c r="AI28" s="18"/>
-      <c r="AJ28" s="18"/>
-      <c r="AK28" s="18"/>
-      <c r="AL28" s="18"/>
-      <c r="AM28" s="18"/>
+      <c r="Z28" s="66"/>
+      <c r="AA28" s="66"/>
+      <c r="AB28" s="66"/>
+      <c r="AC28" s="66"/>
+      <c r="AD28" s="66"/>
+      <c r="AE28" s="66"/>
+      <c r="AF28" s="66"/>
+      <c r="AG28" s="66"/>
+      <c r="AH28" s="66"/>
+      <c r="AI28" s="66"/>
+      <c r="AJ28" s="66"/>
+      <c r="AK28" s="66"/>
+      <c r="AL28" s="66"/>
+      <c r="AM28" s="66"/>
       <c r="AN28" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="41" t="s">
+      <c r="A29" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="45"/>
-      <c r="U29" s="45"/>
-      <c r="V29" s="45"/>
-      <c r="W29" s="45"/>
-      <c r="Y29" s="18" t="s">
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="53"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="Y29" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="Z29" s="18"/>
-      <c r="AA29" s="18"/>
-      <c r="AB29" s="18"/>
-      <c r="AC29" s="18"/>
-      <c r="AD29" s="18"/>
-      <c r="AE29" s="18"/>
-      <c r="AF29" s="18"/>
-      <c r="AG29" s="18"/>
-      <c r="AH29" s="18"/>
-      <c r="AI29" s="18"/>
-      <c r="AJ29" s="18"/>
-      <c r="AK29" s="18"/>
-      <c r="AL29" s="18"/>
-      <c r="AM29" s="18"/>
+      <c r="Z29" s="66"/>
+      <c r="AA29" s="66"/>
+      <c r="AB29" s="66"/>
+      <c r="AC29" s="66"/>
+      <c r="AD29" s="66"/>
+      <c r="AE29" s="66"/>
+      <c r="AF29" s="66"/>
+      <c r="AG29" s="66"/>
+      <c r="AH29" s="66"/>
+      <c r="AI29" s="66"/>
+      <c r="AJ29" s="66"/>
+      <c r="AK29" s="66"/>
+      <c r="AL29" s="66"/>
+      <c r="AM29" s="66"/>
       <c r="AN29" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="45"/>
-      <c r="U30" s="45"/>
-      <c r="V30" s="45"/>
-      <c r="W30" s="45"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="53"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
       <c r="X30" s="3"/>
-      <c r="Y30" s="18" t="s">
+      <c r="Y30" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="Z30" s="18"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="18"/>
-      <c r="AD30" s="18"/>
-      <c r="AE30" s="18"/>
-      <c r="AF30" s="18"/>
-      <c r="AG30" s="18"/>
-      <c r="AH30" s="18"/>
-      <c r="AI30" s="18"/>
-      <c r="AJ30" s="18"/>
-      <c r="AK30" s="18"/>
-      <c r="AL30" s="18"/>
-      <c r="AM30" s="18"/>
+      <c r="Z30" s="66"/>
+      <c r="AA30" s="66"/>
+      <c r="AB30" s="66"/>
+      <c r="AC30" s="66"/>
+      <c r="AD30" s="66"/>
+      <c r="AE30" s="66"/>
+      <c r="AF30" s="66"/>
+      <c r="AG30" s="66"/>
+      <c r="AH30" s="66"/>
+      <c r="AI30" s="66"/>
+      <c r="AJ30" s="66"/>
+      <c r="AK30" s="66"/>
+      <c r="AL30" s="66"/>
+      <c r="AM30" s="66"/>
       <c r="AN30" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="41" t="s">
+      <c r="A31" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="41"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="45"/>
-      <c r="U31" s="45"/>
-      <c r="V31" s="45"/>
-      <c r="W31" s="45"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="53"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="8"/>
       <c r="Z31" s="8"/>
@@ -2498,31 +2498,31 @@
       <c r="AN31" s="3"/>
     </row>
     <row r="32" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="42" t="s">
+      <c r="A32" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="44"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="45"/>
-      <c r="U32" s="45"/>
-      <c r="V32" s="45"/>
-      <c r="W32" s="45"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
+      <c r="L32" s="62"/>
+      <c r="M32" s="62"/>
+      <c r="N32" s="62"/>
+      <c r="O32" s="62"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="11"/>
       <c r="Z32" s="11"/>
@@ -2542,31 +2542,31 @@
       <c r="AN32" s="3"/>
     </row>
     <row r="33" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="41"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="41"/>
-      <c r="O33" s="41"/>
-      <c r="P33" s="44"/>
-      <c r="Q33" s="44"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="45"/>
-      <c r="U33" s="45"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="45"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="11"/>
       <c r="Z33" s="11"/>
@@ -2586,31 +2586,31 @@
       <c r="AN33" s="3"/>
     </row>
     <row r="34" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="44"/>
-      <c r="Q34" s="44"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="45"/>
-      <c r="U34" s="45"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="45"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="11"/>
       <c r="Z34" s="11"/>
@@ -2630,85 +2630,85 @@
       <c r="AN34" s="3"/>
     </row>
     <row r="35" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="43" t="s">
+      <c r="A35" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="43"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="45">
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="63"/>
+      <c r="P35" s="14">
         <f>SUM(P25:Q34)/10</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="45"/>
-      <c r="R35" s="45">
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14">
         <f>SUM(R25:S34)/10</f>
         <v>0</v>
       </c>
-      <c r="S35" s="45"/>
-      <c r="T35" s="45">
+      <c r="S35" s="14"/>
+      <c r="T35" s="14">
         <f>SUM(T25:U34)/10</f>
         <v>0</v>
       </c>
-      <c r="U35" s="45"/>
-      <c r="V35" s="45">
+      <c r="U35" s="14"/>
+      <c r="V35" s="14">
         <f>SUM(V25:W34)/10</f>
         <v>0</v>
       </c>
-      <c r="W35" s="45"/>
+      <c r="W35" s="14"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="11"/>
       <c r="Z35" s="11"/>
       <c r="AA35" s="11"/>
       <c r="AB35" s="11"/>
       <c r="AC35" s="11"/>
-      <c r="AD35" s="69"/>
-      <c r="AE35" s="69"/>
-      <c r="AF35" s="69"/>
-      <c r="AG35" s="69"/>
-      <c r="AH35" s="69"/>
-      <c r="AI35" s="69"/>
-      <c r="AJ35" s="69"/>
-      <c r="AK35" s="69"/>
-      <c r="AL35" s="69"/>
-      <c r="AM35" s="69"/>
-      <c r="AN35" s="69"/>
+      <c r="AD35" s="16"/>
+      <c r="AE35" s="16"/>
+      <c r="AF35" s="16"/>
+      <c r="AG35" s="16"/>
+      <c r="AH35" s="16"/>
+      <c r="AI35" s="16"/>
+      <c r="AJ35" s="16"/>
+      <c r="AK35" s="16"/>
+      <c r="AL35" s="16"/>
+      <c r="AM35" s="16"/>
+      <c r="AN35" s="16"/>
     </row>
     <row r="36" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="40"/>
-      <c r="B36" s="40"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="51"/>
-      <c r="Q36" s="51"/>
-      <c r="R36" s="51"/>
-      <c r="S36" s="51"/>
-      <c r="T36" s="51"/>
-      <c r="U36" s="51"/>
-      <c r="V36" s="51"/>
-      <c r="W36" s="51"/>
+      <c r="A36" s="61"/>
+      <c r="B36" s="61"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="61"/>
+      <c r="N36" s="61"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="49"/>
+      <c r="Q36" s="49"/>
+      <c r="R36" s="49"/>
+      <c r="S36" s="49"/>
+      <c r="T36" s="49"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="49"/>
+      <c r="W36" s="49"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="11"/>
       <c r="Z36" s="11"/>
@@ -2730,29 +2730,29 @@
       <c r="AN36" s="12"/>
     </row>
     <row r="37" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="40"/>
-      <c r="B37" s="40"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
-      <c r="N37" s="40"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="51"/>
-      <c r="Q37" s="51"/>
-      <c r="R37" s="51"/>
-      <c r="S37" s="51"/>
-      <c r="T37" s="51"/>
-      <c r="U37" s="51"/>
-      <c r="V37" s="51"/>
-      <c r="W37" s="51"/>
+      <c r="A37" s="61"/>
+      <c r="B37" s="61"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="61"/>
+      <c r="N37" s="61"/>
+      <c r="O37" s="61"/>
+      <c r="P37" s="49"/>
+      <c r="Q37" s="49"/>
+      <c r="R37" s="49"/>
+      <c r="S37" s="49"/>
+      <c r="T37" s="49"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="49"/>
+      <c r="W37" s="49"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="11"/>
       <c r="Z37" s="11"/>
@@ -2761,72 +2761,72 @@
       <c r="AC37" s="11"/>
       <c r="AE37" s="2"/>
       <c r="AF37" s="2"/>
-      <c r="AG37" s="60" t="s">
+      <c r="AG37" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="AH37" s="60"/>
-      <c r="AI37" s="60"/>
-      <c r="AJ37" s="60"/>
-      <c r="AK37" s="60"/>
-      <c r="AL37" s="60"/>
+      <c r="AH37" s="33"/>
+      <c r="AI37" s="33"/>
+      <c r="AJ37" s="33"/>
+      <c r="AK37" s="33"/>
+      <c r="AL37" s="33"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
     </row>
     <row r="38" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="47" t="s">
+      <c r="A38" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="13" t="s">
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13" t="s">
+      <c r="H38" s="17"/>
+      <c r="I38" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13" t="s">
+      <c r="J38" s="17"/>
+      <c r="K38" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13" t="s">
+      <c r="L38" s="17"/>
+      <c r="M38" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13" t="s">
+      <c r="N38" s="17"/>
+      <c r="O38" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="P38" s="13"/>
-      <c r="Q38" s="13" t="s">
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="R38" s="13"/>
-      <c r="S38" s="13" t="s">
+      <c r="R38" s="17"/>
+      <c r="S38" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="T38" s="13"/>
-      <c r="U38" s="13" t="s">
+      <c r="T38" s="17"/>
+      <c r="U38" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="V38" s="13"/>
-      <c r="W38" s="13" t="s">
+      <c r="V38" s="17"/>
+      <c r="W38" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="X38" s="13"/>
-      <c r="Y38" s="13" t="s">
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="Z38" s="13"/>
-      <c r="AA38" s="13" t="s">
+      <c r="Z38" s="17"/>
+      <c r="AA38" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="AB38" s="13"/>
-      <c r="AC38" s="47"/>
-      <c r="AD38" s="47"/>
+      <c r="AB38" s="17"/>
+      <c r="AC38" s="15"/>
+      <c r="AD38" s="15"/>
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
       <c r="AI38" s="3"/>
@@ -2837,61 +2837,61 @@
       <c r="AN38" s="3"/>
     </row>
     <row r="39" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="66" t="s">
+      <c r="A39" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="66"/>
-      <c r="C39" s="66"/>
-      <c r="D39" s="66"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="44">
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="19">
         <v>18</v>
       </c>
-      <c r="H39" s="44"/>
-      <c r="I39" s="44">
+      <c r="H39" s="19"/>
+      <c r="I39" s="19">
         <v>23</v>
       </c>
-      <c r="J39" s="44"/>
-      <c r="K39" s="44">
+      <c r="J39" s="19"/>
+      <c r="K39" s="19">
         <v>22</v>
       </c>
-      <c r="L39" s="44"/>
-      <c r="M39" s="44">
+      <c r="L39" s="19"/>
+      <c r="M39" s="19">
         <v>19</v>
       </c>
-      <c r="N39" s="44"/>
-      <c r="O39" s="44">
+      <c r="N39" s="19"/>
+      <c r="O39" s="19">
         <v>16</v>
       </c>
-      <c r="P39" s="44"/>
-      <c r="Q39" s="44">
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19">
         <v>22</v>
       </c>
-      <c r="R39" s="44"/>
-      <c r="S39" s="44">
+      <c r="R39" s="19"/>
+      <c r="S39" s="19">
         <v>22</v>
       </c>
-      <c r="T39" s="44"/>
-      <c r="U39" s="44">
+      <c r="T39" s="19"/>
+      <c r="U39" s="19">
         <v>20</v>
       </c>
-      <c r="V39" s="44"/>
-      <c r="W39" s="44">
+      <c r="V39" s="19"/>
+      <c r="W39" s="19">
         <v>22</v>
       </c>
-      <c r="X39" s="44"/>
-      <c r="Y39" s="44">
+      <c r="X39" s="19"/>
+      <c r="Y39" s="19">
         <v>16</v>
       </c>
-      <c r="Z39" s="72"/>
-      <c r="AA39" s="45">
+      <c r="Z39" s="21"/>
+      <c r="AA39" s="14">
         <f>SUM(G39:Z39)</f>
         <v>200</v>
       </c>
-      <c r="AB39" s="45"/>
-      <c r="AC39" s="14"/>
-      <c r="AD39" s="14"/>
+      <c r="AB39" s="14"/>
+      <c r="AC39" s="54"/>
+      <c r="AD39" s="54"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
@@ -2902,78 +2902,78 @@
       <c r="AN39" s="3"/>
     </row>
     <row r="40" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="44"/>
-      <c r="J40" s="44"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="67"/>
-      <c r="M40" s="44"/>
-      <c r="N40" s="44"/>
-      <c r="O40" s="44"/>
-      <c r="P40" s="44"/>
-      <c r="Q40" s="71"/>
-      <c r="R40" s="71"/>
-      <c r="S40" s="44"/>
-      <c r="T40" s="44"/>
-      <c r="U40" s="44"/>
-      <c r="V40" s="44"/>
-      <c r="W40" s="71"/>
-      <c r="X40" s="71"/>
-      <c r="Y40" s="67"/>
-      <c r="Z40" s="73"/>
-      <c r="AA40" s="70">
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="22"/>
+      <c r="Z40" s="23"/>
+      <c r="AA40" s="18">
         <f>SUM(G40:Z40)</f>
         <v>0</v>
       </c>
-      <c r="AB40" s="70"/>
-      <c r="AC40" s="14"/>
-      <c r="AD40" s="14"/>
+      <c r="AB40" s="18"/>
+      <c r="AC40" s="54"/>
+      <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="44"/>
-      <c r="J41" s="44"/>
-      <c r="K41" s="44"/>
-      <c r="L41" s="44"/>
-      <c r="M41" s="44"/>
-      <c r="N41" s="44"/>
-      <c r="O41" s="44"/>
-      <c r="P41" s="44"/>
-      <c r="Q41" s="44"/>
-      <c r="R41" s="44"/>
-      <c r="S41" s="44"/>
-      <c r="T41" s="44"/>
-      <c r="U41" s="44"/>
-      <c r="V41" s="44"/>
-      <c r="W41" s="44"/>
-      <c r="X41" s="44"/>
-      <c r="Y41" s="44"/>
-      <c r="Z41" s="72"/>
-      <c r="AA41" s="45">
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="19"/>
+      <c r="U41" s="19"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="19"/>
+      <c r="X41" s="19"/>
+      <c r="Y41" s="19"/>
+      <c r="Z41" s="21"/>
+      <c r="AA41" s="14">
         <f t="shared" ref="AA41" si="5">SUM(G41:Z41)</f>
         <v>0</v>
       </c>
-      <c r="AB41" s="45"/>
-      <c r="AC41" s="14"/>
-      <c r="AD41" s="14"/>
+      <c r="AB41" s="14"/>
+      <c r="AC41" s="54"/>
+      <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
@@ -3042,6 +3042,238 @@
     <row r="82" ht="12.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="256">
+    <mergeCell ref="Y38:Z38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="AC41:AD41"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:N2"/>
+    <mergeCell ref="Y24:AJ24"/>
+    <mergeCell ref="Y25:AM25"/>
+    <mergeCell ref="Y26:AM26"/>
+    <mergeCell ref="Y27:AM27"/>
+    <mergeCell ref="Y28:AM28"/>
+    <mergeCell ref="Y29:AM29"/>
+    <mergeCell ref="Y30:AM30"/>
+    <mergeCell ref="AD5:AI6"/>
+    <mergeCell ref="AJ5:AN6"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="N10:Q10"/>
+    <mergeCell ref="R10:U10"/>
+    <mergeCell ref="V10:Y10"/>
+    <mergeCell ref="Z10:AC10"/>
+    <mergeCell ref="AJ10:AN10"/>
+    <mergeCell ref="AJ12:AN12"/>
+    <mergeCell ref="AJ11:AN11"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="R17:U17"/>
+    <mergeCell ref="R18:U18"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="C20:M20"/>
+    <mergeCell ref="N21:AC21"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A32:O32"/>
+    <mergeCell ref="A33:O33"/>
+    <mergeCell ref="A34:O34"/>
+    <mergeCell ref="A35:O35"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="Z20:AC20"/>
+    <mergeCell ref="R20:U20"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="AC38:AD38"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="V35:W35"/>
+    <mergeCell ref="V36:W36"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N15:Q15"/>
+    <mergeCell ref="N16:Q16"/>
+    <mergeCell ref="N17:Q17"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="N12:Q12"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="E3:U3"/>
+    <mergeCell ref="Z3:AN3"/>
+    <mergeCell ref="U4:AG4"/>
+    <mergeCell ref="G4:P4"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="N5:AC5"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="V6:Y6"/>
+    <mergeCell ref="Z6:AC6"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="B16:M16"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="B15:M15"/>
+    <mergeCell ref="R15:U15"/>
+    <mergeCell ref="R16:U16"/>
+    <mergeCell ref="R12:U12"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="N8:Q8"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="N13:Q13"/>
+    <mergeCell ref="N14:Q14"/>
+    <mergeCell ref="V8:Y8"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="V11:Y11"/>
+    <mergeCell ref="V13:Y13"/>
+    <mergeCell ref="V14:Y14"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="R7:U7"/>
+    <mergeCell ref="R8:U8"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="R11:U11"/>
+    <mergeCell ref="R13:U13"/>
+    <mergeCell ref="R14:U14"/>
+    <mergeCell ref="Z13:AC13"/>
+    <mergeCell ref="Z14:AC14"/>
+    <mergeCell ref="Z15:AC15"/>
+    <mergeCell ref="Z16:AC16"/>
+    <mergeCell ref="Z17:AC17"/>
+    <mergeCell ref="V16:Y16"/>
+    <mergeCell ref="V17:Y17"/>
+    <mergeCell ref="V18:Y18"/>
+    <mergeCell ref="V19:Y19"/>
+    <mergeCell ref="AG37:AL37"/>
+    <mergeCell ref="V15:Y15"/>
+    <mergeCell ref="Z18:AC18"/>
+    <mergeCell ref="Z19:AC19"/>
+    <mergeCell ref="O1:AA1"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="AH4:AN4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="AJ7:AN7"/>
+    <mergeCell ref="AJ8:AN8"/>
+    <mergeCell ref="AJ9:AN9"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="R19:U19"/>
+    <mergeCell ref="Z12:AC12"/>
+    <mergeCell ref="V12:Y12"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="V20:Y20"/>
+    <mergeCell ref="Z7:AC7"/>
+    <mergeCell ref="Z8:AC8"/>
+    <mergeCell ref="Z9:AC9"/>
+    <mergeCell ref="Z11:AC11"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="AJ19:AN19"/>
+    <mergeCell ref="AJ20:AN20"/>
+    <mergeCell ref="AJ18:AN18"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AJ13:AN13"/>
+    <mergeCell ref="AJ14:AN14"/>
+    <mergeCell ref="AJ15:AN15"/>
+    <mergeCell ref="AJ16:AN16"/>
+    <mergeCell ref="AJ17:AN17"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AJ21:AN21"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="AD22:AI22"/>
     <mergeCell ref="AA41:AB41"/>
     <mergeCell ref="A38:F38"/>
@@ -3066,238 +3298,6 @@
     <mergeCell ref="K39:L39"/>
     <mergeCell ref="M39:N39"/>
     <mergeCell ref="M40:N40"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="AJ19:AN19"/>
-    <mergeCell ref="AJ20:AN20"/>
-    <mergeCell ref="AJ18:AN18"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AJ13:AN13"/>
-    <mergeCell ref="AJ14:AN14"/>
-    <mergeCell ref="AJ15:AN15"/>
-    <mergeCell ref="AJ16:AN16"/>
-    <mergeCell ref="AJ17:AN17"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AJ21:AN21"/>
-    <mergeCell ref="AG37:AL37"/>
-    <mergeCell ref="V15:Y15"/>
-    <mergeCell ref="Z18:AC18"/>
-    <mergeCell ref="Z19:AC19"/>
-    <mergeCell ref="O1:AA1"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="AH4:AN4"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="AJ7:AN7"/>
-    <mergeCell ref="AJ8:AN8"/>
-    <mergeCell ref="AJ9:AN9"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="R19:U19"/>
-    <mergeCell ref="Z12:AC12"/>
-    <mergeCell ref="V12:Y12"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="V20:Y20"/>
-    <mergeCell ref="Z7:AC7"/>
-    <mergeCell ref="Z8:AC8"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="Z11:AC11"/>
-    <mergeCell ref="Z13:AC13"/>
-    <mergeCell ref="Z14:AC14"/>
-    <mergeCell ref="Z15:AC15"/>
-    <mergeCell ref="Z16:AC16"/>
-    <mergeCell ref="Z17:AC17"/>
-    <mergeCell ref="V16:Y16"/>
-    <mergeCell ref="V17:Y17"/>
-    <mergeCell ref="V18:Y18"/>
-    <mergeCell ref="V19:Y19"/>
-    <mergeCell ref="V8:Y8"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="V11:Y11"/>
-    <mergeCell ref="V13:Y13"/>
-    <mergeCell ref="V14:Y14"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="R7:U7"/>
-    <mergeCell ref="R8:U8"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="R11:U11"/>
-    <mergeCell ref="R13:U13"/>
-    <mergeCell ref="R14:U14"/>
-    <mergeCell ref="R15:U15"/>
-    <mergeCell ref="R16:U16"/>
-    <mergeCell ref="R12:U12"/>
-    <mergeCell ref="N7:Q7"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="N13:Q13"/>
-    <mergeCell ref="N14:Q14"/>
-    <mergeCell ref="B16:M16"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="B15:M15"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N15:Q15"/>
-    <mergeCell ref="N16:Q16"/>
-    <mergeCell ref="N17:Q17"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="E3:U3"/>
-    <mergeCell ref="Z3:AN3"/>
-    <mergeCell ref="U4:AG4"/>
-    <mergeCell ref="G4:P4"/>
-    <mergeCell ref="A5:M6"/>
-    <mergeCell ref="N5:AC5"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="R6:U6"/>
-    <mergeCell ref="V6:Y6"/>
-    <mergeCell ref="Z6:AC6"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="V35:W35"/>
-    <mergeCell ref="V36:W36"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="N19:Q19"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="Z20:AC20"/>
-    <mergeCell ref="R20:U20"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="AC38:AD38"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A26:O26"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="C20:M20"/>
-    <mergeCell ref="N21:AC21"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="A33:O33"/>
-    <mergeCell ref="A34:O34"/>
-    <mergeCell ref="A35:O35"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="AC41:AD41"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:N2"/>
-    <mergeCell ref="Y24:AJ24"/>
-    <mergeCell ref="Y25:AM25"/>
-    <mergeCell ref="Y26:AM26"/>
-    <mergeCell ref="Y27:AM27"/>
-    <mergeCell ref="Y28:AM28"/>
-    <mergeCell ref="Y29:AM29"/>
-    <mergeCell ref="Y30:AM30"/>
-    <mergeCell ref="AD5:AI6"/>
-    <mergeCell ref="AJ5:AN6"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="N10:Q10"/>
-    <mergeCell ref="R10:U10"/>
-    <mergeCell ref="V10:Y10"/>
-    <mergeCell ref="Z10:AC10"/>
-    <mergeCell ref="AJ10:AN10"/>
-    <mergeCell ref="AJ12:AN12"/>
-    <mergeCell ref="AJ11:AN11"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="R17:U17"/>
-    <mergeCell ref="R18:U18"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="Y38:Z38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S38:T38"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="W38:X38"/>
   </mergeCells>
   <conditionalFormatting sqref="AD7:AI19">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">

--- a/public/files/report_card_templates/JHS.xlsx
+++ b/public/files/report_card_templates/JHS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\schoolsys\public\files\report_card_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A060D9D4-73A3-4513-B976-7AAB79F45556}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D62969-E561-4F18-A870-471DDECE887D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -504,188 +504,188 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1049,264 +1049,266 @@
   <dimension ref="A1:AN82"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="40" width="1.5703125" customWidth="1"/>
+    <col min="1" max="6" width="1.5703125" customWidth="1"/>
+    <col min="7" max="26" width="2.28515625" customWidth="1"/>
+    <col min="27" max="40" width="1.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O1" s="34" t="s">
+      <c r="O1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="34"/>
-      <c r="AA1" s="34"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="61"/>
+      <c r="Z1" s="61"/>
+      <c r="AA1" s="61"/>
     </row>
     <row r="2" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
-      <c r="Q2" s="35" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="Q2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
     </row>
     <row r="3" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45"/>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
-      <c r="V3" s="37" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="55"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="55"/>
+      <c r="V3" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="45"/>
-      <c r="AH3" s="45"/>
-      <c r="AI3" s="45"/>
-      <c r="AJ3" s="45"/>
-      <c r="AK3" s="45"/>
-      <c r="AL3" s="45"/>
-      <c r="AM3" s="45"/>
-      <c r="AN3" s="45"/>
+      <c r="W3" s="62"/>
+      <c r="X3" s="62"/>
+      <c r="Y3" s="62"/>
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="55"/>
+      <c r="AC3" s="55"/>
+      <c r="AD3" s="55"/>
+      <c r="AE3" s="55"/>
+      <c r="AF3" s="55"/>
+      <c r="AG3" s="55"/>
+      <c r="AH3" s="55"/>
+      <c r="AI3" s="55"/>
+      <c r="AJ3" s="55"/>
+      <c r="AK3" s="55"/>
+      <c r="AL3" s="55"/>
+      <c r="AM3" s="55"/>
+      <c r="AN3" s="55"/>
     </row>
     <row r="4" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="36" t="s">
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="46"/>
-      <c r="Y4" s="46"/>
-      <c r="Z4" s="46"/>
-      <c r="AA4" s="46"/>
-      <c r="AB4" s="46"/>
-      <c r="AC4" s="46"/>
-      <c r="AD4" s="46"/>
-      <c r="AE4" s="46"/>
-      <c r="AF4" s="46"/>
-      <c r="AG4" s="46"/>
-      <c r="AH4" s="36"/>
-      <c r="AI4" s="36"/>
-      <c r="AJ4" s="36"/>
-      <c r="AK4" s="36"/>
-      <c r="AL4" s="36"/>
-      <c r="AM4" s="36"/>
-      <c r="AN4" s="36"/>
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="59"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="56"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="56"/>
+      <c r="Y4" s="56"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="56"/>
+      <c r="AB4" s="56"/>
+      <c r="AC4" s="56"/>
+      <c r="AD4" s="56"/>
+      <c r="AE4" s="56"/>
+      <c r="AF4" s="56"/>
+      <c r="AG4" s="56"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="59"/>
+      <c r="AJ4" s="59"/>
+      <c r="AK4" s="59"/>
+      <c r="AL4" s="59"/>
+      <c r="AM4" s="59"/>
+      <c r="AN4" s="59"/>
     </row>
     <row r="5" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
-      <c r="T5" s="47"/>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="47"/>
-      <c r="Y5" s="47"/>
-      <c r="Z5" s="47"/>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="47"/>
-      <c r="AD5" s="67" t="s">
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="33"/>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="33"/>
+      <c r="AA5" s="33"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="33"/>
+      <c r="AD5" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="AE5" s="68"/>
-      <c r="AF5" s="68"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="69"/>
-      <c r="AJ5" s="67" t="s">
+      <c r="AE5" s="20"/>
+      <c r="AF5" s="20"/>
+      <c r="AG5" s="20"/>
+      <c r="AH5" s="20"/>
+      <c r="AI5" s="21"/>
+      <c r="AJ5" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="AK5" s="68"/>
-      <c r="AL5" s="68"/>
-      <c r="AM5" s="68"/>
-      <c r="AN5" s="69"/>
+      <c r="AK5" s="20"/>
+      <c r="AL5" s="20"/>
+      <c r="AM5" s="20"/>
+      <c r="AN5" s="21"/>
     </row>
     <row r="6" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="32" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="32"/>
-      <c r="R6" s="32" t="s">
+      <c r="O6" s="57"/>
+      <c r="P6" s="57"/>
+      <c r="Q6" s="57"/>
+      <c r="R6" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="S6" s="32"/>
-      <c r="T6" s="32"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="32" t="s">
+      <c r="S6" s="57"/>
+      <c r="T6" s="57"/>
+      <c r="U6" s="57"/>
+      <c r="V6" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="W6" s="32"/>
-      <c r="X6" s="32"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32" t="s">
+      <c r="W6" s="57"/>
+      <c r="X6" s="57"/>
+      <c r="Y6" s="57"/>
+      <c r="Z6" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="70"/>
-      <c r="AE6" s="71"/>
-      <c r="AF6" s="71"/>
-      <c r="AG6" s="71"/>
-      <c r="AH6" s="71"/>
-      <c r="AI6" s="72"/>
-      <c r="AJ6" s="70"/>
-      <c r="AK6" s="71"/>
-      <c r="AL6" s="71"/>
-      <c r="AM6" s="71"/>
-      <c r="AN6" s="72"/>
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="57"/>
+      <c r="AC6" s="57"/>
+      <c r="AD6" s="22"/>
+      <c r="AE6" s="23"/>
+      <c r="AF6" s="23"/>
+      <c r="AG6" s="23"/>
+      <c r="AH6" s="23"/>
+      <c r="AI6" s="24"/>
+      <c r="AJ6" s="22"/>
+      <c r="AK6" s="23"/>
+      <c r="AL6" s="23"/>
+      <c r="AM6" s="23"/>
+      <c r="AN6" s="24"/>
     </row>
     <row r="7" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
       <c r="N7" s="28"/>
       <c r="O7" s="28"/>
       <c r="P7" s="28"/>
@@ -1323,15 +1325,15 @@
       <c r="AA7" s="28"/>
       <c r="AB7" s="28"/>
       <c r="AC7" s="28"/>
-      <c r="AD7" s="25" t="str">
+      <c r="AD7" s="29" t="str">
         <f>IF(COUNT(N7:AC7)=4,SUM(N7:AC7)/4,"")</f>
         <v/>
       </c>
-      <c r="AE7" s="26"/>
-      <c r="AF7" s="26"/>
-      <c r="AG7" s="26"/>
-      <c r="AH7" s="26"/>
-      <c r="AI7" s="27"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AH7" s="30"/>
+      <c r="AI7" s="31"/>
       <c r="AJ7" s="28" t="str">
         <f>IF(AD7&lt;&gt;"",IF(AD7&gt;=75,"Passed","Failed"),"")</f>
         <v/>
@@ -1342,21 +1344,21 @@
       <c r="AN7" s="28"/>
     </row>
     <row r="8" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="41"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
       <c r="N8" s="28"/>
       <c r="O8" s="28"/>
       <c r="P8" s="28"/>
@@ -1373,15 +1375,15 @@
       <c r="AA8" s="28"/>
       <c r="AB8" s="28"/>
       <c r="AC8" s="28"/>
-      <c r="AD8" s="25" t="str">
+      <c r="AD8" s="29" t="str">
         <f t="shared" ref="AD8:AD19" si="0">IF(COUNT(N8:AC8)=4,SUM(N8:AC8)/4,"")</f>
         <v/>
       </c>
-      <c r="AE8" s="26"/>
-      <c r="AF8" s="26"/>
-      <c r="AG8" s="26"/>
-      <c r="AH8" s="26"/>
-      <c r="AI8" s="27"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="30"/>
+      <c r="AH8" s="30"/>
+      <c r="AI8" s="31"/>
       <c r="AJ8" s="28" t="str">
         <f t="shared" ref="AJ8:AJ19" si="1">IF(AD8&lt;&gt;"",IF(AD8&gt;=75,"Passed","Failed"),"")</f>
         <v/>
@@ -1392,21 +1394,21 @@
       <c r="AN8" s="28"/>
     </row>
     <row r="9" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
       <c r="N9" s="28"/>
       <c r="O9" s="28"/>
       <c r="P9" s="28"/>
@@ -1423,15 +1425,15 @@
       <c r="AA9" s="28"/>
       <c r="AB9" s="28"/>
       <c r="AC9" s="28"/>
-      <c r="AD9" s="25" t="str">
+      <c r="AD9" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE9" s="26"/>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="26"/>
-      <c r="AH9" s="26"/>
-      <c r="AI9" s="27"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="31"/>
       <c r="AJ9" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1442,21 +1444,21 @@
       <c r="AN9" s="28"/>
     </row>
     <row r="10" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="40"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="27"/>
       <c r="N10" s="28"/>
       <c r="O10" s="28"/>
       <c r="P10" s="28"/>
@@ -1473,15 +1475,15 @@
       <c r="AA10" s="28"/>
       <c r="AB10" s="28"/>
       <c r="AC10" s="28"/>
-      <c r="AD10" s="25" t="str">
+      <c r="AD10" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE10" s="26"/>
-      <c r="AF10" s="26"/>
-      <c r="AG10" s="26"/>
-      <c r="AH10" s="26"/>
-      <c r="AI10" s="27"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="30"/>
+      <c r="AG10" s="30"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="31"/>
       <c r="AJ10" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1492,21 +1494,21 @@
       <c r="AN10" s="28"/>
     </row>
     <row r="11" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="49"/>
       <c r="N11" s="28"/>
       <c r="O11" s="28"/>
       <c r="P11" s="28"/>
@@ -1523,15 +1525,15 @@
       <c r="AA11" s="28"/>
       <c r="AB11" s="28"/>
       <c r="AC11" s="28"/>
-      <c r="AD11" s="25" t="str">
+      <c r="AD11" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE11" s="26"/>
-      <c r="AF11" s="26"/>
-      <c r="AG11" s="26"/>
-      <c r="AH11" s="26"/>
-      <c r="AI11" s="27"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="30"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="31"/>
       <c r="AJ11" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1542,21 +1544,21 @@
       <c r="AN11" s="28"/>
     </row>
     <row r="12" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="44"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="54"/>
       <c r="N12" s="28"/>
       <c r="O12" s="28"/>
       <c r="P12" s="28"/>
@@ -1573,15 +1575,15 @@
       <c r="AA12" s="28"/>
       <c r="AB12" s="28"/>
       <c r="AC12" s="28"/>
-      <c r="AD12" s="25" t="str">
+      <c r="AD12" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE12" s="26"/>
-      <c r="AF12" s="26"/>
-      <c r="AG12" s="26"/>
-      <c r="AH12" s="26"/>
-      <c r="AI12" s="27"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="30"/>
+      <c r="AG12" s="30"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="31"/>
       <c r="AJ12" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1592,21 +1594,21 @@
       <c r="AN12" s="28"/>
     </row>
     <row r="13" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
       <c r="N13" s="28"/>
       <c r="O13" s="28"/>
       <c r="P13" s="28"/>
@@ -1623,15 +1625,15 @@
       <c r="AA13" s="28"/>
       <c r="AB13" s="28"/>
       <c r="AC13" s="28"/>
-      <c r="AD13" s="25" t="str">
+      <c r="AD13" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE13" s="26"/>
-      <c r="AF13" s="26"/>
-      <c r="AG13" s="26"/>
-      <c r="AH13" s="26"/>
-      <c r="AI13" s="27"/>
+      <c r="AE13" s="30"/>
+      <c r="AF13" s="30"/>
+      <c r="AG13" s="30"/>
+      <c r="AH13" s="30"/>
+      <c r="AI13" s="31"/>
       <c r="AJ13" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1643,20 +1645,20 @@
     </row>
     <row r="14" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="40"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="27"/>
       <c r="N14" s="28"/>
       <c r="O14" s="28"/>
       <c r="P14" s="28"/>
@@ -1673,15 +1675,15 @@
       <c r="AA14" s="28"/>
       <c r="AB14" s="28"/>
       <c r="AC14" s="28"/>
-      <c r="AD14" s="25" t="str">
+      <c r="AD14" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE14" s="26"/>
-      <c r="AF14" s="26"/>
-      <c r="AG14" s="26"/>
-      <c r="AH14" s="26"/>
-      <c r="AI14" s="27"/>
+      <c r="AE14" s="30"/>
+      <c r="AF14" s="30"/>
+      <c r="AG14" s="30"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="31"/>
       <c r="AJ14" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1693,20 +1695,20 @@
     </row>
     <row r="15" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="40"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="27"/>
       <c r="N15" s="28"/>
       <c r="O15" s="28"/>
       <c r="P15" s="28"/>
@@ -1723,15 +1725,15 @@
       <c r="AA15" s="28"/>
       <c r="AB15" s="28"/>
       <c r="AC15" s="28"/>
-      <c r="AD15" s="25" t="str">
+      <c r="AD15" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE15" s="26"/>
-      <c r="AF15" s="26"/>
-      <c r="AG15" s="26"/>
-      <c r="AH15" s="26"/>
-      <c r="AI15" s="27"/>
+      <c r="AE15" s="30"/>
+      <c r="AF15" s="30"/>
+      <c r="AG15" s="30"/>
+      <c r="AH15" s="30"/>
+      <c r="AI15" s="31"/>
       <c r="AJ15" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1743,20 +1745,20 @@
     </row>
     <row r="16" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="40"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="27"/>
       <c r="N16" s="28"/>
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
@@ -1773,15 +1775,15 @@
       <c r="AA16" s="28"/>
       <c r="AB16" s="28"/>
       <c r="AC16" s="28"/>
-      <c r="AD16" s="25" t="str">
+      <c r="AD16" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE16" s="26"/>
-      <c r="AF16" s="26"/>
-      <c r="AG16" s="26"/>
-      <c r="AH16" s="26"/>
-      <c r="AI16" s="27"/>
+      <c r="AE16" s="30"/>
+      <c r="AF16" s="30"/>
+      <c r="AG16" s="30"/>
+      <c r="AH16" s="30"/>
+      <c r="AI16" s="31"/>
       <c r="AJ16" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1793,20 +1795,20 @@
     </row>
     <row r="17" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="40"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="26"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="27"/>
       <c r="N17" s="28"/>
       <c r="O17" s="28"/>
       <c r="P17" s="28"/>
@@ -1823,15 +1825,15 @@
       <c r="AA17" s="28"/>
       <c r="AB17" s="28"/>
       <c r="AC17" s="28"/>
-      <c r="AD17" s="25" t="str">
+      <c r="AD17" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE17" s="26"/>
-      <c r="AF17" s="26"/>
-      <c r="AG17" s="26"/>
-      <c r="AH17" s="26"/>
-      <c r="AI17" s="27"/>
+      <c r="AE17" s="30"/>
+      <c r="AF17" s="30"/>
+      <c r="AG17" s="30"/>
+      <c r="AH17" s="30"/>
+      <c r="AI17" s="31"/>
       <c r="AJ17" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1842,21 +1844,21 @@
       <c r="AN17" s="28"/>
     </row>
     <row r="18" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="49"/>
       <c r="N18" s="28"/>
       <c r="O18" s="28"/>
       <c r="P18" s="28"/>
@@ -1873,15 +1875,15 @@
       <c r="AA18" s="28"/>
       <c r="AB18" s="28"/>
       <c r="AC18" s="28"/>
-      <c r="AD18" s="25" t="str">
+      <c r="AD18" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE18" s="26"/>
-      <c r="AF18" s="26"/>
-      <c r="AG18" s="26"/>
-      <c r="AH18" s="26"/>
-      <c r="AI18" s="27"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="30"/>
+      <c r="AH18" s="30"/>
+      <c r="AI18" s="31"/>
       <c r="AJ18" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1892,21 +1894,21 @@
       <c r="AN18" s="28"/>
     </row>
     <row r="19" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
       <c r="N19" s="28"/>
       <c r="O19" s="28"/>
       <c r="P19" s="28"/>
@@ -1923,15 +1925,15 @@
       <c r="AA19" s="28"/>
       <c r="AB19" s="28"/>
       <c r="AC19" s="28"/>
-      <c r="AD19" s="25" t="str">
+      <c r="AD19" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE19" s="26"/>
-      <c r="AF19" s="26"/>
-      <c r="AG19" s="26"/>
-      <c r="AH19" s="26"/>
-      <c r="AI19" s="27"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="30"/>
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="31"/>
       <c r="AJ19" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1944,53 +1946,53 @@
     <row r="20" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="57"/>
-      <c r="K20" s="57"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="38" t="str">
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="46" t="str">
         <f>IF(SUM(N7:Q13,N18)/8 &gt; 0, SUM(N7:Q13,N18)/8, "")</f>
         <v/>
       </c>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-      <c r="Q20" s="38"/>
-      <c r="R20" s="38" t="str">
+      <c r="O20" s="46"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="46" t="str">
         <f t="shared" ref="R20" si="2">IF(SUM(R7:U13,R18)/8 &gt; 0, SUM(R7:U13,R18)/8, "")</f>
         <v/>
       </c>
-      <c r="S20" s="38"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="38"/>
-      <c r="V20" s="38" t="str">
+      <c r="S20" s="46"/>
+      <c r="T20" s="46"/>
+      <c r="U20" s="46"/>
+      <c r="V20" s="46" t="str">
         <f t="shared" ref="V20" si="3">IF(SUM(V7:Y13,V18)/8 &gt; 0, SUM(V7:Y13,V18)/8, "")</f>
         <v/>
       </c>
-      <c r="W20" s="38"/>
-      <c r="X20" s="38"/>
-      <c r="Y20" s="38"/>
-      <c r="Z20" s="38" t="str">
+      <c r="W20" s="46"/>
+      <c r="X20" s="46"/>
+      <c r="Y20" s="46"/>
+      <c r="Z20" s="46" t="str">
         <f t="shared" ref="Z20" si="4">IF(SUM(Z7:AC13,Z18)/8 &gt; 0, SUM(Z7:AC13,Z18)/8, "")</f>
         <v/>
       </c>
-      <c r="AA20" s="38"/>
-      <c r="AB20" s="38"/>
-      <c r="AC20" s="38"/>
-      <c r="AD20" s="25"/>
-      <c r="AE20" s="26"/>
-      <c r="AF20" s="26"/>
-      <c r="AG20" s="26"/>
-      <c r="AH20" s="26"/>
-      <c r="AI20" s="27"/>
+      <c r="AA20" s="46"/>
+      <c r="AB20" s="46"/>
+      <c r="AC20" s="46"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
+      <c r="AG20" s="30"/>
+      <c r="AH20" s="30"/>
+      <c r="AI20" s="31"/>
       <c r="AJ20" s="28"/>
       <c r="AK20" s="28"/>
       <c r="AL20" s="28"/>
@@ -2000,51 +2002,51 @@
     <row r="21" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="51" t="s">
+      <c r="C21" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-      <c r="L21" s="51"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="58" t="s">
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="O21" s="59"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="59"/>
-      <c r="R21" s="59"/>
-      <c r="S21" s="59"/>
-      <c r="T21" s="59"/>
-      <c r="U21" s="59"/>
-      <c r="V21" s="59"/>
-      <c r="W21" s="59"/>
-      <c r="X21" s="59"/>
-      <c r="Y21" s="59"/>
-      <c r="Z21" s="59"/>
-      <c r="AA21" s="59"/>
-      <c r="AB21" s="59"/>
-      <c r="AC21" s="60"/>
-      <c r="AD21" s="29" t="str">
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="38"/>
+      <c r="V21" s="38"/>
+      <c r="W21" s="38"/>
+      <c r="X21" s="38"/>
+      <c r="Y21" s="38"/>
+      <c r="Z21" s="38"/>
+      <c r="AA21" s="38"/>
+      <c r="AB21" s="38"/>
+      <c r="AC21" s="39"/>
+      <c r="AD21" s="63" t="str">
         <f>IF(COUNT(AD7:AI13,AD18)=8,SUM(AD7:AI13,AD18)/8,"")</f>
         <v/>
       </c>
-      <c r="AE21" s="30"/>
-      <c r="AF21" s="30"/>
-      <c r="AG21" s="30"/>
-      <c r="AH21" s="30"/>
-      <c r="AI21" s="31"/>
-      <c r="AJ21" s="32"/>
-      <c r="AK21" s="32"/>
-      <c r="AL21" s="32"/>
-      <c r="AM21" s="32"/>
-      <c r="AN21" s="32"/>
+      <c r="AE21" s="64"/>
+      <c r="AF21" s="64"/>
+      <c r="AG21" s="64"/>
+      <c r="AH21" s="64"/>
+      <c r="AI21" s="65"/>
+      <c r="AJ21" s="57"/>
+      <c r="AK21" s="57"/>
+      <c r="AL21" s="57"/>
+      <c r="AM21" s="57"/>
+      <c r="AN21" s="57"/>
     </row>
     <row r="22" spans="1:40" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
@@ -2076,12 +2078,12 @@
       <c r="AA22" s="10"/>
       <c r="AB22" s="10"/>
       <c r="AC22" s="10"/>
-      <c r="AD22" s="13"/>
-      <c r="AE22" s="13"/>
-      <c r="AF22" s="13"/>
-      <c r="AG22" s="13"/>
-      <c r="AH22" s="13"/>
-      <c r="AI22" s="13"/>
+      <c r="AD22" s="67"/>
+      <c r="AE22" s="67"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="67"/>
+      <c r="AH22" s="67"/>
+      <c r="AI22" s="67"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
@@ -2118,367 +2120,367 @@
       <c r="Y23" s="2"/>
     </row>
     <row r="24" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
+      <c r="A24" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="47"/>
-      <c r="P24" s="55" t="s">
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55" t="s">
+      <c r="Q24" s="34"/>
+      <c r="R24" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="S24" s="55"/>
-      <c r="T24" s="55" t="s">
+      <c r="S24" s="34"/>
+      <c r="T24" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="U24" s="55"/>
-      <c r="V24" s="55" t="s">
+      <c r="U24" s="34"/>
+      <c r="V24" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="W24" s="55"/>
-      <c r="Y24" s="65" t="s">
+      <c r="W24" s="34"/>
+      <c r="Y24" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="Z24" s="65"/>
-      <c r="AA24" s="65"/>
-      <c r="AB24" s="65"/>
-      <c r="AC24" s="65"/>
-      <c r="AD24" s="65"/>
-      <c r="AE24" s="65"/>
-      <c r="AF24" s="65"/>
-      <c r="AG24" s="65"/>
-      <c r="AH24" s="65"/>
-      <c r="AI24" s="65"/>
-      <c r="AJ24" s="65"/>
+      <c r="Z24" s="17"/>
+      <c r="AA24" s="17"/>
+      <c r="AB24" s="17"/>
+      <c r="AC24" s="17"/>
+      <c r="AD24" s="17"/>
+      <c r="AE24" s="17"/>
+      <c r="AF24" s="17"/>
+      <c r="AG24" s="17"/>
+      <c r="AH24" s="17"/>
+      <c r="AI24" s="17"/>
+      <c r="AJ24" s="17"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
       <c r="AN24" s="3"/>
     </row>
     <row r="25" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="53"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="53"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="19"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="Y25" s="66" t="s">
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="41"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="44"/>
+      <c r="S25" s="44"/>
+      <c r="T25" s="44"/>
+      <c r="U25" s="44"/>
+      <c r="V25" s="45"/>
+      <c r="W25" s="45"/>
+      <c r="Y25" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="Z25" s="66"/>
-      <c r="AA25" s="66"/>
-      <c r="AB25" s="66"/>
-      <c r="AC25" s="66"/>
-      <c r="AD25" s="66"/>
-      <c r="AE25" s="66"/>
-      <c r="AF25" s="66"/>
-      <c r="AG25" s="66"/>
-      <c r="AH25" s="66"/>
-      <c r="AI25" s="66"/>
-      <c r="AJ25" s="66"/>
-      <c r="AK25" s="66"/>
-      <c r="AL25" s="66"/>
-      <c r="AM25" s="66"/>
+      <c r="Z25" s="18"/>
+      <c r="AA25" s="18"/>
+      <c r="AB25" s="18"/>
+      <c r="AC25" s="18"/>
+      <c r="AD25" s="18"/>
+      <c r="AE25" s="18"/>
+      <c r="AF25" s="18"/>
+      <c r="AG25" s="18"/>
+      <c r="AH25" s="18"/>
+      <c r="AI25" s="18"/>
+      <c r="AJ25" s="18"/>
+      <c r="AK25" s="18"/>
+      <c r="AL25" s="18"/>
+      <c r="AM25" s="18"/>
       <c r="AN25" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="53"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="Y26" s="66" t="s">
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="41"/>
+      <c r="K26" s="41"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="41"/>
+      <c r="P26" s="44"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="45"/>
+      <c r="S26" s="45"/>
+      <c r="T26" s="45"/>
+      <c r="U26" s="45"/>
+      <c r="V26" s="45"/>
+      <c r="W26" s="45"/>
+      <c r="Y26" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="Z26" s="66"/>
-      <c r="AA26" s="66"/>
-      <c r="AB26" s="66"/>
-      <c r="AC26" s="66"/>
-      <c r="AD26" s="66"/>
-      <c r="AE26" s="66"/>
-      <c r="AF26" s="66"/>
-      <c r="AG26" s="66"/>
-      <c r="AH26" s="66"/>
-      <c r="AI26" s="66"/>
-      <c r="AJ26" s="66"/>
-      <c r="AK26" s="66"/>
-      <c r="AL26" s="66"/>
-      <c r="AM26" s="66"/>
+      <c r="Z26" s="18"/>
+      <c r="AA26" s="18"/>
+      <c r="AB26" s="18"/>
+      <c r="AC26" s="18"/>
+      <c r="AD26" s="18"/>
+      <c r="AE26" s="18"/>
+      <c r="AF26" s="18"/>
+      <c r="AG26" s="18"/>
+      <c r="AH26" s="18"/>
+      <c r="AI26" s="18"/>
+      <c r="AJ26" s="18"/>
+      <c r="AK26" s="18"/>
+      <c r="AL26" s="18"/>
+      <c r="AM26" s="18"/>
       <c r="AN26" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="53"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="53"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
-      <c r="W27" s="14"/>
-      <c r="Y27" s="66" t="s">
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="44"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" s="45"/>
+      <c r="S27" s="45"/>
+      <c r="T27" s="45"/>
+      <c r="U27" s="45"/>
+      <c r="V27" s="45"/>
+      <c r="W27" s="45"/>
+      <c r="Y27" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="Z27" s="66"/>
-      <c r="AA27" s="66"/>
-      <c r="AB27" s="66"/>
-      <c r="AC27" s="66"/>
-      <c r="AD27" s="66"/>
-      <c r="AE27" s="66"/>
-      <c r="AF27" s="66"/>
-      <c r="AG27" s="66"/>
-      <c r="AH27" s="66"/>
-      <c r="AI27" s="66"/>
-      <c r="AJ27" s="66"/>
-      <c r="AK27" s="66"/>
-      <c r="AL27" s="66"/>
-      <c r="AM27" s="66"/>
+      <c r="Z27" s="18"/>
+      <c r="AA27" s="18"/>
+      <c r="AB27" s="18"/>
+      <c r="AC27" s="18"/>
+      <c r="AD27" s="18"/>
+      <c r="AE27" s="18"/>
+      <c r="AF27" s="18"/>
+      <c r="AG27" s="18"/>
+      <c r="AH27" s="18"/>
+      <c r="AI27" s="18"/>
+      <c r="AJ27" s="18"/>
+      <c r="AK27" s="18"/>
+      <c r="AL27" s="18"/>
+      <c r="AM27" s="18"/>
       <c r="AN27" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="53" t="s">
+      <c r="A28" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="53"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="53"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="14"/>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
-      <c r="Y28" s="66" t="s">
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="44"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="45"/>
+      <c r="U28" s="45"/>
+      <c r="V28" s="45"/>
+      <c r="W28" s="45"/>
+      <c r="Y28" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="Z28" s="66"/>
-      <c r="AA28" s="66"/>
-      <c r="AB28" s="66"/>
-      <c r="AC28" s="66"/>
-      <c r="AD28" s="66"/>
-      <c r="AE28" s="66"/>
-      <c r="AF28" s="66"/>
-      <c r="AG28" s="66"/>
-      <c r="AH28" s="66"/>
-      <c r="AI28" s="66"/>
-      <c r="AJ28" s="66"/>
-      <c r="AK28" s="66"/>
-      <c r="AL28" s="66"/>
-      <c r="AM28" s="66"/>
+      <c r="Z28" s="18"/>
+      <c r="AA28" s="18"/>
+      <c r="AB28" s="18"/>
+      <c r="AC28" s="18"/>
+      <c r="AD28" s="18"/>
+      <c r="AE28" s="18"/>
+      <c r="AF28" s="18"/>
+      <c r="AG28" s="18"/>
+      <c r="AH28" s="18"/>
+      <c r="AI28" s="18"/>
+      <c r="AJ28" s="18"/>
+      <c r="AK28" s="18"/>
+      <c r="AL28" s="18"/>
+      <c r="AM28" s="18"/>
       <c r="AN28" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="53" t="s">
+      <c r="A29" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="53"/>
-      <c r="C29" s="53"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="53"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="53"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="53"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="53"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
-      <c r="Y29" s="66" t="s">
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="44"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="45"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="45"/>
+      <c r="U29" s="45"/>
+      <c r="V29" s="45"/>
+      <c r="W29" s="45"/>
+      <c r="Y29" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="Z29" s="66"/>
-      <c r="AA29" s="66"/>
-      <c r="AB29" s="66"/>
-      <c r="AC29" s="66"/>
-      <c r="AD29" s="66"/>
-      <c r="AE29" s="66"/>
-      <c r="AF29" s="66"/>
-      <c r="AG29" s="66"/>
-      <c r="AH29" s="66"/>
-      <c r="AI29" s="66"/>
-      <c r="AJ29" s="66"/>
-      <c r="AK29" s="66"/>
-      <c r="AL29" s="66"/>
-      <c r="AM29" s="66"/>
+      <c r="Z29" s="18"/>
+      <c r="AA29" s="18"/>
+      <c r="AB29" s="18"/>
+      <c r="AC29" s="18"/>
+      <c r="AD29" s="18"/>
+      <c r="AE29" s="18"/>
+      <c r="AF29" s="18"/>
+      <c r="AG29" s="18"/>
+      <c r="AH29" s="18"/>
+      <c r="AI29" s="18"/>
+      <c r="AJ29" s="18"/>
+      <c r="AK29" s="18"/>
+      <c r="AL29" s="18"/>
+      <c r="AM29" s="18"/>
       <c r="AN29" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="53" t="s">
+      <c r="A30" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="53"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="53"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="53"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
-      <c r="W30" s="14"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="41"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="44"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="45"/>
+      <c r="S30" s="45"/>
+      <c r="T30" s="45"/>
+      <c r="U30" s="45"/>
+      <c r="V30" s="45"/>
+      <c r="W30" s="45"/>
       <c r="X30" s="3"/>
-      <c r="Y30" s="66" t="s">
+      <c r="Y30" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="Z30" s="66"/>
-      <c r="AA30" s="66"/>
-      <c r="AB30" s="66"/>
-      <c r="AC30" s="66"/>
-      <c r="AD30" s="66"/>
-      <c r="AE30" s="66"/>
-      <c r="AF30" s="66"/>
-      <c r="AG30" s="66"/>
-      <c r="AH30" s="66"/>
-      <c r="AI30" s="66"/>
-      <c r="AJ30" s="66"/>
-      <c r="AK30" s="66"/>
-      <c r="AL30" s="66"/>
-      <c r="AM30" s="66"/>
+      <c r="Z30" s="18"/>
+      <c r="AA30" s="18"/>
+      <c r="AB30" s="18"/>
+      <c r="AC30" s="18"/>
+      <c r="AD30" s="18"/>
+      <c r="AE30" s="18"/>
+      <c r="AF30" s="18"/>
+      <c r="AG30" s="18"/>
+      <c r="AH30" s="18"/>
+      <c r="AI30" s="18"/>
+      <c r="AJ30" s="18"/>
+      <c r="AK30" s="18"/>
+      <c r="AL30" s="18"/>
+      <c r="AM30" s="18"/>
       <c r="AN30" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="53" t="s">
+      <c r="A31" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="53"/>
-      <c r="K31" s="53"/>
-      <c r="L31" s="53"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="53"/>
-      <c r="O31" s="53"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14"/>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="41"/>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="44"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="45"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="45"/>
+      <c r="U31" s="45"/>
+      <c r="V31" s="45"/>
+      <c r="W31" s="45"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="8"/>
       <c r="Z31" s="8"/>
@@ -2498,31 +2500,31 @@
       <c r="AN31" s="3"/>
     </row>
     <row r="32" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="62" t="s">
+      <c r="A32" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="62"/>
-      <c r="C32" s="62"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="62"/>
-      <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
-      <c r="K32" s="62"/>
-      <c r="L32" s="62"/>
-      <c r="M32" s="62"/>
-      <c r="N32" s="62"/>
-      <c r="O32" s="62"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
-      <c r="V32" s="14"/>
-      <c r="W32" s="14"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="44"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="45"/>
+      <c r="S32" s="45"/>
+      <c r="T32" s="45"/>
+      <c r="U32" s="45"/>
+      <c r="V32" s="45"/>
+      <c r="W32" s="45"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="11"/>
       <c r="Z32" s="11"/>
@@ -2542,31 +2544,31 @@
       <c r="AN32" s="3"/>
     </row>
     <row r="33" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="53" t="s">
+      <c r="A33" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="53"/>
-      <c r="O33" s="53"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="41"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="44"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="45"/>
+      <c r="S33" s="45"/>
+      <c r="T33" s="45"/>
+      <c r="U33" s="45"/>
+      <c r="V33" s="45"/>
+      <c r="W33" s="45"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="11"/>
       <c r="Z33" s="11"/>
@@ -2586,31 +2588,31 @@
       <c r="AN33" s="3"/>
     </row>
     <row r="34" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="53"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="14"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="14"/>
-      <c r="V34" s="14"/>
-      <c r="W34" s="14"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="44"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="45"/>
+      <c r="S34" s="45"/>
+      <c r="T34" s="45"/>
+      <c r="U34" s="45"/>
+      <c r="V34" s="45"/>
+      <c r="W34" s="45"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="11"/>
       <c r="Z34" s="11"/>
@@ -2630,85 +2632,85 @@
       <c r="AN34" s="3"/>
     </row>
     <row r="35" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="63" t="s">
+      <c r="A35" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="63"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="63"/>
-      <c r="E35" s="63"/>
-      <c r="F35" s="63"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="63"/>
-      <c r="J35" s="63"/>
-      <c r="K35" s="63"/>
-      <c r="L35" s="63"/>
-      <c r="M35" s="63"/>
-      <c r="N35" s="63"/>
-      <c r="O35" s="63"/>
-      <c r="P35" s="14">
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="43"/>
+      <c r="M35" s="43"/>
+      <c r="N35" s="43"/>
+      <c r="O35" s="43"/>
+      <c r="P35" s="45">
         <f>SUM(P25:Q34)/10</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="14"/>
-      <c r="R35" s="14">
+      <c r="Q35" s="45"/>
+      <c r="R35" s="45">
         <f>SUM(R25:S34)/10</f>
         <v>0</v>
       </c>
-      <c r="S35" s="14"/>
-      <c r="T35" s="14">
+      <c r="S35" s="45"/>
+      <c r="T35" s="45">
         <f>SUM(T25:U34)/10</f>
         <v>0</v>
       </c>
-      <c r="U35" s="14"/>
-      <c r="V35" s="14">
+      <c r="U35" s="45"/>
+      <c r="V35" s="45">
         <f>SUM(V25:W34)/10</f>
         <v>0</v>
       </c>
-      <c r="W35" s="14"/>
+      <c r="W35" s="45"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="11"/>
       <c r="Z35" s="11"/>
       <c r="AA35" s="11"/>
       <c r="AB35" s="11"/>
       <c r="AC35" s="11"/>
-      <c r="AD35" s="16"/>
-      <c r="AE35" s="16"/>
-      <c r="AF35" s="16"/>
-      <c r="AG35" s="16"/>
-      <c r="AH35" s="16"/>
-      <c r="AI35" s="16"/>
-      <c r="AJ35" s="16"/>
-      <c r="AK35" s="16"/>
-      <c r="AL35" s="16"/>
-      <c r="AM35" s="16"/>
-      <c r="AN35" s="16"/>
+      <c r="AD35" s="68"/>
+      <c r="AE35" s="68"/>
+      <c r="AF35" s="68"/>
+      <c r="AG35" s="68"/>
+      <c r="AH35" s="68"/>
+      <c r="AI35" s="68"/>
+      <c r="AJ35" s="68"/>
+      <c r="AK35" s="68"/>
+      <c r="AL35" s="68"/>
+      <c r="AM35" s="68"/>
+      <c r="AN35" s="68"/>
     </row>
     <row r="36" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="61"/>
-      <c r="B36" s="61"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
-      <c r="J36" s="61"/>
-      <c r="K36" s="61"/>
-      <c r="L36" s="61"/>
-      <c r="M36" s="61"/>
-      <c r="N36" s="61"/>
-      <c r="O36" s="61"/>
-      <c r="P36" s="49"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="49"/>
-      <c r="S36" s="49"/>
-      <c r="T36" s="49"/>
-      <c r="U36" s="49"/>
-      <c r="V36" s="49"/>
-      <c r="W36" s="49"/>
+      <c r="A36" s="40"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="40"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="40"/>
+      <c r="M36" s="40"/>
+      <c r="N36" s="40"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="51"/>
+      <c r="Q36" s="51"/>
+      <c r="R36" s="51"/>
+      <c r="S36" s="51"/>
+      <c r="T36" s="51"/>
+      <c r="U36" s="51"/>
+      <c r="V36" s="51"/>
+      <c r="W36" s="51"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="11"/>
       <c r="Z36" s="11"/>
@@ -2730,29 +2732,29 @@
       <c r="AN36" s="12"/>
     </row>
     <row r="37" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="61"/>
-      <c r="B37" s="61"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61"/>
-      <c r="J37" s="61"/>
-      <c r="K37" s="61"/>
-      <c r="L37" s="61"/>
-      <c r="M37" s="61"/>
-      <c r="N37" s="61"/>
-      <c r="O37" s="61"/>
-      <c r="P37" s="49"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="49"/>
-      <c r="S37" s="49"/>
-      <c r="T37" s="49"/>
-      <c r="U37" s="49"/>
-      <c r="V37" s="49"/>
-      <c r="W37" s="49"/>
+      <c r="A37" s="40"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="40"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="40"/>
+      <c r="M37" s="40"/>
+      <c r="N37" s="40"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="51"/>
+      <c r="Q37" s="51"/>
+      <c r="R37" s="51"/>
+      <c r="S37" s="51"/>
+      <c r="T37" s="51"/>
+      <c r="U37" s="51"/>
+      <c r="V37" s="51"/>
+      <c r="W37" s="51"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="11"/>
       <c r="Z37" s="11"/>
@@ -2761,72 +2763,72 @@
       <c r="AC37" s="11"/>
       <c r="AE37" s="2"/>
       <c r="AF37" s="2"/>
-      <c r="AG37" s="33" t="s">
+      <c r="AG37" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="AH37" s="33"/>
-      <c r="AI37" s="33"/>
-      <c r="AJ37" s="33"/>
-      <c r="AK37" s="33"/>
-      <c r="AL37" s="33"/>
+      <c r="AH37" s="60"/>
+      <c r="AI37" s="60"/>
+      <c r="AJ37" s="60"/>
+      <c r="AK37" s="60"/>
+      <c r="AL37" s="60"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
     </row>
     <row r="38" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="17" t="s">
+      <c r="B38" s="47"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17" t="s">
+      <c r="H38" s="13"/>
+      <c r="I38" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17" t="s">
+      <c r="J38" s="13"/>
+      <c r="K38" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17" t="s">
+      <c r="L38" s="13"/>
+      <c r="M38" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17" t="s">
+      <c r="N38" s="13"/>
+      <c r="O38" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17" t="s">
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="R38" s="17"/>
-      <c r="S38" s="17" t="s">
+      <c r="R38" s="13"/>
+      <c r="S38" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="T38" s="17"/>
-      <c r="U38" s="17" t="s">
+      <c r="T38" s="13"/>
+      <c r="U38" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="V38" s="17"/>
-      <c r="W38" s="17" t="s">
+      <c r="V38" s="13"/>
+      <c r="W38" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="X38" s="17"/>
-      <c r="Y38" s="17" t="s">
+      <c r="X38" s="13"/>
+      <c r="Y38" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="Z38" s="17"/>
-      <c r="AA38" s="17" t="s">
+      <c r="Z38" s="13"/>
+      <c r="AA38" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AB38" s="17"/>
-      <c r="AC38" s="15"/>
-      <c r="AD38" s="15"/>
+      <c r="AB38" s="13"/>
+      <c r="AC38" s="47"/>
+      <c r="AD38" s="47"/>
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
       <c r="AI38" s="3"/>
@@ -2837,61 +2839,61 @@
       <c r="AN38" s="3"/>
     </row>
     <row r="39" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="19">
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="44">
         <v>18</v>
       </c>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19">
+      <c r="H39" s="44"/>
+      <c r="I39" s="44">
         <v>23</v>
       </c>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19">
+      <c r="J39" s="44"/>
+      <c r="K39" s="44">
         <v>22</v>
       </c>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19">
+      <c r="L39" s="44"/>
+      <c r="M39" s="44">
         <v>19</v>
       </c>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19">
+      <c r="N39" s="44"/>
+      <c r="O39" s="44">
         <v>16</v>
       </c>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="19">
+      <c r="P39" s="44"/>
+      <c r="Q39" s="44">
         <v>22</v>
       </c>
-      <c r="R39" s="19"/>
-      <c r="S39" s="19">
+      <c r="R39" s="44"/>
+      <c r="S39" s="44">
         <v>22</v>
       </c>
-      <c r="T39" s="19"/>
-      <c r="U39" s="19">
+      <c r="T39" s="44"/>
+      <c r="U39" s="44">
         <v>20</v>
       </c>
-      <c r="V39" s="19"/>
-      <c r="W39" s="19">
+      <c r="V39" s="44"/>
+      <c r="W39" s="44">
         <v>22</v>
       </c>
-      <c r="X39" s="19"/>
-      <c r="Y39" s="19">
+      <c r="X39" s="44"/>
+      <c r="Y39" s="44">
         <v>16</v>
       </c>
-      <c r="Z39" s="21"/>
-      <c r="AA39" s="14">
+      <c r="Z39" s="70"/>
+      <c r="AA39" s="45">
         <f>SUM(G39:Z39)</f>
         <v>200</v>
       </c>
-      <c r="AB39" s="14"/>
-      <c r="AC39" s="54"/>
-      <c r="AD39" s="54"/>
+      <c r="AB39" s="45"/>
+      <c r="AC39" s="14"/>
+      <c r="AD39" s="14"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
@@ -2902,78 +2904,78 @@
       <c r="AN39" s="3"/>
     </row>
     <row r="40" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="20"/>
-      <c r="R40" s="20"/>
-      <c r="S40" s="19"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="19"/>
-      <c r="V40" s="19"/>
-      <c r="W40" s="20"/>
-      <c r="X40" s="20"/>
-      <c r="Y40" s="22"/>
-      <c r="Z40" s="23"/>
-      <c r="AA40" s="18">
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="71"/>
+      <c r="M40" s="71"/>
+      <c r="N40" s="71"/>
+      <c r="O40" s="71"/>
+      <c r="P40" s="71"/>
+      <c r="Q40" s="72"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="71"/>
+      <c r="T40" s="71"/>
+      <c r="U40" s="71"/>
+      <c r="V40" s="71"/>
+      <c r="W40" s="72"/>
+      <c r="X40" s="72"/>
+      <c r="Y40" s="71"/>
+      <c r="Z40" s="73"/>
+      <c r="AA40" s="69">
         <f>SUM(G40:Z40)</f>
         <v>0</v>
       </c>
-      <c r="AB40" s="18"/>
-      <c r="AC40" s="54"/>
-      <c r="AD40" s="54"/>
+      <c r="AB40" s="69"/>
+      <c r="AC40" s="14"/>
+      <c r="AD40" s="14"/>
     </row>
     <row r="41" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="24" t="s">
+      <c r="A41" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="19"/>
-      <c r="T41" s="19"/>
-      <c r="U41" s="19"/>
-      <c r="V41" s="19"/>
-      <c r="W41" s="19"/>
-      <c r="X41" s="19"/>
-      <c r="Y41" s="19"/>
-      <c r="Z41" s="21"/>
-      <c r="AA41" s="14">
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="71"/>
+      <c r="K41" s="71"/>
+      <c r="L41" s="71"/>
+      <c r="M41" s="71"/>
+      <c r="N41" s="71"/>
+      <c r="O41" s="71"/>
+      <c r="P41" s="71"/>
+      <c r="Q41" s="71"/>
+      <c r="R41" s="71"/>
+      <c r="S41" s="71"/>
+      <c r="T41" s="71"/>
+      <c r="U41" s="71"/>
+      <c r="V41" s="71"/>
+      <c r="W41" s="71"/>
+      <c r="X41" s="71"/>
+      <c r="Y41" s="71"/>
+      <c r="Z41" s="73"/>
+      <c r="AA41" s="45">
         <f t="shared" ref="AA41" si="5">SUM(G41:Z41)</f>
         <v>0</v>
       </c>
-      <c r="AB41" s="14"/>
-      <c r="AC41" s="54"/>
-      <c r="AD41" s="54"/>
+      <c r="AB41" s="45"/>
+      <c r="AC41" s="14"/>
+      <c r="AD41" s="14"/>
     </row>
     <row r="42" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
@@ -3042,16 +3044,228 @@
     <row r="82" ht="12.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="256">
-    <mergeCell ref="Y38:Z38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S38:T38"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="AD22:AI22"/>
+    <mergeCell ref="AA41:AB41"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="AD35:AN35"/>
+    <mergeCell ref="AA38:AB38"/>
+    <mergeCell ref="AA39:AB39"/>
+    <mergeCell ref="AA40:AB40"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="W41:X41"/>
+    <mergeCell ref="W40:X40"/>
+    <mergeCell ref="W39:X39"/>
+    <mergeCell ref="Y39:Z39"/>
+    <mergeCell ref="Y40:Z40"/>
+    <mergeCell ref="Y41:Z41"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="Q41:R41"/>
+    <mergeCell ref="S41:T41"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="S39:T39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="AJ19:AN19"/>
+    <mergeCell ref="AJ20:AN20"/>
+    <mergeCell ref="AJ18:AN18"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AJ13:AN13"/>
+    <mergeCell ref="AJ14:AN14"/>
+    <mergeCell ref="AJ15:AN15"/>
+    <mergeCell ref="AJ16:AN16"/>
+    <mergeCell ref="AJ17:AN17"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AJ21:AN21"/>
+    <mergeCell ref="AG37:AL37"/>
+    <mergeCell ref="V15:Y15"/>
+    <mergeCell ref="Z18:AC18"/>
+    <mergeCell ref="Z19:AC19"/>
+    <mergeCell ref="O1:AA1"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="AH4:AN4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="AJ7:AN7"/>
+    <mergeCell ref="AJ8:AN8"/>
+    <mergeCell ref="AJ9:AN9"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="R19:U19"/>
+    <mergeCell ref="Z12:AC12"/>
+    <mergeCell ref="V12:Y12"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="V20:Y20"/>
+    <mergeCell ref="Z7:AC7"/>
+    <mergeCell ref="Z8:AC8"/>
+    <mergeCell ref="Z9:AC9"/>
+    <mergeCell ref="Z11:AC11"/>
+    <mergeCell ref="Z13:AC13"/>
+    <mergeCell ref="Z14:AC14"/>
+    <mergeCell ref="Z15:AC15"/>
+    <mergeCell ref="Z16:AC16"/>
+    <mergeCell ref="Z17:AC17"/>
+    <mergeCell ref="V16:Y16"/>
+    <mergeCell ref="V17:Y17"/>
+    <mergeCell ref="V18:Y18"/>
+    <mergeCell ref="V19:Y19"/>
+    <mergeCell ref="V8:Y8"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="V11:Y11"/>
+    <mergeCell ref="V13:Y13"/>
+    <mergeCell ref="V14:Y14"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="R7:U7"/>
+    <mergeCell ref="R8:U8"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="R11:U11"/>
+    <mergeCell ref="R13:U13"/>
+    <mergeCell ref="R14:U14"/>
+    <mergeCell ref="R15:U15"/>
+    <mergeCell ref="R16:U16"/>
+    <mergeCell ref="R12:U12"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="N8:Q8"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="N13:Q13"/>
+    <mergeCell ref="N14:Q14"/>
+    <mergeCell ref="B16:M16"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="B15:M15"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N15:Q15"/>
+    <mergeCell ref="N16:Q16"/>
+    <mergeCell ref="N17:Q17"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="N12:Q12"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="E3:U3"/>
+    <mergeCell ref="Z3:AN3"/>
+    <mergeCell ref="U4:AG4"/>
+    <mergeCell ref="G4:P4"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="N5:AC5"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="V6:Y6"/>
+    <mergeCell ref="Z6:AC6"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="V35:W35"/>
+    <mergeCell ref="V36:W36"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="Z20:AC20"/>
+    <mergeCell ref="R20:U20"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="AC38:AD38"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="C20:M20"/>
+    <mergeCell ref="N21:AC21"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A32:O32"/>
+    <mergeCell ref="A33:O33"/>
+    <mergeCell ref="A34:O34"/>
+    <mergeCell ref="A35:O35"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="P25:Q25"/>
     <mergeCell ref="AC41:AD41"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:N2"/>
@@ -3076,228 +3290,16 @@
     <mergeCell ref="R17:U17"/>
     <mergeCell ref="R18:U18"/>
     <mergeCell ref="C21:G21"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="C20:M20"/>
-    <mergeCell ref="N21:AC21"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="A33:O33"/>
-    <mergeCell ref="A34:O34"/>
-    <mergeCell ref="A35:O35"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="Z20:AC20"/>
-    <mergeCell ref="R20:U20"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="AC38:AD38"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A26:O26"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="N19:Q19"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="V35:W35"/>
-    <mergeCell ref="V36:W36"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N15:Q15"/>
-    <mergeCell ref="N16:Q16"/>
-    <mergeCell ref="N17:Q17"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="E3:U3"/>
-    <mergeCell ref="Z3:AN3"/>
-    <mergeCell ref="U4:AG4"/>
-    <mergeCell ref="G4:P4"/>
-    <mergeCell ref="A5:M6"/>
-    <mergeCell ref="N5:AC5"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="R6:U6"/>
-    <mergeCell ref="V6:Y6"/>
-    <mergeCell ref="Z6:AC6"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="B16:M16"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="B15:M15"/>
-    <mergeCell ref="R15:U15"/>
-    <mergeCell ref="R16:U16"/>
-    <mergeCell ref="R12:U12"/>
-    <mergeCell ref="N7:Q7"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="N13:Q13"/>
-    <mergeCell ref="N14:Q14"/>
-    <mergeCell ref="V8:Y8"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="V11:Y11"/>
-    <mergeCell ref="V13:Y13"/>
-    <mergeCell ref="V14:Y14"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="R7:U7"/>
-    <mergeCell ref="R8:U8"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="R11:U11"/>
-    <mergeCell ref="R13:U13"/>
-    <mergeCell ref="R14:U14"/>
-    <mergeCell ref="Z13:AC13"/>
-    <mergeCell ref="Z14:AC14"/>
-    <mergeCell ref="Z15:AC15"/>
-    <mergeCell ref="Z16:AC16"/>
-    <mergeCell ref="Z17:AC17"/>
-    <mergeCell ref="V16:Y16"/>
-    <mergeCell ref="V17:Y17"/>
-    <mergeCell ref="V18:Y18"/>
-    <mergeCell ref="V19:Y19"/>
-    <mergeCell ref="AG37:AL37"/>
-    <mergeCell ref="V15:Y15"/>
-    <mergeCell ref="Z18:AC18"/>
-    <mergeCell ref="Z19:AC19"/>
-    <mergeCell ref="O1:AA1"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="AH4:AN4"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="AJ7:AN7"/>
-    <mergeCell ref="AJ8:AN8"/>
-    <mergeCell ref="AJ9:AN9"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="R19:U19"/>
-    <mergeCell ref="Z12:AC12"/>
-    <mergeCell ref="V12:Y12"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="V20:Y20"/>
-    <mergeCell ref="Z7:AC7"/>
-    <mergeCell ref="Z8:AC8"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="Z11:AC11"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="AJ19:AN19"/>
-    <mergeCell ref="AJ20:AN20"/>
-    <mergeCell ref="AJ18:AN18"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AJ13:AN13"/>
-    <mergeCell ref="AJ14:AN14"/>
-    <mergeCell ref="AJ15:AN15"/>
-    <mergeCell ref="AJ16:AN16"/>
-    <mergeCell ref="AJ17:AN17"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AJ21:AN21"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="AD22:AI22"/>
-    <mergeCell ref="AA41:AB41"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="AD35:AN35"/>
-    <mergeCell ref="AA38:AB38"/>
-    <mergeCell ref="AA39:AB39"/>
-    <mergeCell ref="AA40:AB40"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="U41:V41"/>
-    <mergeCell ref="W41:X41"/>
-    <mergeCell ref="W40:X40"/>
-    <mergeCell ref="W39:X39"/>
-    <mergeCell ref="Y39:Z39"/>
-    <mergeCell ref="Y40:Z40"/>
-    <mergeCell ref="Y41:Z41"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="Q41:R41"/>
-    <mergeCell ref="S41:T41"/>
-    <mergeCell ref="S40:T40"/>
-    <mergeCell ref="S39:T39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="Y38:Z38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="W38:X38"/>
   </mergeCells>
   <conditionalFormatting sqref="AD7:AI19">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">

--- a/public/files/report_card_templates/JHS.xlsx
+++ b/public/files/report_card_templates/JHS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\schoolsys\public\files\report_card_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D62969-E561-4F18-A870-471DDECE887D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0535CC62-A542-4B68-9FFA-6F3FDBE62B29}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -504,14 +504,158 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -542,150 +686,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1050,265 +1050,265 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="1.5703125" customWidth="1"/>
-    <col min="7" max="26" width="2.28515625" customWidth="1"/>
+    <col min="7" max="26" width="2" customWidth="1"/>
     <col min="27" max="40" width="1.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O1" s="61" t="s">
+      <c r="O1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
-      <c r="U1" s="61"/>
-      <c r="V1" s="61"/>
-      <c r="W1" s="61"/>
-      <c r="X1" s="61"/>
-      <c r="Y1" s="61"/>
-      <c r="Z1" s="61"/>
-      <c r="AA1" s="61"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
     </row>
     <row r="2" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="Q2" s="15" t="s">
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="Q2" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
     </row>
     <row r="3" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="55"/>
-      <c r="U3" s="55"/>
-      <c r="V3" s="62" t="s">
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="W3" s="62"/>
-      <c r="X3" s="62"/>
-      <c r="Y3" s="62"/>
-      <c r="Z3" s="55"/>
-      <c r="AA3" s="55"/>
-      <c r="AB3" s="55"/>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="55"/>
-      <c r="AE3" s="55"/>
-      <c r="AF3" s="55"/>
-      <c r="AG3" s="55"/>
-      <c r="AH3" s="55"/>
-      <c r="AI3" s="55"/>
-      <c r="AJ3" s="55"/>
-      <c r="AK3" s="55"/>
-      <c r="AL3" s="55"/>
-      <c r="AM3" s="55"/>
-      <c r="AN3" s="55"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="45"/>
+      <c r="AG3" s="45"/>
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="45"/>
+      <c r="AJ3" s="45"/>
+      <c r="AK3" s="45"/>
+      <c r="AL3" s="45"/>
+      <c r="AM3" s="45"/>
+      <c r="AN3" s="45"/>
     </row>
     <row r="4" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="59" t="s">
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="59"/>
-      <c r="S4" s="59"/>
-      <c r="T4" s="59"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="56"/>
-      <c r="Y4" s="56"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="56"/>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="56"/>
-      <c r="AG4" s="56"/>
-      <c r="AH4" s="59"/>
-      <c r="AI4" s="59"/>
-      <c r="AJ4" s="59"/>
-      <c r="AK4" s="59"/>
-      <c r="AL4" s="59"/>
-      <c r="AM4" s="59"/>
-      <c r="AN4" s="59"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
+      <c r="Z4" s="46"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="46"/>
+      <c r="AC4" s="46"/>
+      <c r="AD4" s="46"/>
+      <c r="AE4" s="46"/>
+      <c r="AF4" s="46"/>
+      <c r="AG4" s="46"/>
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="36"/>
+      <c r="AK4" s="36"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="36"/>
+      <c r="AN4" s="36"/>
     </row>
     <row r="5" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="19" t="s">
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="47"/>
+      <c r="X5" s="47"/>
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="47"/>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="AE5" s="20"/>
-      <c r="AF5" s="20"/>
-      <c r="AG5" s="20"/>
-      <c r="AH5" s="20"/>
-      <c r="AI5" s="21"/>
-      <c r="AJ5" s="19" t="s">
+      <c r="AE5" s="68"/>
+      <c r="AF5" s="68"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="69"/>
+      <c r="AJ5" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="AK5" s="20"/>
-      <c r="AL5" s="20"/>
-      <c r="AM5" s="20"/>
-      <c r="AN5" s="21"/>
+      <c r="AK5" s="68"/>
+      <c r="AL5" s="68"/>
+      <c r="AM5" s="68"/>
+      <c r="AN5" s="69"/>
     </row>
     <row r="6" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="57" t="s">
+      <c r="A6" s="47"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="O6" s="57"/>
-      <c r="P6" s="57"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="57" t="s">
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="S6" s="57"/>
-      <c r="T6" s="57"/>
-      <c r="U6" s="57"/>
-      <c r="V6" s="57" t="s">
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="57"/>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="57" t="s">
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="57"/>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="23"/>
-      <c r="AF6" s="23"/>
-      <c r="AG6" s="23"/>
-      <c r="AH6" s="23"/>
-      <c r="AI6" s="24"/>
-      <c r="AJ6" s="22"/>
-      <c r="AK6" s="23"/>
-      <c r="AL6" s="23"/>
-      <c r="AM6" s="23"/>
-      <c r="AN6" s="24"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="70"/>
+      <c r="AE6" s="71"/>
+      <c r="AF6" s="71"/>
+      <c r="AG6" s="71"/>
+      <c r="AH6" s="71"/>
+      <c r="AI6" s="72"/>
+      <c r="AJ6" s="70"/>
+      <c r="AK6" s="71"/>
+      <c r="AL6" s="71"/>
+      <c r="AM6" s="71"/>
+      <c r="AN6" s="72"/>
     </row>
     <row r="7" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="49"/>
-      <c r="M7" s="49"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
       <c r="N7" s="28"/>
       <c r="O7" s="28"/>
       <c r="P7" s="28"/>
@@ -1325,15 +1325,15 @@
       <c r="AA7" s="28"/>
       <c r="AB7" s="28"/>
       <c r="AC7" s="28"/>
-      <c r="AD7" s="29" t="str">
+      <c r="AD7" s="25" t="str">
         <f>IF(COUNT(N7:AC7)=4,SUM(N7:AC7)/4,"")</f>
         <v/>
       </c>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AH7" s="30"/>
-      <c r="AI7" s="31"/>
+      <c r="AE7" s="26"/>
+      <c r="AF7" s="26"/>
+      <c r="AG7" s="26"/>
+      <c r="AH7" s="26"/>
+      <c r="AI7" s="27"/>
       <c r="AJ7" s="28" t="str">
         <f>IF(AD7&lt;&gt;"",IF(AD7&gt;=75,"Passed","Failed"),"")</f>
         <v/>
@@ -1344,21 +1344,21 @@
       <c r="AN7" s="28"/>
     </row>
     <row r="8" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
       <c r="N8" s="28"/>
       <c r="O8" s="28"/>
       <c r="P8" s="28"/>
@@ -1375,15 +1375,15 @@
       <c r="AA8" s="28"/>
       <c r="AB8" s="28"/>
       <c r="AC8" s="28"/>
-      <c r="AD8" s="29" t="str">
+      <c r="AD8" s="25" t="str">
         <f t="shared" ref="AD8:AD19" si="0">IF(COUNT(N8:AC8)=4,SUM(N8:AC8)/4,"")</f>
         <v/>
       </c>
-      <c r="AE8" s="30"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="30"/>
-      <c r="AH8" s="30"/>
-      <c r="AI8" s="31"/>
+      <c r="AE8" s="26"/>
+      <c r="AF8" s="26"/>
+      <c r="AG8" s="26"/>
+      <c r="AH8" s="26"/>
+      <c r="AI8" s="27"/>
       <c r="AJ8" s="28" t="str">
         <f t="shared" ref="AJ8:AJ19" si="1">IF(AD8&lt;&gt;"",IF(AD8&gt;=75,"Passed","Failed"),"")</f>
         <v/>
@@ -1394,21 +1394,21 @@
       <c r="AN8" s="28"/>
     </row>
     <row r="9" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
       <c r="N9" s="28"/>
       <c r="O9" s="28"/>
       <c r="P9" s="28"/>
@@ -1425,15 +1425,15 @@
       <c r="AA9" s="28"/>
       <c r="AB9" s="28"/>
       <c r="AC9" s="28"/>
-      <c r="AD9" s="29" t="str">
+      <c r="AD9" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE9" s="30"/>
-      <c r="AF9" s="30"/>
-      <c r="AG9" s="30"/>
-      <c r="AH9" s="30"/>
-      <c r="AI9" s="31"/>
+      <c r="AE9" s="26"/>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26"/>
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="27"/>
       <c r="AJ9" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1444,21 +1444,21 @@
       <c r="AN9" s="28"/>
     </row>
     <row r="10" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="27"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="39"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="40"/>
       <c r="N10" s="28"/>
       <c r="O10" s="28"/>
       <c r="P10" s="28"/>
@@ -1475,15 +1475,15 @@
       <c r="AA10" s="28"/>
       <c r="AB10" s="28"/>
       <c r="AC10" s="28"/>
-      <c r="AD10" s="29" t="str">
+      <c r="AD10" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="30"/>
-      <c r="AG10" s="30"/>
-      <c r="AH10" s="30"/>
-      <c r="AI10" s="31"/>
+      <c r="AE10" s="26"/>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="26"/>
+      <c r="AH10" s="26"/>
+      <c r="AI10" s="27"/>
       <c r="AJ10" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1494,21 +1494,21 @@
       <c r="AN10" s="28"/>
     </row>
     <row r="11" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="49"/>
-      <c r="M11" s="49"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
       <c r="N11" s="28"/>
       <c r="O11" s="28"/>
       <c r="P11" s="28"/>
@@ -1525,15 +1525,15 @@
       <c r="AA11" s="28"/>
       <c r="AB11" s="28"/>
       <c r="AC11" s="28"/>
-      <c r="AD11" s="29" t="str">
+      <c r="AD11" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="30"/>
-      <c r="AG11" s="30"/>
-      <c r="AH11" s="30"/>
-      <c r="AI11" s="31"/>
+      <c r="AE11" s="26"/>
+      <c r="AF11" s="26"/>
+      <c r="AG11" s="26"/>
+      <c r="AH11" s="26"/>
+      <c r="AI11" s="27"/>
       <c r="AJ11" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1544,21 +1544,21 @@
       <c r="AN11" s="28"/>
     </row>
     <row r="12" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="54"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="44"/>
       <c r="N12" s="28"/>
       <c r="O12" s="28"/>
       <c r="P12" s="28"/>
@@ -1575,15 +1575,15 @@
       <c r="AA12" s="28"/>
       <c r="AB12" s="28"/>
       <c r="AC12" s="28"/>
-      <c r="AD12" s="29" t="str">
+      <c r="AD12" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE12" s="30"/>
-      <c r="AF12" s="30"/>
-      <c r="AG12" s="30"/>
-      <c r="AH12" s="30"/>
-      <c r="AI12" s="31"/>
+      <c r="AE12" s="26"/>
+      <c r="AF12" s="26"/>
+      <c r="AG12" s="26"/>
+      <c r="AH12" s="26"/>
+      <c r="AI12" s="27"/>
       <c r="AJ12" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1594,21 +1594,21 @@
       <c r="AN12" s="28"/>
     </row>
     <row r="13" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
       <c r="N13" s="28"/>
       <c r="O13" s="28"/>
       <c r="P13" s="28"/>
@@ -1625,15 +1625,15 @@
       <c r="AA13" s="28"/>
       <c r="AB13" s="28"/>
       <c r="AC13" s="28"/>
-      <c r="AD13" s="29" t="str">
+      <c r="AD13" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE13" s="30"/>
-      <c r="AF13" s="30"/>
-      <c r="AG13" s="30"/>
-      <c r="AH13" s="30"/>
-      <c r="AI13" s="31"/>
+      <c r="AE13" s="26"/>
+      <c r="AF13" s="26"/>
+      <c r="AG13" s="26"/>
+      <c r="AH13" s="26"/>
+      <c r="AI13" s="27"/>
       <c r="AJ13" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1645,20 +1645,20 @@
     </row>
     <row r="14" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="27"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="40"/>
       <c r="N14" s="28"/>
       <c r="O14" s="28"/>
       <c r="P14" s="28"/>
@@ -1675,15 +1675,15 @@
       <c r="AA14" s="28"/>
       <c r="AB14" s="28"/>
       <c r="AC14" s="28"/>
-      <c r="AD14" s="29" t="str">
+      <c r="AD14" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE14" s="30"/>
-      <c r="AF14" s="30"/>
-      <c r="AG14" s="30"/>
-      <c r="AH14" s="30"/>
-      <c r="AI14" s="31"/>
+      <c r="AE14" s="26"/>
+      <c r="AF14" s="26"/>
+      <c r="AG14" s="26"/>
+      <c r="AH14" s="26"/>
+      <c r="AI14" s="27"/>
       <c r="AJ14" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1695,20 +1695,20 @@
     </row>
     <row r="15" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="27"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39"/>
+      <c r="M15" s="40"/>
       <c r="N15" s="28"/>
       <c r="O15" s="28"/>
       <c r="P15" s="28"/>
@@ -1725,15 +1725,15 @@
       <c r="AA15" s="28"/>
       <c r="AB15" s="28"/>
       <c r="AC15" s="28"/>
-      <c r="AD15" s="29" t="str">
+      <c r="AD15" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE15" s="30"/>
-      <c r="AF15" s="30"/>
-      <c r="AG15" s="30"/>
-      <c r="AH15" s="30"/>
-      <c r="AI15" s="31"/>
+      <c r="AE15" s="26"/>
+      <c r="AF15" s="26"/>
+      <c r="AG15" s="26"/>
+      <c r="AH15" s="26"/>
+      <c r="AI15" s="27"/>
       <c r="AJ15" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1745,20 +1745,20 @@
     </row>
     <row r="16" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="27"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="40"/>
       <c r="N16" s="28"/>
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
@@ -1775,15 +1775,15 @@
       <c r="AA16" s="28"/>
       <c r="AB16" s="28"/>
       <c r="AC16" s="28"/>
-      <c r="AD16" s="29" t="str">
+      <c r="AD16" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE16" s="30"/>
-      <c r="AF16" s="30"/>
-      <c r="AG16" s="30"/>
-      <c r="AH16" s="30"/>
-      <c r="AI16" s="31"/>
+      <c r="AE16" s="26"/>
+      <c r="AF16" s="26"/>
+      <c r="AG16" s="26"/>
+      <c r="AH16" s="26"/>
+      <c r="AI16" s="27"/>
       <c r="AJ16" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1795,20 +1795,20 @@
     </row>
     <row r="17" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="27"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="40"/>
       <c r="N17" s="28"/>
       <c r="O17" s="28"/>
       <c r="P17" s="28"/>
@@ -1825,15 +1825,15 @@
       <c r="AA17" s="28"/>
       <c r="AB17" s="28"/>
       <c r="AC17" s="28"/>
-      <c r="AD17" s="29" t="str">
+      <c r="AD17" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE17" s="30"/>
-      <c r="AF17" s="30"/>
-      <c r="AG17" s="30"/>
-      <c r="AH17" s="30"/>
-      <c r="AI17" s="31"/>
+      <c r="AE17" s="26"/>
+      <c r="AF17" s="26"/>
+      <c r="AG17" s="26"/>
+      <c r="AH17" s="26"/>
+      <c r="AI17" s="27"/>
       <c r="AJ17" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1844,21 +1844,21 @@
       <c r="AN17" s="28"/>
     </row>
     <row r="18" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
       <c r="N18" s="28"/>
       <c r="O18" s="28"/>
       <c r="P18" s="28"/>
@@ -1875,15 +1875,15 @@
       <c r="AA18" s="28"/>
       <c r="AB18" s="28"/>
       <c r="AC18" s="28"/>
-      <c r="AD18" s="29" t="str">
+      <c r="AD18" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE18" s="30"/>
-      <c r="AF18" s="30"/>
-      <c r="AG18" s="30"/>
-      <c r="AH18" s="30"/>
-      <c r="AI18" s="31"/>
+      <c r="AE18" s="26"/>
+      <c r="AF18" s="26"/>
+      <c r="AG18" s="26"/>
+      <c r="AH18" s="26"/>
+      <c r="AI18" s="27"/>
       <c r="AJ18" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1894,21 +1894,21 @@
       <c r="AN18" s="28"/>
     </row>
     <row r="19" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="48"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
       <c r="N19" s="28"/>
       <c r="O19" s="28"/>
       <c r="P19" s="28"/>
@@ -1925,15 +1925,15 @@
       <c r="AA19" s="28"/>
       <c r="AB19" s="28"/>
       <c r="AC19" s="28"/>
-      <c r="AD19" s="29" t="str">
+      <c r="AD19" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="30"/>
-      <c r="AH19" s="30"/>
-      <c r="AI19" s="31"/>
+      <c r="AE19" s="26"/>
+      <c r="AF19" s="26"/>
+      <c r="AG19" s="26"/>
+      <c r="AH19" s="26"/>
+      <c r="AI19" s="27"/>
       <c r="AJ19" s="28" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1946,53 +1946,53 @@
     <row r="20" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="46" t="str">
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="K20" s="57"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="38" t="str">
         <f>IF(SUM(N7:Q13,N18)/8 &gt; 0, SUM(N7:Q13,N18)/8, "")</f>
         <v/>
       </c>
-      <c r="O20" s="46"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="46"/>
-      <c r="R20" s="46" t="str">
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="38" t="str">
         <f t="shared" ref="R20" si="2">IF(SUM(R7:U13,R18)/8 &gt; 0, SUM(R7:U13,R18)/8, "")</f>
         <v/>
       </c>
-      <c r="S20" s="46"/>
-      <c r="T20" s="46"/>
-      <c r="U20" s="46"/>
-      <c r="V20" s="46" t="str">
+      <c r="S20" s="38"/>
+      <c r="T20" s="38"/>
+      <c r="U20" s="38"/>
+      <c r="V20" s="38" t="str">
         <f t="shared" ref="V20" si="3">IF(SUM(V7:Y13,V18)/8 &gt; 0, SUM(V7:Y13,V18)/8, "")</f>
         <v/>
       </c>
-      <c r="W20" s="46"/>
-      <c r="X20" s="46"/>
-      <c r="Y20" s="46"/>
-      <c r="Z20" s="46" t="str">
+      <c r="W20" s="38"/>
+      <c r="X20" s="38"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="38" t="str">
         <f t="shared" ref="Z20" si="4">IF(SUM(Z7:AC13,Z18)/8 &gt; 0, SUM(Z7:AC13,Z18)/8, "")</f>
         <v/>
       </c>
-      <c r="AA20" s="46"/>
-      <c r="AB20" s="46"/>
-      <c r="AC20" s="46"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
-      <c r="AG20" s="30"/>
-      <c r="AH20" s="30"/>
-      <c r="AI20" s="31"/>
+      <c r="AA20" s="38"/>
+      <c r="AB20" s="38"/>
+      <c r="AC20" s="38"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="26"/>
+      <c r="AF20" s="26"/>
+      <c r="AG20" s="26"/>
+      <c r="AH20" s="26"/>
+      <c r="AI20" s="27"/>
       <c r="AJ20" s="28"/>
       <c r="AK20" s="28"/>
       <c r="AL20" s="28"/>
@@ -2002,51 +2002,51 @@
     <row r="21" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="37" t="s">
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="38"/>
-      <c r="V21" s="38"/>
-      <c r="W21" s="38"/>
-      <c r="X21" s="38"/>
-      <c r="Y21" s="38"/>
-      <c r="Z21" s="38"/>
-      <c r="AA21" s="38"/>
-      <c r="AB21" s="38"/>
-      <c r="AC21" s="39"/>
-      <c r="AD21" s="63" t="str">
+      <c r="O21" s="59"/>
+      <c r="P21" s="59"/>
+      <c r="Q21" s="59"/>
+      <c r="R21" s="59"/>
+      <c r="S21" s="59"/>
+      <c r="T21" s="59"/>
+      <c r="U21" s="59"/>
+      <c r="V21" s="59"/>
+      <c r="W21" s="59"/>
+      <c r="X21" s="59"/>
+      <c r="Y21" s="59"/>
+      <c r="Z21" s="59"/>
+      <c r="AA21" s="59"/>
+      <c r="AB21" s="59"/>
+      <c r="AC21" s="60"/>
+      <c r="AD21" s="29" t="str">
         <f>IF(COUNT(AD7:AI13,AD18)=8,SUM(AD7:AI13,AD18)/8,"")</f>
         <v/>
       </c>
-      <c r="AE21" s="64"/>
-      <c r="AF21" s="64"/>
-      <c r="AG21" s="64"/>
-      <c r="AH21" s="64"/>
-      <c r="AI21" s="65"/>
-      <c r="AJ21" s="57"/>
-      <c r="AK21" s="57"/>
-      <c r="AL21" s="57"/>
-      <c r="AM21" s="57"/>
-      <c r="AN21" s="57"/>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="30"/>
+      <c r="AG21" s="30"/>
+      <c r="AH21" s="30"/>
+      <c r="AI21" s="31"/>
+      <c r="AJ21" s="32"/>
+      <c r="AK21" s="32"/>
+      <c r="AL21" s="32"/>
+      <c r="AM21" s="32"/>
+      <c r="AN21" s="32"/>
     </row>
     <row r="22" spans="1:40" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
@@ -2078,12 +2078,12 @@
       <c r="AA22" s="10"/>
       <c r="AB22" s="10"/>
       <c r="AC22" s="10"/>
-      <c r="AD22" s="67"/>
-      <c r="AE22" s="67"/>
-      <c r="AF22" s="67"/>
-      <c r="AG22" s="67"/>
-      <c r="AH22" s="67"/>
-      <c r="AI22" s="67"/>
+      <c r="AD22" s="13"/>
+      <c r="AE22" s="13"/>
+      <c r="AF22" s="13"/>
+      <c r="AG22" s="13"/>
+      <c r="AH22" s="13"/>
+      <c r="AI22" s="13"/>
       <c r="AJ22" s="4"/>
       <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
@@ -2120,367 +2120,367 @@
       <c r="Y23" s="2"/>
     </row>
     <row r="24" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="34" t="s">
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
+      <c r="N24" s="47"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="Q24" s="34"/>
-      <c r="R24" s="34" t="s">
+      <c r="Q24" s="55"/>
+      <c r="R24" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="S24" s="34"/>
-      <c r="T24" s="34" t="s">
+      <c r="S24" s="55"/>
+      <c r="T24" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="U24" s="34"/>
-      <c r="V24" s="34" t="s">
+      <c r="U24" s="55"/>
+      <c r="V24" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="W24" s="34"/>
-      <c r="Y24" s="17" t="s">
+      <c r="W24" s="55"/>
+      <c r="Y24" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="Z24" s="17"/>
-      <c r="AA24" s="17"/>
-      <c r="AB24" s="17"/>
-      <c r="AC24" s="17"/>
-      <c r="AD24" s="17"/>
-      <c r="AE24" s="17"/>
-      <c r="AF24" s="17"/>
-      <c r="AG24" s="17"/>
-      <c r="AH24" s="17"/>
-      <c r="AI24" s="17"/>
-      <c r="AJ24" s="17"/>
+      <c r="Z24" s="65"/>
+      <c r="AA24" s="65"/>
+      <c r="AB24" s="65"/>
+      <c r="AC24" s="65"/>
+      <c r="AD24" s="65"/>
+      <c r="AE24" s="65"/>
+      <c r="AF24" s="65"/>
+      <c r="AG24" s="65"/>
+      <c r="AH24" s="65"/>
+      <c r="AI24" s="65"/>
+      <c r="AJ24" s="65"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
       <c r="AN24" s="3"/>
     </row>
     <row r="25" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="41"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="44"/>
-      <c r="R25" s="44"/>
-      <c r="S25" s="44"/>
-      <c r="T25" s="44"/>
-      <c r="U25" s="44"/>
-      <c r="V25" s="45"/>
-      <c r="W25" s="45"/>
-      <c r="Y25" s="18" t="s">
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="21"/>
+      <c r="S25" s="21"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="21"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="Y25" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="Z25" s="18"/>
-      <c r="AA25" s="18"/>
-      <c r="AB25" s="18"/>
-      <c r="AC25" s="18"/>
-      <c r="AD25" s="18"/>
-      <c r="AE25" s="18"/>
-      <c r="AF25" s="18"/>
-      <c r="AG25" s="18"/>
-      <c r="AH25" s="18"/>
-      <c r="AI25" s="18"/>
-      <c r="AJ25" s="18"/>
-      <c r="AK25" s="18"/>
-      <c r="AL25" s="18"/>
-      <c r="AM25" s="18"/>
+      <c r="Z25" s="66"/>
+      <c r="AA25" s="66"/>
+      <c r="AB25" s="66"/>
+      <c r="AC25" s="66"/>
+      <c r="AD25" s="66"/>
+      <c r="AE25" s="66"/>
+      <c r="AF25" s="66"/>
+      <c r="AG25" s="66"/>
+      <c r="AH25" s="66"/>
+      <c r="AI25" s="66"/>
+      <c r="AJ25" s="66"/>
+      <c r="AK25" s="66"/>
+      <c r="AL25" s="66"/>
+      <c r="AM25" s="66"/>
       <c r="AN25" s="3">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="45"/>
-      <c r="S26" s="45"/>
-      <c r="T26" s="45"/>
-      <c r="U26" s="45"/>
-      <c r="V26" s="45"/>
-      <c r="W26" s="45"/>
-      <c r="Y26" s="18" t="s">
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="Y26" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="Z26" s="18"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="18"/>
-      <c r="AC26" s="18"/>
-      <c r="AD26" s="18"/>
-      <c r="AE26" s="18"/>
-      <c r="AF26" s="18"/>
-      <c r="AG26" s="18"/>
-      <c r="AH26" s="18"/>
-      <c r="AI26" s="18"/>
-      <c r="AJ26" s="18"/>
-      <c r="AK26" s="18"/>
-      <c r="AL26" s="18"/>
-      <c r="AM26" s="18"/>
+      <c r="Z26" s="66"/>
+      <c r="AA26" s="66"/>
+      <c r="AB26" s="66"/>
+      <c r="AC26" s="66"/>
+      <c r="AD26" s="66"/>
+      <c r="AE26" s="66"/>
+      <c r="AF26" s="66"/>
+      <c r="AG26" s="66"/>
+      <c r="AH26" s="66"/>
+      <c r="AI26" s="66"/>
+      <c r="AJ26" s="66"/>
+      <c r="AK26" s="66"/>
+      <c r="AL26" s="66"/>
+      <c r="AM26" s="66"/>
       <c r="AN26" s="3">
         <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="45"/>
-      <c r="S27" s="45"/>
-      <c r="T27" s="45"/>
-      <c r="U27" s="45"/>
-      <c r="V27" s="45"/>
-      <c r="W27" s="45"/>
-      <c r="Y27" s="18" t="s">
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="53"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="Y27" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="Z27" s="18"/>
-      <c r="AA27" s="18"/>
-      <c r="AB27" s="18"/>
-      <c r="AC27" s="18"/>
-      <c r="AD27" s="18"/>
-      <c r="AE27" s="18"/>
-      <c r="AF27" s="18"/>
-      <c r="AG27" s="18"/>
-      <c r="AH27" s="18"/>
-      <c r="AI27" s="18"/>
-      <c r="AJ27" s="18"/>
-      <c r="AK27" s="18"/>
-      <c r="AL27" s="18"/>
-      <c r="AM27" s="18"/>
+      <c r="Z27" s="66"/>
+      <c r="AA27" s="66"/>
+      <c r="AB27" s="66"/>
+      <c r="AC27" s="66"/>
+      <c r="AD27" s="66"/>
+      <c r="AE27" s="66"/>
+      <c r="AF27" s="66"/>
+      <c r="AG27" s="66"/>
+      <c r="AH27" s="66"/>
+      <c r="AI27" s="66"/>
+      <c r="AJ27" s="66"/>
+      <c r="AK27" s="66"/>
+      <c r="AL27" s="66"/>
+      <c r="AM27" s="66"/>
       <c r="AN27" s="3">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="45"/>
-      <c r="T28" s="45"/>
-      <c r="U28" s="45"/>
-      <c r="V28" s="45"/>
-      <c r="W28" s="45"/>
-      <c r="Y28" s="18" t="s">
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="53"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="Y28" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="Z28" s="18"/>
-      <c r="AA28" s="18"/>
-      <c r="AB28" s="18"/>
-      <c r="AC28" s="18"/>
-      <c r="AD28" s="18"/>
-      <c r="AE28" s="18"/>
-      <c r="AF28" s="18"/>
-      <c r="AG28" s="18"/>
-      <c r="AH28" s="18"/>
-      <c r="AI28" s="18"/>
-      <c r="AJ28" s="18"/>
-      <c r="AK28" s="18"/>
-      <c r="AL28" s="18"/>
-      <c r="AM28" s="18"/>
+      <c r="Z28" s="66"/>
+      <c r="AA28" s="66"/>
+      <c r="AB28" s="66"/>
+      <c r="AC28" s="66"/>
+      <c r="AD28" s="66"/>
+      <c r="AE28" s="66"/>
+      <c r="AF28" s="66"/>
+      <c r="AG28" s="66"/>
+      <c r="AH28" s="66"/>
+      <c r="AI28" s="66"/>
+      <c r="AJ28" s="66"/>
+      <c r="AK28" s="66"/>
+      <c r="AL28" s="66"/>
+      <c r="AM28" s="66"/>
       <c r="AN28" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="41" t="s">
+      <c r="A29" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="45"/>
-      <c r="S29" s="45"/>
-      <c r="T29" s="45"/>
-      <c r="U29" s="45"/>
-      <c r="V29" s="45"/>
-      <c r="W29" s="45"/>
-      <c r="Y29" s="18" t="s">
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="53"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="21"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="Y29" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="Z29" s="18"/>
-      <c r="AA29" s="18"/>
-      <c r="AB29" s="18"/>
-      <c r="AC29" s="18"/>
-      <c r="AD29" s="18"/>
-      <c r="AE29" s="18"/>
-      <c r="AF29" s="18"/>
-      <c r="AG29" s="18"/>
-      <c r="AH29" s="18"/>
-      <c r="AI29" s="18"/>
-      <c r="AJ29" s="18"/>
-      <c r="AK29" s="18"/>
-      <c r="AL29" s="18"/>
-      <c r="AM29" s="18"/>
+      <c r="Z29" s="66"/>
+      <c r="AA29" s="66"/>
+      <c r="AB29" s="66"/>
+      <c r="AC29" s="66"/>
+      <c r="AD29" s="66"/>
+      <c r="AE29" s="66"/>
+      <c r="AF29" s="66"/>
+      <c r="AG29" s="66"/>
+      <c r="AH29" s="66"/>
+      <c r="AI29" s="66"/>
+      <c r="AJ29" s="66"/>
+      <c r="AK29" s="66"/>
+      <c r="AL29" s="66"/>
+      <c r="AM29" s="66"/>
       <c r="AN29" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
-      <c r="L30" s="41"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="41"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="45"/>
-      <c r="U30" s="45"/>
-      <c r="V30" s="45"/>
-      <c r="W30" s="45"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="53"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="21"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
       <c r="X30" s="3"/>
-      <c r="Y30" s="18" t="s">
+      <c r="Y30" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="Z30" s="18"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="18"/>
-      <c r="AD30" s="18"/>
-      <c r="AE30" s="18"/>
-      <c r="AF30" s="18"/>
-      <c r="AG30" s="18"/>
-      <c r="AH30" s="18"/>
-      <c r="AI30" s="18"/>
-      <c r="AJ30" s="18"/>
-      <c r="AK30" s="18"/>
-      <c r="AL30" s="18"/>
-      <c r="AM30" s="18"/>
+      <c r="Z30" s="66"/>
+      <c r="AA30" s="66"/>
+      <c r="AB30" s="66"/>
+      <c r="AC30" s="66"/>
+      <c r="AD30" s="66"/>
+      <c r="AE30" s="66"/>
+      <c r="AF30" s="66"/>
+      <c r="AG30" s="66"/>
+      <c r="AH30" s="66"/>
+      <c r="AI30" s="66"/>
+      <c r="AJ30" s="66"/>
+      <c r="AK30" s="66"/>
+      <c r="AL30" s="66"/>
+      <c r="AM30" s="66"/>
       <c r="AN30" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="41" t="s">
+      <c r="A31" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="41"/>
-      <c r="M31" s="41"/>
-      <c r="N31" s="41"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="45"/>
-      <c r="U31" s="45"/>
-      <c r="V31" s="45"/>
-      <c r="W31" s="45"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
+      <c r="L31" s="53"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="53"/>
+      <c r="O31" s="53"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="8"/>
       <c r="Z31" s="8"/>
@@ -2500,31 +2500,31 @@
       <c r="AN31" s="3"/>
     </row>
     <row r="32" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="42" t="s">
+      <c r="A32" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="42"/>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="44"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="45"/>
-      <c r="U32" s="45"/>
-      <c r="V32" s="45"/>
-      <c r="W32" s="45"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
+      <c r="L32" s="62"/>
+      <c r="M32" s="62"/>
+      <c r="N32" s="62"/>
+      <c r="O32" s="62"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="11"/>
       <c r="Z32" s="11"/>
@@ -2544,31 +2544,31 @@
       <c r="AN32" s="3"/>
     </row>
     <row r="33" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="53" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="41"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="41"/>
-      <c r="O33" s="41"/>
-      <c r="P33" s="44"/>
-      <c r="Q33" s="44"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="45"/>
-      <c r="T33" s="45"/>
-      <c r="U33" s="45"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="45"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="53"/>
+      <c r="O33" s="53"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="11"/>
       <c r="Z33" s="11"/>
@@ -2588,31 +2588,31 @@
       <c r="AN33" s="3"/>
     </row>
     <row r="34" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="44"/>
-      <c r="Q34" s="44"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="45"/>
-      <c r="U34" s="45"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="45"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="21"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="11"/>
       <c r="Z34" s="11"/>
@@ -2632,85 +2632,85 @@
       <c r="AN34" s="3"/>
     </row>
     <row r="35" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="43" t="s">
+      <c r="A35" s="63" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="43"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="45">
+      <c r="B35" s="63"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="E35" s="63"/>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="63"/>
+      <c r="L35" s="63"/>
+      <c r="M35" s="63"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="63"/>
+      <c r="P35" s="14">
         <f>SUM(P25:Q34)/10</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="45"/>
-      <c r="R35" s="45">
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14">
         <f>SUM(R25:S34)/10</f>
         <v>0</v>
       </c>
-      <c r="S35" s="45"/>
-      <c r="T35" s="45">
+      <c r="S35" s="14"/>
+      <c r="T35" s="14">
         <f>SUM(T25:U34)/10</f>
         <v>0</v>
       </c>
-      <c r="U35" s="45"/>
-      <c r="V35" s="45">
+      <c r="U35" s="14"/>
+      <c r="V35" s="14">
         <f>SUM(V25:W34)/10</f>
         <v>0</v>
       </c>
-      <c r="W35" s="45"/>
+      <c r="W35" s="14"/>
       <c r="X35" s="3"/>
       <c r="Y35" s="11"/>
       <c r="Z35" s="11"/>
       <c r="AA35" s="11"/>
       <c r="AB35" s="11"/>
       <c r="AC35" s="11"/>
-      <c r="AD35" s="68"/>
-      <c r="AE35" s="68"/>
-      <c r="AF35" s="68"/>
-      <c r="AG35" s="68"/>
-      <c r="AH35" s="68"/>
-      <c r="AI35" s="68"/>
-      <c r="AJ35" s="68"/>
-      <c r="AK35" s="68"/>
-      <c r="AL35" s="68"/>
-      <c r="AM35" s="68"/>
-      <c r="AN35" s="68"/>
+      <c r="AD35" s="16"/>
+      <c r="AE35" s="16"/>
+      <c r="AF35" s="16"/>
+      <c r="AG35" s="16"/>
+      <c r="AH35" s="16"/>
+      <c r="AI35" s="16"/>
+      <c r="AJ35" s="16"/>
+      <c r="AK35" s="16"/>
+      <c r="AL35" s="16"/>
+      <c r="AM35" s="16"/>
+      <c r="AN35" s="16"/>
     </row>
     <row r="36" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="40"/>
-      <c r="B36" s="40"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="40"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="40"/>
-      <c r="M36" s="40"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="40"/>
-      <c r="P36" s="51"/>
-      <c r="Q36" s="51"/>
-      <c r="R36" s="51"/>
-      <c r="S36" s="51"/>
-      <c r="T36" s="51"/>
-      <c r="U36" s="51"/>
-      <c r="V36" s="51"/>
-      <c r="W36" s="51"/>
+      <c r="A36" s="61"/>
+      <c r="B36" s="61"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="61"/>
+      <c r="J36" s="61"/>
+      <c r="K36" s="61"/>
+      <c r="L36" s="61"/>
+      <c r="M36" s="61"/>
+      <c r="N36" s="61"/>
+      <c r="O36" s="61"/>
+      <c r="P36" s="49"/>
+      <c r="Q36" s="49"/>
+      <c r="R36" s="49"/>
+      <c r="S36" s="49"/>
+      <c r="T36" s="49"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="49"/>
+      <c r="W36" s="49"/>
       <c r="X36" s="3"/>
       <c r="Y36" s="11"/>
       <c r="Z36" s="11"/>
@@ -2732,29 +2732,29 @@
       <c r="AN36" s="12"/>
     </row>
     <row r="37" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="40"/>
-      <c r="B37" s="40"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="40"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="40"/>
-      <c r="M37" s="40"/>
-      <c r="N37" s="40"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="51"/>
-      <c r="Q37" s="51"/>
-      <c r="R37" s="51"/>
-      <c r="S37" s="51"/>
-      <c r="T37" s="51"/>
-      <c r="U37" s="51"/>
-      <c r="V37" s="51"/>
-      <c r="W37" s="51"/>
+      <c r="A37" s="61"/>
+      <c r="B37" s="61"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="61"/>
+      <c r="G37" s="61"/>
+      <c r="H37" s="61"/>
+      <c r="I37" s="61"/>
+      <c r="J37" s="61"/>
+      <c r="K37" s="61"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="61"/>
+      <c r="N37" s="61"/>
+      <c r="O37" s="61"/>
+      <c r="P37" s="49"/>
+      <c r="Q37" s="49"/>
+      <c r="R37" s="49"/>
+      <c r="S37" s="49"/>
+      <c r="T37" s="49"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="49"/>
+      <c r="W37" s="49"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="11"/>
       <c r="Z37" s="11"/>
@@ -2763,72 +2763,72 @@
       <c r="AC37" s="11"/>
       <c r="AE37" s="2"/>
       <c r="AF37" s="2"/>
-      <c r="AG37" s="60" t="s">
+      <c r="AG37" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="AH37" s="60"/>
-      <c r="AI37" s="60"/>
-      <c r="AJ37" s="60"/>
-      <c r="AK37" s="60"/>
-      <c r="AL37" s="60"/>
+      <c r="AH37" s="33"/>
+      <c r="AI37" s="33"/>
+      <c r="AJ37" s="33"/>
+      <c r="AK37" s="33"/>
+      <c r="AL37" s="33"/>
       <c r="AM37" s="3"/>
       <c r="AN37" s="3"/>
     </row>
     <row r="38" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="47" t="s">
+      <c r="A38" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="13" t="s">
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13" t="s">
+      <c r="H38" s="17"/>
+      <c r="I38" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13" t="s">
+      <c r="J38" s="17"/>
+      <c r="K38" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13" t="s">
+      <c r="L38" s="17"/>
+      <c r="M38" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13" t="s">
+      <c r="N38" s="17"/>
+      <c r="O38" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="P38" s="13"/>
-      <c r="Q38" s="13" t="s">
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="R38" s="13"/>
-      <c r="S38" s="13" t="s">
+      <c r="R38" s="17"/>
+      <c r="S38" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="T38" s="13"/>
-      <c r="U38" s="13" t="s">
+      <c r="T38" s="17"/>
+      <c r="U38" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="V38" s="13"/>
-      <c r="W38" s="13" t="s">
+      <c r="V38" s="17"/>
+      <c r="W38" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="X38" s="13"/>
-      <c r="Y38" s="13" t="s">
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="Z38" s="13"/>
-      <c r="AA38" s="13" t="s">
+      <c r="Z38" s="17"/>
+      <c r="AA38" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="AB38" s="13"/>
-      <c r="AC38" s="47"/>
-      <c r="AD38" s="47"/>
+      <c r="AB38" s="17"/>
+      <c r="AC38" s="15"/>
+      <c r="AD38" s="15"/>
       <c r="AG38" s="3"/>
       <c r="AH38" s="3"/>
       <c r="AI38" s="3"/>
@@ -2839,61 +2839,61 @@
       <c r="AN38" s="3"/>
     </row>
     <row r="39" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="66" t="s">
+      <c r="A39" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="66"/>
-      <c r="C39" s="66"/>
-      <c r="D39" s="66"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="44">
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="21">
         <v>18</v>
       </c>
-      <c r="H39" s="44"/>
-      <c r="I39" s="44">
+      <c r="H39" s="21"/>
+      <c r="I39" s="21">
         <v>23</v>
       </c>
-      <c r="J39" s="44"/>
-      <c r="K39" s="44">
+      <c r="J39" s="21"/>
+      <c r="K39" s="21">
         <v>22</v>
       </c>
-      <c r="L39" s="44"/>
-      <c r="M39" s="44">
+      <c r="L39" s="21"/>
+      <c r="M39" s="21">
         <v>19</v>
       </c>
-      <c r="N39" s="44"/>
-      <c r="O39" s="44">
+      <c r="N39" s="21"/>
+      <c r="O39" s="21">
         <v>16</v>
       </c>
-      <c r="P39" s="44"/>
-      <c r="Q39" s="44">
+      <c r="P39" s="21"/>
+      <c r="Q39" s="21">
         <v>22</v>
       </c>
-      <c r="R39" s="44"/>
-      <c r="S39" s="44">
+      <c r="R39" s="21"/>
+      <c r="S39" s="21">
         <v>22</v>
       </c>
-      <c r="T39" s="44"/>
-      <c r="U39" s="44">
+      <c r="T39" s="21"/>
+      <c r="U39" s="21">
         <v>20</v>
       </c>
-      <c r="V39" s="44"/>
-      <c r="W39" s="44">
+      <c r="V39" s="21"/>
+      <c r="W39" s="21">
         <v>22</v>
       </c>
-      <c r="X39" s="44"/>
-      <c r="Y39" s="44">
+      <c r="X39" s="21"/>
+      <c r="Y39" s="21">
         <v>16</v>
       </c>
-      <c r="Z39" s="70"/>
-      <c r="AA39" s="45">
+      <c r="Z39" s="22"/>
+      <c r="AA39" s="14">
         <f>SUM(G39:Z39)</f>
         <v>200</v>
       </c>
-      <c r="AB39" s="45"/>
-      <c r="AC39" s="14"/>
-      <c r="AD39" s="14"/>
+      <c r="AB39" s="14"/>
+      <c r="AC39" s="54"/>
+      <c r="AD39" s="54"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
@@ -2904,78 +2904,78 @@
       <c r="AN39" s="3"/>
     </row>
     <row r="40" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="71"/>
-      <c r="K40" s="71"/>
-      <c r="L40" s="71"/>
-      <c r="M40" s="71"/>
-      <c r="N40" s="71"/>
-      <c r="O40" s="71"/>
-      <c r="P40" s="71"/>
-      <c r="Q40" s="72"/>
-      <c r="R40" s="72"/>
-      <c r="S40" s="71"/>
-      <c r="T40" s="71"/>
-      <c r="U40" s="71"/>
-      <c r="V40" s="71"/>
-      <c r="W40" s="72"/>
-      <c r="X40" s="72"/>
-      <c r="Y40" s="71"/>
-      <c r="Z40" s="73"/>
-      <c r="AA40" s="69">
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="20"/>
+      <c r="R40" s="20"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="19"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="19"/>
+      <c r="Z40" s="23"/>
+      <c r="AA40" s="18">
         <f>SUM(G40:Z40)</f>
         <v>0</v>
       </c>
-      <c r="AB40" s="69"/>
-      <c r="AC40" s="14"/>
-      <c r="AD40" s="14"/>
+      <c r="AB40" s="18"/>
+      <c r="AC40" s="54"/>
+      <c r="AD40" s="54"/>
     </row>
     <row r="41" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="66" t="s">
+      <c r="A41" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="71"/>
-      <c r="K41" s="71"/>
-      <c r="L41" s="71"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="71"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="71"/>
-      <c r="R41" s="71"/>
-      <c r="S41" s="71"/>
-      <c r="T41" s="71"/>
-      <c r="U41" s="71"/>
-      <c r="V41" s="71"/>
-      <c r="W41" s="71"/>
-      <c r="X41" s="71"/>
-      <c r="Y41" s="71"/>
-      <c r="Z41" s="73"/>
-      <c r="AA41" s="45">
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="19"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="19"/>
+      <c r="U41" s="19"/>
+      <c r="V41" s="19"/>
+      <c r="W41" s="19"/>
+      <c r="X41" s="19"/>
+      <c r="Y41" s="19"/>
+      <c r="Z41" s="23"/>
+      <c r="AA41" s="14">
         <f t="shared" ref="AA41" si="5">SUM(G41:Z41)</f>
         <v>0</v>
       </c>
-      <c r="AB41" s="45"/>
-      <c r="AC41" s="14"/>
-      <c r="AD41" s="14"/>
+      <c r="AB41" s="14"/>
+      <c r="AC41" s="54"/>
+      <c r="AD41" s="54"/>
     </row>
     <row r="42" spans="1:40" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E42" s="2"/>
@@ -3044,6 +3044,238 @@
     <row r="82" ht="12.95" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="256">
+    <mergeCell ref="Y38:Z38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="AC41:AD41"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:N2"/>
+    <mergeCell ref="Y24:AJ24"/>
+    <mergeCell ref="Y25:AM25"/>
+    <mergeCell ref="Y26:AM26"/>
+    <mergeCell ref="Y27:AM27"/>
+    <mergeCell ref="Y28:AM28"/>
+    <mergeCell ref="Y29:AM29"/>
+    <mergeCell ref="Y30:AM30"/>
+    <mergeCell ref="AD5:AI6"/>
+    <mergeCell ref="AJ5:AN6"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="N10:Q10"/>
+    <mergeCell ref="R10:U10"/>
+    <mergeCell ref="V10:Y10"/>
+    <mergeCell ref="Z10:AC10"/>
+    <mergeCell ref="AJ10:AN10"/>
+    <mergeCell ref="AJ12:AN12"/>
+    <mergeCell ref="AJ11:AN11"/>
+    <mergeCell ref="AD10:AI10"/>
+    <mergeCell ref="R17:U17"/>
+    <mergeCell ref="R18:U18"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="AC40:AD40"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="T24:U24"/>
+    <mergeCell ref="V24:W24"/>
+    <mergeCell ref="C20:M20"/>
+    <mergeCell ref="N21:AC21"/>
+    <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A32:O32"/>
+    <mergeCell ref="A33:O33"/>
+    <mergeCell ref="A34:O34"/>
+    <mergeCell ref="A35:O35"/>
+    <mergeCell ref="A36:O36"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="V29:W29"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="Z20:AC20"/>
+    <mergeCell ref="R20:U20"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="AC38:AD38"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="A30:O30"/>
+    <mergeCell ref="A26:O26"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="T33:U33"/>
+    <mergeCell ref="V33:W33"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="T34:U34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="T31:U31"/>
+    <mergeCell ref="V31:W31"/>
+    <mergeCell ref="V32:W32"/>
+    <mergeCell ref="T32:U32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="V30:W30"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="T27:U27"/>
+    <mergeCell ref="V27:W27"/>
+    <mergeCell ref="V28:W28"/>
+    <mergeCell ref="T28:U28"/>
+    <mergeCell ref="V25:W25"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="T26:U26"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="T29:U29"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="V37:W37"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="V35:W35"/>
+    <mergeCell ref="V36:W36"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="N15:Q15"/>
+    <mergeCell ref="N16:Q16"/>
+    <mergeCell ref="N17:Q17"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="N12:Q12"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="E3:U3"/>
+    <mergeCell ref="Z3:AN3"/>
+    <mergeCell ref="U4:AG4"/>
+    <mergeCell ref="G4:P4"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="N5:AC5"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="R6:U6"/>
+    <mergeCell ref="V6:Y6"/>
+    <mergeCell ref="Z6:AC6"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="AD11:AI11"/>
+    <mergeCell ref="AD12:AI12"/>
+    <mergeCell ref="AD14:AI14"/>
+    <mergeCell ref="AD15:AI15"/>
+    <mergeCell ref="AD16:AI16"/>
+    <mergeCell ref="B16:M16"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A13:M13"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="B15:M15"/>
+    <mergeCell ref="R15:U15"/>
+    <mergeCell ref="R16:U16"/>
+    <mergeCell ref="R12:U12"/>
+    <mergeCell ref="N7:Q7"/>
+    <mergeCell ref="N8:Q8"/>
+    <mergeCell ref="N9:Q9"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="N13:Q13"/>
+    <mergeCell ref="N14:Q14"/>
+    <mergeCell ref="V8:Y8"/>
+    <mergeCell ref="V9:Y9"/>
+    <mergeCell ref="V11:Y11"/>
+    <mergeCell ref="V13:Y13"/>
+    <mergeCell ref="V14:Y14"/>
+    <mergeCell ref="V7:Y7"/>
+    <mergeCell ref="R7:U7"/>
+    <mergeCell ref="R8:U8"/>
+    <mergeCell ref="R9:U9"/>
+    <mergeCell ref="R11:U11"/>
+    <mergeCell ref="R13:U13"/>
+    <mergeCell ref="R14:U14"/>
+    <mergeCell ref="Z13:AC13"/>
+    <mergeCell ref="Z14:AC14"/>
+    <mergeCell ref="Z15:AC15"/>
+    <mergeCell ref="Z16:AC16"/>
+    <mergeCell ref="Z17:AC17"/>
+    <mergeCell ref="V16:Y16"/>
+    <mergeCell ref="V17:Y17"/>
+    <mergeCell ref="V18:Y18"/>
+    <mergeCell ref="V19:Y19"/>
+    <mergeCell ref="AG37:AL37"/>
+    <mergeCell ref="V15:Y15"/>
+    <mergeCell ref="Z18:AC18"/>
+    <mergeCell ref="Z19:AC19"/>
+    <mergeCell ref="O1:AA1"/>
+    <mergeCell ref="Q2:Z2"/>
+    <mergeCell ref="AH4:AN4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="AJ7:AN7"/>
+    <mergeCell ref="AJ8:AN8"/>
+    <mergeCell ref="AJ9:AN9"/>
+    <mergeCell ref="AD7:AI7"/>
+    <mergeCell ref="AD8:AI8"/>
+    <mergeCell ref="AD9:AI9"/>
+    <mergeCell ref="R19:U19"/>
+    <mergeCell ref="Z12:AC12"/>
+    <mergeCell ref="V12:Y12"/>
+    <mergeCell ref="AD18:AI18"/>
+    <mergeCell ref="V20:Y20"/>
+    <mergeCell ref="Z7:AC7"/>
+    <mergeCell ref="Z8:AC8"/>
+    <mergeCell ref="Z9:AC9"/>
+    <mergeCell ref="Z11:AC11"/>
+    <mergeCell ref="AD19:AI19"/>
+    <mergeCell ref="AD20:AI20"/>
+    <mergeCell ref="AJ19:AN19"/>
+    <mergeCell ref="AJ20:AN20"/>
+    <mergeCell ref="AJ18:AN18"/>
+    <mergeCell ref="AD21:AI21"/>
+    <mergeCell ref="AJ13:AN13"/>
+    <mergeCell ref="AJ14:AN14"/>
+    <mergeCell ref="AJ15:AN15"/>
+    <mergeCell ref="AJ16:AN16"/>
+    <mergeCell ref="AJ17:AN17"/>
+    <mergeCell ref="AD13:AI13"/>
+    <mergeCell ref="AD17:AI17"/>
+    <mergeCell ref="AJ21:AN21"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="O41:P41"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="AD22:AI22"/>
     <mergeCell ref="AA41:AB41"/>
     <mergeCell ref="A38:F38"/>
@@ -3068,238 +3300,6 @@
     <mergeCell ref="K39:L39"/>
     <mergeCell ref="M39:N39"/>
     <mergeCell ref="M40:N40"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="AD19:AI19"/>
-    <mergeCell ref="AD20:AI20"/>
-    <mergeCell ref="AJ19:AN19"/>
-    <mergeCell ref="AJ20:AN20"/>
-    <mergeCell ref="AJ18:AN18"/>
-    <mergeCell ref="AD21:AI21"/>
-    <mergeCell ref="AJ13:AN13"/>
-    <mergeCell ref="AJ14:AN14"/>
-    <mergeCell ref="AJ15:AN15"/>
-    <mergeCell ref="AJ16:AN16"/>
-    <mergeCell ref="AJ17:AN17"/>
-    <mergeCell ref="AD13:AI13"/>
-    <mergeCell ref="AD17:AI17"/>
-    <mergeCell ref="AJ21:AN21"/>
-    <mergeCell ref="AG37:AL37"/>
-    <mergeCell ref="V15:Y15"/>
-    <mergeCell ref="Z18:AC18"/>
-    <mergeCell ref="Z19:AC19"/>
-    <mergeCell ref="O1:AA1"/>
-    <mergeCell ref="Q2:Z2"/>
-    <mergeCell ref="AH4:AN4"/>
-    <mergeCell ref="Q4:T4"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="AJ7:AN7"/>
-    <mergeCell ref="AJ8:AN8"/>
-    <mergeCell ref="AJ9:AN9"/>
-    <mergeCell ref="AD7:AI7"/>
-    <mergeCell ref="AD8:AI8"/>
-    <mergeCell ref="AD9:AI9"/>
-    <mergeCell ref="R19:U19"/>
-    <mergeCell ref="Z12:AC12"/>
-    <mergeCell ref="V12:Y12"/>
-    <mergeCell ref="AD18:AI18"/>
-    <mergeCell ref="V20:Y20"/>
-    <mergeCell ref="Z7:AC7"/>
-    <mergeCell ref="Z8:AC8"/>
-    <mergeCell ref="Z9:AC9"/>
-    <mergeCell ref="Z11:AC11"/>
-    <mergeCell ref="Z13:AC13"/>
-    <mergeCell ref="Z14:AC14"/>
-    <mergeCell ref="Z15:AC15"/>
-    <mergeCell ref="Z16:AC16"/>
-    <mergeCell ref="Z17:AC17"/>
-    <mergeCell ref="V16:Y16"/>
-    <mergeCell ref="V17:Y17"/>
-    <mergeCell ref="V18:Y18"/>
-    <mergeCell ref="V19:Y19"/>
-    <mergeCell ref="V8:Y8"/>
-    <mergeCell ref="V9:Y9"/>
-    <mergeCell ref="V11:Y11"/>
-    <mergeCell ref="V13:Y13"/>
-    <mergeCell ref="V14:Y14"/>
-    <mergeCell ref="V7:Y7"/>
-    <mergeCell ref="R7:U7"/>
-    <mergeCell ref="R8:U8"/>
-    <mergeCell ref="R9:U9"/>
-    <mergeCell ref="R11:U11"/>
-    <mergeCell ref="R13:U13"/>
-    <mergeCell ref="R14:U14"/>
-    <mergeCell ref="R15:U15"/>
-    <mergeCell ref="R16:U16"/>
-    <mergeCell ref="R12:U12"/>
-    <mergeCell ref="N7:Q7"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="N13:Q13"/>
-    <mergeCell ref="N14:Q14"/>
-    <mergeCell ref="B16:M16"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="B15:M15"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="N15:Q15"/>
-    <mergeCell ref="N16:Q16"/>
-    <mergeCell ref="N17:Q17"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="E3:U3"/>
-    <mergeCell ref="Z3:AN3"/>
-    <mergeCell ref="U4:AG4"/>
-    <mergeCell ref="G4:P4"/>
-    <mergeCell ref="A5:M6"/>
-    <mergeCell ref="N5:AC5"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="R6:U6"/>
-    <mergeCell ref="V6:Y6"/>
-    <mergeCell ref="Z6:AC6"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="AD11:AI11"/>
-    <mergeCell ref="AD12:AI12"/>
-    <mergeCell ref="AD14:AI14"/>
-    <mergeCell ref="AD15:AI15"/>
-    <mergeCell ref="AD16:AI16"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="U39:V39"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="V37:W37"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="V35:W35"/>
-    <mergeCell ref="V36:W36"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="N19:Q19"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="V30:W30"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="T27:U27"/>
-    <mergeCell ref="V27:W27"/>
-    <mergeCell ref="V28:W28"/>
-    <mergeCell ref="T28:U28"/>
-    <mergeCell ref="V25:W25"/>
-    <mergeCell ref="V26:W26"/>
-    <mergeCell ref="T26:U26"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="T29:U29"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="Z20:AC20"/>
-    <mergeCell ref="R20:U20"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A29:O29"/>
-    <mergeCell ref="AC38:AD38"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A26:O26"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="T33:U33"/>
-    <mergeCell ref="V33:W33"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="T34:U34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="T31:U31"/>
-    <mergeCell ref="V31:W31"/>
-    <mergeCell ref="V32:W32"/>
-    <mergeCell ref="T32:U32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="AC40:AD40"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="T24:U24"/>
-    <mergeCell ref="V24:W24"/>
-    <mergeCell ref="C20:M20"/>
-    <mergeCell ref="N21:AC21"/>
-    <mergeCell ref="A37:O37"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="A33:O33"/>
-    <mergeCell ref="A34:O34"/>
-    <mergeCell ref="A35:O35"/>
-    <mergeCell ref="A36:O36"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="V29:W29"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="AC41:AD41"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:N2"/>
-    <mergeCell ref="Y24:AJ24"/>
-    <mergeCell ref="Y25:AM25"/>
-    <mergeCell ref="Y26:AM26"/>
-    <mergeCell ref="Y27:AM27"/>
-    <mergeCell ref="Y28:AM28"/>
-    <mergeCell ref="Y29:AM29"/>
-    <mergeCell ref="Y30:AM30"/>
-    <mergeCell ref="AD5:AI6"/>
-    <mergeCell ref="AJ5:AN6"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="N10:Q10"/>
-    <mergeCell ref="R10:U10"/>
-    <mergeCell ref="V10:Y10"/>
-    <mergeCell ref="Z10:AC10"/>
-    <mergeCell ref="AJ10:AN10"/>
-    <mergeCell ref="AJ12:AN12"/>
-    <mergeCell ref="AJ11:AN11"/>
-    <mergeCell ref="AD10:AI10"/>
-    <mergeCell ref="R17:U17"/>
-    <mergeCell ref="R18:U18"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="Y38:Z38"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S38:T38"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="W38:X38"/>
   </mergeCells>
   <conditionalFormatting sqref="AD7:AI19">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="lessThan">
